--- a/research/traditional_assets/database/data/bermuda/bermuda_diversified.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_diversified.xlsx
@@ -647,10 +647,10 @@
         <v>0.00276033400041405</v>
       </c>
       <c r="X2">
-        <v>0.1527517320064138</v>
+        <v>0.1527079293300832</v>
       </c>
       <c r="Y2">
-        <v>-0.1499913980059997</v>
+        <v>-0.1499475953296691</v>
       </c>
       <c r="Z2">
         <v>0.8195114293997604</v>
@@ -659,10 +659,10 @@
         <v>0.04941759435624462</v>
       </c>
       <c r="AB2">
-        <v>0.09567619779689535</v>
+        <v>0.09565990743403557</v>
       </c>
       <c r="AC2">
-        <v>-0.04625860344065073</v>
+        <v>-0.04624231307779095</v>
       </c>
       <c r="AD2">
         <v>20188</v>
@@ -781,10 +781,10 @@
         <v>0.00276033400041405</v>
       </c>
       <c r="X3">
-        <v>0.1527517320064138</v>
+        <v>0.1527079293300832</v>
       </c>
       <c r="Y3">
-        <v>-0.1499913980059997</v>
+        <v>-0.1499475953296691</v>
       </c>
       <c r="Z3">
         <v>0.8195114293997604</v>
@@ -793,10 +793,10 @@
         <v>0.04941759435624462</v>
       </c>
       <c r="AB3">
-        <v>0.09567619779689535</v>
+        <v>0.09565990743403557</v>
       </c>
       <c r="AC3">
-        <v>-0.04625860344065073</v>
+        <v>-0.04624231307779095</v>
       </c>
       <c r="AD3">
         <v>20188</v>
@@ -1151,13 +1151,13 @@
         <v>11960.8</v>
       </c>
       <c r="L2">
-        <v>37048.4025677905</v>
+        <v>37048.4883705928</v>
       </c>
       <c r="M2">
         <v>27034.0424251906</v>
       </c>
       <c r="N2">
-        <v>31921.4025677905</v>
+        <v>31921.4883705928</v>
       </c>
       <c r="O2">
         <v>20200.2424251906</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0956761977968953</v>
+        <v>0.0956599074340356</v>
       </c>
       <c r="R2">
-        <v>0.085575709358859</v>
+        <v>0.0855594189959992</v>
       </c>
       <c r="S2">
         <v>0.0618811058765187</v>
       </c>
       <c r="T2">
-        <v>0.0600811058765187</v>
+        <v>0.0586811058765187</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.152751732006414</v>
+        <v>0.152707929330083</v>
       </c>
       <c r="X2">
-        <v>0.085575709358859</v>
+        <v>0.0855594189959992</v>
       </c>
       <c r="Y2">
         <v>1.95805627019448</v>
@@ -1230,7 +1230,7 @@
         <v>11960.8</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788712</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08557570935885898</v>
+        <v>0.0855594189959992</v>
       </c>
       <c r="C2">
-        <v>37048.40256779047</v>
+        <v>37048.48837059282</v>
       </c>
       <c r="D2">
-        <v>31921.40256779047</v>
+        <v>31921.48837059282</v>
       </c>
       <c r="E2">
         <v>-20200.24242519059</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08557570935885898</v>
+        <v>0.0855594189959992</v>
       </c>
       <c r="T2">
         <v>0.7282077218429368</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08571852041762418</v>
+        <v>0.08568823005476439</v>
       </c>
       <c r="C3">
-        <v>36645.40494802807</v>
+        <v>36653.44943373097</v>
       </c>
       <c r="D3">
-        <v>31840.01537227997</v>
+        <v>31848.05985798288</v>
       </c>
       <c r="E3">
         <v>-19878.63200093869</v>
@@ -1533,37 +1533,37 @@
         <v>3542</v>
       </c>
       <c r="M3">
-        <v>19.32270995047087</v>
+        <v>18.8724553565182</v>
       </c>
       <c r="N3">
-        <v>3522.677290049529</v>
+        <v>3523.127544643482</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>3522.677290049529</v>
+        <v>3523.127544643482</v>
       </c>
       <c r="Q3">
-        <v>4685.677290049529</v>
+        <v>4686.127544643482</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08597748420086766</v>
+        <v>0.08596102928888807</v>
       </c>
       <c r="T3">
         <v>0.7355633553969059</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>183.3076213988135</v>
+        <v>187.6809314468272</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08586133147638934</v>
+        <v>0.08581704111352957</v>
       </c>
       <c r="C4">
-        <v>36242.8212844015</v>
+        <v>36258.74753456071</v>
       </c>
       <c r="D4">
-        <v>31759.04213290531</v>
+        <v>31774.96838306452</v>
       </c>
       <c r="E4">
         <v>-19557.02157668678</v>
@@ -1615,37 +1615,37 @@
         <v>3542</v>
       </c>
       <c r="M4">
-        <v>38.64541990094174</v>
+        <v>37.7449107130364</v>
       </c>
       <c r="N4">
-        <v>3503.354580099058</v>
+        <v>3504.255089286964</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>3503.354580099058</v>
+        <v>3504.255089286964</v>
       </c>
       <c r="Q4">
-        <v>4666.354580099058</v>
+        <v>4667.255089286964</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08638745852944793</v>
+        <v>0.08637083571020326</v>
       </c>
       <c r="T4">
         <v>0.743069103921364</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>91.65381069940673</v>
+        <v>93.84046572341362</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08600414253515455</v>
+        <v>0.08594585217229476</v>
       </c>
       <c r="C5">
-        <v>35840.64842669165</v>
+        <v>35864.38035788525</v>
       </c>
       <c r="D5">
-        <v>31678.47969944737</v>
+        <v>31702.21163064097</v>
       </c>
       <c r="E5">
         <v>-19235.41115243488</v>
@@ -1697,37 +1697,37 @@
         <v>3542</v>
       </c>
       <c r="M5">
-        <v>57.9681298514126</v>
+        <v>56.6173660695546</v>
       </c>
       <c r="N5">
-        <v>3484.031870148588</v>
+        <v>3485.382633930446</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3484.031870148588</v>
+        <v>3485.382633930446</v>
       </c>
       <c r="Q5">
-        <v>4647.031870148588</v>
+        <v>4648.382633930445</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08680588593696803</v>
+        <v>0.08678909174845278</v>
       </c>
       <c r="T5">
         <v>0.7507296101473575</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.10254046627117</v>
+        <v>62.56031048227575</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08614695359391972</v>
+        <v>0.08607466323105994</v>
       </c>
       <c r="C6">
-        <v>35438.88325656293</v>
+        <v>35470.34560966431</v>
       </c>
       <c r="D6">
-        <v>31598.32495357056</v>
+        <v>31629.78730667194</v>
       </c>
       <c r="E6">
         <v>-18913.80072818297</v>
@@ -1779,37 +1779,37 @@
         <v>3542</v>
       </c>
       <c r="M6">
-        <v>77.29083980188348</v>
+        <v>75.48982142607281</v>
       </c>
       <c r="N6">
-        <v>3464.709160198116</v>
+        <v>3466.510178573927</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>3464.709160198116</v>
+        <v>3466.510178573927</v>
       </c>
       <c r="Q6">
-        <v>4627.709160198116</v>
+        <v>4629.510178573927</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08723303058214477</v>
+        <v>0.08721606145416583</v>
       </c>
       <c r="T6">
         <v>0.7585497102530592</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.82690534970337</v>
+        <v>46.92023286170681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08628976465268491</v>
+        <v>0.08620347428982512</v>
       </c>
       <c r="C7">
-        <v>35037.52268716084</v>
+        <v>35076.64101677293</v>
       </c>
       <c r="D7">
-        <v>31518.57480842036</v>
+        <v>31557.69313803245</v>
       </c>
       <c r="E7">
         <v>-18592.19030393106</v>
@@ -1861,37 +1861,37 @@
         <v>3542</v>
       </c>
       <c r="M7">
-        <v>96.61354975235433</v>
+        <v>94.362276782591</v>
       </c>
       <c r="N7">
-        <v>3445.386450247646</v>
+        <v>3447.637723217409</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3445.386450247646</v>
+        <v>3447.637723217409</v>
       </c>
       <c r="Q7">
-        <v>4608.386450247646</v>
+        <v>4610.637723217409</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08766916774616734</v>
+        <v>0.08765201999578862</v>
       </c>
       <c r="T7">
         <v>0.7665344440451966</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.6615242797627</v>
+        <v>37.53618628936545</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0864325757114501</v>
+        <v>0.08633228534859032</v>
       </c>
       <c r="C8">
-        <v>34636.56366271571</v>
+        <v>34683.26432676362</v>
       </c>
       <c r="D8">
-        <v>31439.22620822715</v>
+        <v>31485.92687227505</v>
       </c>
       <c r="E8">
         <v>-18270.57987967916</v>
@@ -1943,37 +1943,37 @@
         <v>3542</v>
       </c>
       <c r="M8">
-        <v>115.9362597028252</v>
+        <v>113.2347321391092</v>
       </c>
       <c r="N8">
-        <v>3426.063740297175</v>
+        <v>3428.765267860891</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3426.063740297175</v>
+        <v>3428.765267860891</v>
       </c>
       <c r="Q8">
-        <v>4589.063740297175</v>
+        <v>4591.76526786089</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08811458442431808</v>
+        <v>0.08809725425106298</v>
       </c>
       <c r="T8">
         <v>0.7746890657903583</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.55127023313558</v>
+        <v>31.28015524113787</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08657538677021528</v>
+        <v>0.08646109640735551</v>
       </c>
       <c r="C9">
-        <v>34236.0031581525</v>
+        <v>34290.21330763189</v>
       </c>
       <c r="D9">
-        <v>31360.27612791585</v>
+        <v>31414.48627739523</v>
       </c>
       <c r="E9">
         <v>-17948.96945542725</v>
@@ -2025,37 +2025,37 @@
         <v>3542</v>
       </c>
       <c r="M9">
-        <v>135.2589696532961</v>
+        <v>132.1071874956274</v>
       </c>
       <c r="N9">
-        <v>3406.741030346704</v>
+        <v>3409.892812504373</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>3406.741030346704</v>
+        <v>3409.892812504373</v>
       </c>
       <c r="Q9">
-        <v>4569.741030346704</v>
+        <v>4572.892812504373</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08856957995576234</v>
+        <v>0.08855206343655828</v>
       </c>
       <c r="T9">
         <v>0.7830190557450933</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.18680305697336</v>
+        <v>26.81156163526103</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08671819782898048</v>
+        <v>0.08658990746612068</v>
       </c>
       <c r="C10">
-        <v>33835.83817870624</v>
+        <v>33897.4857475848</v>
       </c>
       <c r="D10">
-        <v>31281.72157272149</v>
+        <v>31343.36914160005</v>
       </c>
       <c r="E10">
         <v>-17627.35903117535</v>
@@ -2107,37 +2107,37 @@
         <v>3542</v>
       </c>
       <c r="M10">
-        <v>154.581679603767</v>
+        <v>150.9796428521456</v>
       </c>
       <c r="N10">
-        <v>3387.418320396233</v>
+        <v>3391.020357147854</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3387.418320396233</v>
+        <v>3391.020357147854</v>
       </c>
       <c r="Q10">
-        <v>4550.418320396233</v>
+        <v>4554.020357147854</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08903446669441194</v>
+        <v>0.08901675977825999</v>
       </c>
       <c r="T10">
         <v>0.7915301324379748</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.91345267485168</v>
+        <v>23.4601164308534</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08686100888774569</v>
+        <v>0.0867187185248859</v>
       </c>
       <c r="C11">
-        <v>33436.06575954339</v>
+        <v>33505.07945481258</v>
       </c>
       <c r="D11">
-        <v>31203.55957781054</v>
+        <v>31272.57327307973</v>
       </c>
       <c r="E11">
         <v>-17305.74860692344</v>
@@ -2189,37 +2189,37 @@
         <v>3542</v>
       </c>
       <c r="M11">
-        <v>173.9043895542378</v>
+        <v>169.8520982086638</v>
       </c>
       <c r="N11">
-        <v>3368.095610445762</v>
+        <v>3372.147901791336</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>3368.095610445762</v>
+        <v>3372.147901791336</v>
       </c>
       <c r="Q11">
-        <v>4531.095610445762</v>
+        <v>4535.147901791336</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08950957072402087</v>
+        <v>0.08949166922637275</v>
       </c>
       <c r="T11">
         <v>0.8002282657614691</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.36751348875706</v>
+        <v>20.85343682742526</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08700381994651087</v>
+        <v>0.08684752958365108</v>
       </c>
       <c r="C12">
-        <v>33036.6829653889</v>
+        <v>33112.99225726369</v>
       </c>
       <c r="D12">
-        <v>31125.78720790796</v>
+        <v>31202.09649978275</v>
       </c>
       <c r="E12">
         <v>-16984.13818267153</v>
@@ -2271,37 +2271,37 @@
         <v>3542</v>
       </c>
       <c r="M12">
-        <v>193.2270995047087</v>
+        <v>188.724553565182</v>
       </c>
       <c r="N12">
-        <v>3348.772900495291</v>
+        <v>3353.275446434818</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>3348.772900495291</v>
+        <v>3353.275446434818</v>
       </c>
       <c r="Q12">
-        <v>4511.772900495291</v>
+        <v>4516.275446434818</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08999523262095444</v>
+        <v>0.0899771322177769</v>
       </c>
       <c r="T12">
         <v>0.8091196909365965</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.33076213988135</v>
+        <v>18.76809314468273</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08714663100527605</v>
+        <v>0.08697634064241626</v>
       </c>
       <c r="C13">
-        <v>32637.68689015868</v>
+        <v>32721.22200242248</v>
       </c>
       <c r="D13">
-        <v>31048.40155692965</v>
+        <v>31131.93666919345</v>
       </c>
       <c r="E13">
         <v>-16662.52775841963</v>
@@ -2353,37 +2353,37 @@
         <v>3542</v>
       </c>
       <c r="M13">
-        <v>212.5498094551795</v>
+        <v>207.5970089217002</v>
       </c>
       <c r="N13">
-        <v>3329.450190544821</v>
+        <v>3334.4029910783</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>3329.450190544821</v>
+        <v>3334.4029910783</v>
       </c>
       <c r="Q13">
-        <v>4492.450190544821</v>
+        <v>4497.402991078299</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09049180826838088</v>
+        <v>0.09047350448988674</v>
       </c>
       <c r="T13">
         <v>0.8182109234190301</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.66432921807395</v>
+        <v>17.06190285880248</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08728944206404123</v>
+        <v>0.08710515170118144</v>
       </c>
       <c r="C14">
-        <v>32239.07465659767</v>
+        <v>32329.76655709016</v>
       </c>
       <c r="D14">
-        <v>30971.39974762054</v>
+        <v>31062.09164811303</v>
       </c>
       <c r="E14">
         <v>-16340.91733416772</v>
@@ -2435,37 +2435,37 @@
         <v>3542</v>
       </c>
       <c r="M14">
-        <v>231.8725194056504</v>
+        <v>226.4694642782184</v>
       </c>
       <c r="N14">
-        <v>3310.127480594349</v>
+        <v>3315.530535721782</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3310.127480594349</v>
+        <v>3315.530535721782</v>
       </c>
       <c r="Q14">
-        <v>4473.127480594349</v>
+        <v>4478.530535721782</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09099966972597612</v>
+        <v>0.09098115794999909</v>
       </c>
       <c r="T14">
         <v>0.827508774821519</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.27563511656779</v>
+        <v>15.64007762056894</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08743225312280642</v>
+        <v>0.08723396275994663</v>
       </c>
       <c r="C15">
-        <v>31840.84341592322</v>
+        <v>31938.62380716849</v>
       </c>
       <c r="D15">
-        <v>30894.77893119799</v>
+        <v>30992.55932244327</v>
       </c>
       <c r="E15">
         <v>-16019.30690991582</v>
@@ -2517,37 +2517,37 @@
         <v>3542</v>
       </c>
       <c r="M15">
-        <v>251.1952293561213</v>
+        <v>245.3419196347366</v>
       </c>
       <c r="N15">
-        <v>3290.804770643879</v>
+        <v>3296.658080365263</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3290.804770643879</v>
+        <v>3296.658080365263</v>
       </c>
       <c r="Q15">
-        <v>4453.804770643879</v>
+        <v>4459.658080365263</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09151920615960803</v>
+        <v>0.09150048160459678</v>
       </c>
       <c r="T15">
         <v>0.8370203699344101</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.10058626144719</v>
+        <v>14.43699472667902</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0875750641815716</v>
+        <v>0.08736277381871183</v>
       </c>
       <c r="C16">
-        <v>31442.99034747376</v>
+        <v>31547.79165744662</v>
       </c>
       <c r="D16">
-        <v>30818.53628700044</v>
+        <v>30923.3375969733</v>
       </c>
       <c r="E16">
         <v>-15697.69648566391</v>
@@ -2599,37 +2599,37 @@
         <v>3542</v>
       </c>
       <c r="M16">
-        <v>270.5179393065922</v>
+        <v>264.2143749912548</v>
       </c>
       <c r="N16">
-        <v>3271.482060693408</v>
+        <v>3277.785625008745</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3271.482060693408</v>
+        <v>3277.785625008745</v>
       </c>
       <c r="Q16">
-        <v>4434.482060693408</v>
+        <v>4440.785625008745</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09205082483588253</v>
+        <v>0.09203188255348743</v>
       </c>
       <c r="T16">
         <v>0.8467531649336475</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.09340152848668</v>
+        <v>13.40578081763052</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08771787524033679</v>
+        <v>0.087491584877477</v>
       </c>
       <c r="C17">
-        <v>31045.5126583627</v>
+        <v>31157.26803139051</v>
       </c>
       <c r="D17">
-        <v>30742.66902214129</v>
+        <v>30854.42439516911</v>
       </c>
       <c r="E17">
         <v>-15376.08606141201</v>
@@ -2681,37 +2681,37 @@
         <v>3542</v>
       </c>
       <c r="M17">
-        <v>289.840649257063</v>
+        <v>283.0868303477729</v>
       </c>
       <c r="N17">
-        <v>3252.159350742937</v>
+        <v>3258.913169652227</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3252.159350742937</v>
+        <v>3258.913169652227</v>
       </c>
       <c r="Q17">
-        <v>4415.159350742937</v>
+        <v>4421.913169652227</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09259495218689293</v>
+        <v>0.0925757870541167</v>
       </c>
       <c r="T17">
         <v>0.8567149668740434</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.22050809325424</v>
+        <v>12.51206209645515</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08786068629910199</v>
+        <v>0.08762039593624218</v>
       </c>
       <c r="C18">
-        <v>30648.40758313735</v>
+        <v>30767.05087093536</v>
       </c>
       <c r="D18">
-        <v>30667.17437116785</v>
+        <v>30785.81765896586</v>
       </c>
       <c r="E18">
         <v>-15054.4756371601</v>
@@ -2763,37 +2763,37 @@
         <v>3542</v>
       </c>
       <c r="M18">
-        <v>309.1633592075339</v>
+        <v>301.9592857042912</v>
       </c>
       <c r="N18">
-        <v>3232.836640792466</v>
+        <v>3240.040714295709</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>3232.836640792466</v>
+        <v>3240.040714295709</v>
       </c>
       <c r="Q18">
-        <v>4395.836640792466</v>
+        <v>4403.040714295708</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0931520349510226</v>
+        <v>0.0931326416619038</v>
       </c>
       <c r="T18">
         <v>0.8669139545749248</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.45672633742584</v>
+        <v>11.7300582154267</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08800349735786715</v>
+        <v>0.08774920699500736</v>
       </c>
       <c r="C19">
-        <v>30251.67238344296</v>
+        <v>30377.13813628067</v>
       </c>
       <c r="D19">
-        <v>30592.04959572536</v>
+        <v>30717.51534856307</v>
       </c>
       <c r="E19">
         <v>-14732.86521290819</v>
@@ -2845,37 +2845,37 @@
         <v>3542</v>
       </c>
       <c r="M19">
-        <v>328.4860691580047</v>
+        <v>320.8317410608094</v>
       </c>
       <c r="N19">
-        <v>3213.513930841995</v>
+        <v>3221.168258939191</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3213.513930841995</v>
+        <v>3221.168258939191</v>
       </c>
       <c r="Q19">
-        <v>4376.513930841995</v>
+        <v>4384.168258939191</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09372254139621564</v>
+        <v>0.09370291445301107</v>
       </c>
       <c r="T19">
         <v>0.8773587010155866</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.78280125875374</v>
+        <v>11.04005479098984</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08814630841663235</v>
+        <v>0.08787801805377257</v>
       </c>
       <c r="C20">
-        <v>29855.30434769152</v>
+        <v>29987.52780568812</v>
       </c>
       <c r="D20">
-        <v>30517.29198422583</v>
+        <v>30649.51544222243</v>
       </c>
       <c r="E20">
         <v>-14411.25478865629</v>
@@ -2927,37 +2927,37 @@
         <v>3542</v>
       </c>
       <c r="M20">
-        <v>347.8087791084756</v>
+        <v>339.7041964173275</v>
       </c>
       <c r="N20">
-        <v>3194.191220891525</v>
+        <v>3202.295803582672</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>3194.191220891525</v>
+        <v>3202.295803582672</v>
       </c>
       <c r="Q20">
-        <v>4357.191220891525</v>
+        <v>4365.295803582672</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09430696263275486</v>
+        <v>0.09428709633658439</v>
       </c>
       <c r="T20">
         <v>0.8880581973694351</v>
       </c>
       <c r="U20">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.18375674437853</v>
+        <v>10.42671841371263</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08828911947539754</v>
+        <v>0.08800682911253775</v>
       </c>
       <c r="C21">
-        <v>29459.30079073564</v>
+        <v>29598.21787528209</v>
       </c>
       <c r="D21">
-        <v>30442.89885152185</v>
+        <v>30581.81593606831</v>
       </c>
       <c r="E21">
         <v>-14089.64436440438</v>
@@ -3009,37 +3009,37 @@
         <v>3542</v>
       </c>
       <c r="M21">
-        <v>367.1314890589465</v>
+        <v>358.5766517738458</v>
       </c>
       <c r="N21">
-        <v>3174.868510941054</v>
+        <v>3183.423348226154</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3174.868510941054</v>
+        <v>3183.423348226154</v>
       </c>
       <c r="Q21">
-        <v>4337.868510941054</v>
+        <v>4346.423348226154</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09490581402328269</v>
+        <v>0.09488570246419653</v>
       </c>
       <c r="T21">
         <v>0.8990218788184404</v>
       </c>
       <c r="U21">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.647769547305973</v>
+        <v>9.877943760359329</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08843193053416275</v>
+        <v>0.08813564017130296</v>
       </c>
       <c r="C22">
-        <v>29063.65905354693</v>
+        <v>29209.2063588528</v>
       </c>
       <c r="D22">
-        <v>30368.86753858505</v>
+        <v>30514.41484389091</v>
       </c>
       <c r="E22">
         <v>-13768.03394015248</v>
@@ -3091,37 +3091,37 @@
         <v>3542</v>
       </c>
       <c r="M22">
-        <v>386.4541990094173</v>
+        <v>377.449107130364</v>
       </c>
       <c r="N22">
-        <v>3155.545800990583</v>
+        <v>3164.550892869636</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>3155.545800990583</v>
+        <v>3164.550892869636</v>
       </c>
       <c r="Q22">
-        <v>4318.545800990583</v>
+        <v>4327.550892869636</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09551963669857373</v>
+        <v>0.095499273744999</v>
       </c>
       <c r="T22">
         <v>0.910259652303671</v>
       </c>
       <c r="U22">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.165381069940675</v>
+        <v>9.384046572341362</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08857474159292791</v>
+        <v>0.08826445123006812</v>
       </c>
       <c r="C23">
-        <v>28668.37650289934</v>
+        <v>28820.49128766207</v>
       </c>
       <c r="D23">
-        <v>30295.19541218936</v>
+        <v>30447.3101969521</v>
       </c>
       <c r="E23">
         <v>-13446.42351590057</v>
@@ -3173,37 +3173,37 @@
         <v>3542</v>
       </c>
       <c r="M23">
-        <v>405.7769089598882</v>
+        <v>396.3215624868822</v>
       </c>
       <c r="N23">
-        <v>3136.223091040112</v>
+        <v>3145.678437513118</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>3136.223091040112</v>
+        <v>3145.678437513118</v>
       </c>
       <c r="Q23">
-        <v>4299.223091040112</v>
+        <v>4308.678437513117</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09614899918842909</v>
+        <v>0.09612837847594835</v>
       </c>
       <c r="T23">
         <v>0.9217819263834643</v>
       </c>
       <c r="U23">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.728934352324451</v>
+        <v>8.937187211753677</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08895955265169309</v>
+        <v>0.08872326228883332</v>
       </c>
       <c r="C24">
-        <v>28150.02074288238</v>
+        <v>28262.24060391155</v>
       </c>
       <c r="D24">
-        <v>30098.45007642431</v>
+        <v>30210.66993745348</v>
       </c>
       <c r="E24">
         <v>-13124.81309164866</v>
@@ -3255,37 +3255,37 @@
         <v>3542</v>
       </c>
       <c r="M24">
-        <v>432.8825911772552</v>
+        <v>425.8071618437132</v>
       </c>
       <c r="N24">
-        <v>3109.117408822745</v>
+        <v>3116.192838156287</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>3109.117408822745</v>
+        <v>3116.192838156287</v>
       </c>
       <c r="Q24">
-        <v>4272.117408822745</v>
+        <v>4279.192838156287</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09679449917802432</v>
+        <v>0.09677361409743486</v>
       </c>
       <c r="T24">
         <v>0.9335996433883804</v>
       </c>
       <c r="U24">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.182357230784628</v>
+        <v>8.318319458656834</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08911336371045829</v>
+        <v>0.0888670733475985</v>
       </c>
       <c r="C25">
-        <v>27750.48313925028</v>
+        <v>27867.21231345746</v>
       </c>
       <c r="D25">
-        <v>30020.52289704412</v>
+        <v>30137.2520712513</v>
       </c>
       <c r="E25">
         <v>-12803.20266739676</v>
@@ -3337,37 +3337,37 @@
         <v>3542</v>
       </c>
       <c r="M25">
-        <v>452.5590725944031</v>
+        <v>445.1620328366093</v>
       </c>
       <c r="N25">
-        <v>3089.440927405597</v>
+        <v>3096.837967163391</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>3089.440927405597</v>
+        <v>3096.837967163391</v>
       </c>
       <c r="Q25">
-        <v>4252.440927405597</v>
+        <v>4259.83796716339</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09745676540111556</v>
+        <v>0.09743560908571323</v>
       </c>
       <c r="T25">
         <v>0.9457243140817361</v>
       </c>
       <c r="U25">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.826602568576601</v>
+        <v>7.956653395236972</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08926717476922348</v>
+        <v>0.08901088440636369</v>
       </c>
       <c r="C26">
-        <v>27351.34801237904</v>
+        <v>27472.53999760711</v>
       </c>
       <c r="D26">
-        <v>29942.99819442478</v>
+        <v>30064.19017965286</v>
       </c>
       <c r="E26">
         <v>-12481.59224314485</v>
@@ -3419,37 +3419,37 @@
         <v>3542</v>
       </c>
       <c r="M26">
-        <v>472.2355540115511</v>
+        <v>464.5169038295053</v>
       </c>
       <c r="N26">
-        <v>3069.764445988449</v>
+        <v>3077.483096170495</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>3069.764445988449</v>
+        <v>3077.483096170495</v>
       </c>
       <c r="Q26">
-        <v>4232.764445988449</v>
+        <v>4240.483096170495</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09813645968270919</v>
+        <v>0.09811502499473579</v>
       </c>
       <c r="T26">
         <v>0.9581680550564958</v>
       </c>
       <c r="U26">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.500494128219243</v>
+        <v>7.625126170435433</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08942098582798866</v>
+        <v>0.08915469546512887</v>
       </c>
       <c r="C27">
-        <v>26952.6122522439</v>
+        <v>27078.22107364872</v>
       </c>
       <c r="D27">
-        <v>29865.87285854154</v>
+        <v>29991.48167994637</v>
       </c>
       <c r="E27">
         <v>-12159.98181889295</v>
@@ -3501,37 +3501,37 @@
         <v>3542</v>
       </c>
       <c r="M27">
-        <v>491.9120354286991</v>
+        <v>483.8717748224014</v>
       </c>
       <c r="N27">
-        <v>3050.087964571301</v>
+        <v>3058.128225177599</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>3050.087964571301</v>
+        <v>3058.128225177599</v>
       </c>
       <c r="Q27">
-        <v>4213.087964571301</v>
+        <v>4221.128225177599</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09883427914514531</v>
+        <v>0.09881255866133226</v>
       </c>
       <c r="T27">
         <v>0.9709436291239157</v>
       </c>
       <c r="U27">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.200474363090472</v>
+        <v>7.320121123618016</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08957479688675385</v>
+        <v>0.08929850652389407</v>
       </c>
       <c r="C28">
-        <v>26554.27278078018</v>
+        <v>26684.25298379478</v>
       </c>
       <c r="D28">
-        <v>29789.14381132974</v>
+        <v>29919.12401434434</v>
       </c>
       <c r="E28">
         <v>-11838.37139464104</v>
@@ -3583,37 +3583,37 @@
         <v>3542</v>
       </c>
       <c r="M28">
-        <v>511.5885168458471</v>
+        <v>503.2266458152975</v>
       </c>
       <c r="N28">
-        <v>3030.411483154153</v>
+        <v>3038.773354184702</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>3030.411483154153</v>
+        <v>3038.773354184702</v>
       </c>
       <c r="Q28">
-        <v>4193.411483154153</v>
+        <v>4201.773354184703</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09955095859305269</v>
+        <v>0.0995289445891881</v>
       </c>
       <c r="T28">
         <v>0.9840644889769417</v>
       </c>
       <c r="U28">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.923533041433146</v>
+        <v>7.038578003478859</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09032260794551904</v>
+        <v>0.08944231758265925</v>
       </c>
       <c r="C29">
-        <v>25865.163605915</v>
+        <v>26290.63319488212</v>
       </c>
       <c r="D29">
-        <v>29421.64506071646</v>
+        <v>29847.11464968359</v>
       </c>
       <c r="E29">
         <v>-11516.76097038913</v>
@@ -3665,45 +3665,45 @@
         <v>3542</v>
       </c>
       <c r="M29">
-        <v>550.3686574635582</v>
+        <v>522.5815168081936</v>
       </c>
       <c r="N29">
-        <v>2991.631342536442</v>
+        <v>3019.418483191806</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2991.631342536442</v>
+        <v>3019.418483191806</v>
       </c>
       <c r="Q29">
-        <v>4154.631342536442</v>
+        <v>4182.418483191806</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1002872730943274</v>
+        <v>0.100264957528766</v>
       </c>
       <c r="T29">
         <v>0.9975448244423792</v>
       </c>
       <c r="U29">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.435686247693944</v>
+        <v>6.777889929275939</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09049841900428422</v>
+        <v>0.09006212864142443</v>
       </c>
       <c r="C30">
-        <v>25458.46655305599</v>
+        <v>25662.59527231056</v>
       </c>
       <c r="D30">
-        <v>29336.55843210937</v>
+        <v>29540.68715136393</v>
       </c>
       <c r="E30">
         <v>-11195.15054613723</v>
@@ -3747,37 +3747,37 @@
         <v>3542</v>
       </c>
       <c r="M30">
-        <v>570.7526818140605</v>
+        <v>557.2450439954804</v>
       </c>
       <c r="N30">
-        <v>2971.24731818594</v>
+        <v>2984.754956004519</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2971.24731818594</v>
+        <v>2984.754956004519</v>
       </c>
       <c r="Q30">
-        <v>4134.24731818594</v>
+        <v>4147.754956004519</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.101044040776193</v>
+        <v>0.1010214152722211</v>
       </c>
       <c r="T30">
         <v>1.011399613670745</v>
       </c>
       <c r="U30">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.205840310276301</v>
+        <v>6.356270079323895</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09067423006304941</v>
+        <v>0.09022293970018963</v>
       </c>
       <c r="C31">
-        <v>25052.26021766744</v>
+        <v>25262.50696447801</v>
       </c>
       <c r="D31">
-        <v>29251.96252097271</v>
+        <v>29462.20926778328</v>
       </c>
       <c r="E31">
         <v>-10873.54012188532</v>
@@ -3829,37 +3829,37 @@
         <v>3542</v>
       </c>
       <c r="M31">
-        <v>591.1367061645625</v>
+        <v>577.1466527096046</v>
       </c>
       <c r="N31">
-        <v>2950.863293835438</v>
+        <v>2964.853347290396</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2950.863293835438</v>
+        <v>2964.853347290396</v>
       </c>
       <c r="Q31">
-        <v>4113.863293835438</v>
+        <v>4127.853347290396</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1018221258575479</v>
+        <v>0.1017991816845059</v>
       </c>
       <c r="T31">
         <v>1.025644678652024</v>
       </c>
       <c r="U31">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.9918458168185</v>
+        <v>6.137088352450659</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09085004112181461</v>
+        <v>0.0903837507589548</v>
       </c>
       <c r="C32">
-        <v>24646.54036680614</v>
+        <v>24862.83452104974</v>
       </c>
       <c r="D32">
-        <v>29167.85309436332</v>
+        <v>29384.14724860692</v>
       </c>
       <c r="E32">
         <v>-10551.92969763342</v>
@@ -3911,37 +3911,37 @@
         <v>3542</v>
       </c>
       <c r="M32">
-        <v>611.5207305150647</v>
+        <v>597.0482614237288</v>
       </c>
       <c r="N32">
-        <v>2930.479269484935</v>
+        <v>2944.951738576271</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2930.479269484935</v>
+        <v>2944.951738576271</v>
       </c>
       <c r="Q32">
-        <v>4093.479269484935</v>
+        <v>4107.951738576271</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1026224419412271</v>
+        <v>0.1025991699942846</v>
       </c>
       <c r="T32">
         <v>1.04029674548991</v>
       </c>
       <c r="U32">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.792117622924549</v>
+        <v>5.932518740702304</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09149085218057977</v>
+        <v>0.09054456181772</v>
       </c>
       <c r="C33">
-        <v>24022.41273142784</v>
+        <v>24463.57464518245</v>
       </c>
       <c r="D33">
-        <v>28865.33588323692</v>
+        <v>29306.49779699153</v>
       </c>
       <c r="E33">
         <v>-10230.31927338151</v>
@@ -3993,45 +3993,45 @@
         <v>3542</v>
       </c>
       <c r="M33">
-        <v>646.8596395932805</v>
+        <v>616.9498701378532</v>
       </c>
       <c r="N33">
-        <v>2895.14036040672</v>
+        <v>2925.050129862147</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2895.14036040672</v>
+        <v>2925.050129862147</v>
       </c>
       <c r="Q33">
-        <v>4058.14036040672</v>
+        <v>4088.050129862147</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1034459555925492</v>
+        <v>0.1034223463710133</v>
       </c>
       <c r="T33">
         <v>1.0553735099173</v>
       </c>
       <c r="U33">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.475685578755646</v>
+        <v>5.741147168421584</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09168166323934497</v>
+        <v>0.09096137287648519</v>
       </c>
       <c r="C34">
-        <v>23611.93201275016</v>
+        <v>23942.59961608493</v>
       </c>
       <c r="D34">
-        <v>28776.46558881115</v>
+        <v>29107.13319214592</v>
       </c>
       <c r="E34">
         <v>-9908.708849129604</v>
@@ -4075,37 +4075,37 @@
         <v>3542</v>
       </c>
       <c r="M34">
-        <v>667.7260795801606</v>
+        <v>645.0847057128265</v>
       </c>
       <c r="N34">
-        <v>2874.27392041984</v>
+        <v>2896.915294287173</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2874.27392041984</v>
+        <v>2896.915294287173</v>
       </c>
       <c r="Q34">
-        <v>4037.27392041984</v>
+        <v>4059.915294287173</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1042936902336162</v>
+        <v>0.1042697338176459</v>
       </c>
       <c r="T34">
         <v>1.070893708592554</v>
       </c>
       <c r="U34">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.304570404419531</v>
+        <v>5.490751785978318</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09187247429811016</v>
+        <v>0.09113018393525037</v>
       </c>
       <c r="C35">
-        <v>23201.99684031768</v>
+        <v>23541.01491433906</v>
       </c>
       <c r="D35">
-        <v>28688.14084063058</v>
+        <v>29027.15891465195</v>
       </c>
       <c r="E35">
         <v>-9587.098424877699</v>
@@ -4157,37 +4157,37 @@
         <v>3542</v>
       </c>
       <c r="M35">
-        <v>688.5925195670404</v>
+        <v>665.2436027663522</v>
       </c>
       <c r="N35">
-        <v>2853.407480432959</v>
+        <v>2876.756397233648</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2853.407480432959</v>
+        <v>2876.756397233648</v>
       </c>
       <c r="Q35">
-        <v>4016.407480432959</v>
+        <v>4039.756397233648</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1051667303863567</v>
+        <v>0.1051424164119391</v>
       </c>
       <c r="T35">
         <v>1.086877196780503</v>
       </c>
       <c r="U35">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.143825846709849</v>
+        <v>5.324365368221401</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09206328535687533</v>
+        <v>0.09129899499401556</v>
       </c>
       <c r="C36">
-        <v>22792.6022061015</v>
+        <v>23139.86848041861</v>
       </c>
       <c r="D36">
-        <v>28600.3566306663</v>
+        <v>28947.62290498341</v>
       </c>
       <c r="E36">
         <v>-9265.488000625792</v>
@@ -4239,37 +4239,37 @@
         <v>3542</v>
       </c>
       <c r="M36">
-        <v>709.4589595539205</v>
+        <v>685.402499819878</v>
       </c>
       <c r="N36">
-        <v>2832.541040446079</v>
+        <v>2856.597500180122</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2832.541040446079</v>
+        <v>2856.597500180122</v>
       </c>
       <c r="Q36">
-        <v>3995.541040446079</v>
+        <v>4019.597500180122</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1060662263013015</v>
+        <v>0.1060415439333321</v>
       </c>
       <c r="T36">
         <v>1.103345033095359</v>
       </c>
       <c r="U36">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.992536851218382</v>
+        <v>5.167766386803124</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09225409641564053</v>
+        <v>0.09146780605278074</v>
       </c>
       <c r="C37">
-        <v>22383.74316318292</v>
+        <v>22739.15672153429</v>
       </c>
       <c r="D37">
-        <v>28513.10801199963</v>
+        <v>28868.52157035101</v>
       </c>
       <c r="E37">
         <v>-8943.877576373885</v>
@@ -4321,37 +4321,37 @@
         <v>3542</v>
       </c>
       <c r="M37">
-        <v>730.3253995408006</v>
+        <v>705.561396873404</v>
       </c>
       <c r="N37">
-        <v>2811.6746004592</v>
+        <v>2836.438603126596</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2811.6746004592</v>
+        <v>2836.438603126596</v>
       </c>
       <c r="Q37">
-        <v>3974.6746004592</v>
+        <v>3999.438603126596</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1069933990136292</v>
+        <v>0.1069683369169218</v>
       </c>
       <c r="T37">
         <v>1.120319572066057</v>
       </c>
       <c r="U37">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.849892941183571</v>
+        <v>5.020115918608748</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09244490747440573</v>
+        <v>0.09163661711154594</v>
       </c>
       <c r="C38">
-        <v>21975.41482482426</v>
+        <v>22338.87608405996</v>
       </c>
       <c r="D38">
-        <v>28426.39009789287</v>
+        <v>28789.85135712858</v>
       </c>
       <c r="E38">
         <v>-8622.267152121982</v>
@@ -4403,37 +4403,37 @@
         <v>3542</v>
       </c>
       <c r="M38">
-        <v>751.1918395276805</v>
+        <v>725.7202939269296</v>
       </c>
       <c r="N38">
-        <v>2790.808160472319</v>
+        <v>2816.27970607307</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2790.808160472319</v>
+        <v>2816.27970607307</v>
       </c>
       <c r="Q38">
-        <v>3953.808160472319</v>
+        <v>3979.27970607307</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1079495458732171</v>
+        <v>0.1079240921812487</v>
       </c>
       <c r="T38">
         <v>1.137824565379589</v>
       </c>
       <c r="U38">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.715173692817361</v>
+        <v>4.880668254202951</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0926357185331709</v>
+        <v>0.09180542817031115</v>
       </c>
       <c r="C39">
-        <v>21567.61236355635</v>
+        <v>21939.02305300042</v>
       </c>
       <c r="D39">
-        <v>28340.19806087686</v>
+        <v>28711.60875032093</v>
       </c>
       <c r="E39">
         <v>-8300.656727870075</v>
@@ -4485,37 +4485,37 @@
         <v>3542</v>
       </c>
       <c r="M39">
-        <v>772.0582795145606</v>
+        <v>745.8791909804554</v>
       </c>
       <c r="N39">
-        <v>2769.941720485439</v>
+        <v>2796.120809019545</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2769.941720485439</v>
+        <v>2796.120809019545</v>
       </c>
       <c r="Q39">
-        <v>3932.941720485439</v>
+        <v>3959.120809019545</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1089360466013635</v>
+        <v>0.1089101888825384</v>
       </c>
       <c r="T39">
         <v>1.155885272766566</v>
       </c>
       <c r="U39">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.587736565984459</v>
+        <v>4.748758301386655</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.0928265295919361</v>
+        <v>0.09197423922907633</v>
       </c>
       <c r="C40">
-        <v>21160.33101028277</v>
+        <v>21539.59415146795</v>
       </c>
       <c r="D40">
-        <v>28254.52713185519</v>
+        <v>28633.79027304037</v>
       </c>
       <c r="E40">
         <v>-7979.046303618168</v>
@@ -4567,37 +4567,37 @@
         <v>3542</v>
       </c>
       <c r="M40">
-        <v>792.9247195014406</v>
+        <v>766.0380880339814</v>
       </c>
       <c r="N40">
-        <v>2749.07528049856</v>
+        <v>2775.961911966019</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2749.07528049856</v>
+        <v>2775.961911966019</v>
       </c>
       <c r="Q40">
-        <v>3912.07528049856</v>
+        <v>3938.961911966019</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1099543699336435</v>
+        <v>0.1099280951548374</v>
       </c>
       <c r="T40">
         <v>1.17452858361764</v>
       </c>
       <c r="U40">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.46700665635329</v>
+        <v>4.623790977665953</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09301734065070129</v>
+        <v>0.0921430502878415</v>
       </c>
       <c r="C41">
-        <v>20753.56605340026</v>
+        <v>21140.58594016722</v>
       </c>
       <c r="D41">
-        <v>28169.37259922459</v>
+        <v>28556.39248599156</v>
       </c>
       <c r="E41">
         <v>-7657.435879366261</v>
@@ -4649,37 +4649,37 @@
         <v>3542</v>
       </c>
       <c r="M41">
-        <v>813.7911594883207</v>
+        <v>786.1969850875072</v>
       </c>
       <c r="N41">
-        <v>2728.208840511679</v>
+        <v>2755.803014912493</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>2728.208840511679</v>
+        <v>2755.803014912493</v>
       </c>
       <c r="Q41">
-        <v>3891.208840511679</v>
+        <v>3918.803014912493</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1110060809161623</v>
+        <v>0.1109793754032774</v>
       </c>
       <c r="T41">
         <v>1.193783150562191</v>
       </c>
       <c r="U41">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.352468024139101</v>
+        <v>4.505232234648878</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09376815170946648</v>
+        <v>0.09231186134660668</v>
       </c>
       <c r="C42">
-        <v>20101.81115278415</v>
+        <v>20741.9950168887</v>
       </c>
       <c r="D42">
-        <v>27839.22812286038</v>
+        <v>28479.41198696494</v>
       </c>
       <c r="E42">
         <v>-7335.825455114356</v>
@@ -4731,45 +4731,45 @@
         <v>3542</v>
       </c>
       <c r="M42">
-        <v>852.6677832333073</v>
+        <v>806.355882141033</v>
       </c>
       <c r="N42">
-        <v>2689.332216766693</v>
+        <v>2735.644117858967</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>2689.332216766693</v>
+        <v>2735.644117858967</v>
       </c>
       <c r="Q42">
-        <v>3852.332216766693</v>
+        <v>3898.644117858967</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1120928489314316</v>
+        <v>0.1120656983266653</v>
       </c>
       <c r="T42">
         <v>1.213679536404895</v>
       </c>
       <c r="U42">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.154021143579241</v>
+        <v>4.392601428782656</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09397296276823167</v>
+        <v>0.09248067240537186</v>
       </c>
       <c r="C43">
-        <v>19691.48093021222</v>
+        <v>20343.81801600998</v>
       </c>
       <c r="D43">
-        <v>27750.50832454037</v>
+        <v>28402.84541033812</v>
       </c>
       <c r="E43">
         <v>-7014.21503086245</v>
@@ -4813,45 +4813,45 @@
         <v>3542</v>
       </c>
       <c r="M43">
-        <v>873.9844778141401</v>
+        <v>826.5147791945589</v>
       </c>
       <c r="N43">
-        <v>2668.01552218586</v>
+        <v>2715.485220805441</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>2668.01552218586</v>
+        <v>2715.485220805441</v>
       </c>
       <c r="Q43">
-        <v>3831.01552218586</v>
+        <v>3878.485220805441</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.113216456540439</v>
+        <v>0.1131888457559308</v>
       </c>
       <c r="T43">
         <v>1.234250376004978</v>
       </c>
       <c r="U43">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.052703554711455</v>
+        <v>4.285464808568444</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09417777382699685</v>
+        <v>0.09306948346413707</v>
       </c>
       <c r="C44">
-        <v>19281.71438690782</v>
+        <v>19758.33666547222</v>
       </c>
       <c r="D44">
-        <v>27662.35220548787</v>
+        <v>28138.97448405227</v>
       </c>
       <c r="E44">
         <v>-6692.604606610545</v>
@@ -4895,37 +4895,37 @@
         <v>3542</v>
       </c>
       <c r="M44">
-        <v>895.3011723949727</v>
+        <v>860.1813140666646</v>
       </c>
       <c r="N44">
-        <v>2646.698827605027</v>
+        <v>2681.818685933335</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>2646.698827605027</v>
+        <v>2681.818685933335</v>
       </c>
       <c r="Q44">
-        <v>3809.698827605027</v>
+        <v>3844.818685933335</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.114378809239412</v>
+        <v>0.1143507224068952</v>
       </c>
       <c r="T44">
         <v>1.255530554901615</v>
       </c>
       <c r="U44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.956210612932611</v>
+        <v>4.117736507498107</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09438258488576204</v>
+        <v>0.09324829452290226</v>
       </c>
       <c r="C45">
-        <v>18872.50616789677</v>
+        <v>19357.56131210316</v>
       </c>
       <c r="D45">
-        <v>27574.75441072872</v>
+        <v>28059.80955493511</v>
       </c>
       <c r="E45">
         <v>-6370.99418235864</v>
@@ -4977,37 +4977,37 @@
         <v>3542</v>
       </c>
       <c r="M45">
-        <v>916.6178669758053</v>
+        <v>880.6618215444423</v>
       </c>
       <c r="N45">
-        <v>2625.382133024194</v>
+        <v>2661.338178455558</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2625.382133024194</v>
+        <v>2661.338178455558</v>
       </c>
       <c r="Q45">
-        <v>3788.382133024194</v>
+        <v>3824.338178455558</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1155819462436123</v>
+        <v>0.1155533666596477</v>
       </c>
       <c r="T45">
         <v>1.277557406741994</v>
       </c>
       <c r="U45">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.864205714957434</v>
+        <v>4.021975193370244</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09458739594452722</v>
+        <v>0.09342710558166745</v>
       </c>
       <c r="C46">
-        <v>18463.85098582067</v>
+        <v>18957.23014719814</v>
       </c>
       <c r="D46">
-        <v>27487.70965290453</v>
+        <v>27981.08881428201</v>
       </c>
       <c r="E46">
         <v>-6049.383758106733</v>
@@ -5059,37 +5059,37 @@
         <v>3542</v>
       </c>
       <c r="M46">
-        <v>937.9345615566381</v>
+        <v>901.1423290222201</v>
       </c>
       <c r="N46">
-        <v>2604.065438443362</v>
+        <v>2640.85767097778</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2604.065438443362</v>
+        <v>2640.85767097778</v>
       </c>
       <c r="Q46">
-        <v>3767.065438443362</v>
+        <v>3803.85767097778</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1168280524265339</v>
+        <v>0.1167989624928557</v>
       </c>
       <c r="T46">
         <v>1.300370931862387</v>
       </c>
       <c r="U46">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.77638285779931</v>
+        <v>3.930566666248193</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09479220700329241</v>
+        <v>0.09360591664043262</v>
       </c>
       <c r="C47">
-        <v>18055.74361987312</v>
+        <v>18557.33944275385</v>
       </c>
       <c r="D47">
-        <v>27401.21271120889</v>
+        <v>27902.80853408963</v>
       </c>
       <c r="E47">
         <v>-5727.773333854826</v>
@@ -5141,37 +5141,37 @@
         <v>3542</v>
       </c>
       <c r="M47">
-        <v>959.2512561374708</v>
+        <v>921.6228364999979</v>
       </c>
       <c r="N47">
-        <v>2582.748743862529</v>
+        <v>2620.377163500002</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2582.748743862529</v>
+        <v>2620.377163500002</v>
       </c>
       <c r="Q47">
-        <v>3745.748743862529</v>
+        <v>3783.377163500002</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1181194715615618</v>
+        <v>0.1180898527199985</v>
       </c>
       <c r="T47">
         <v>1.32401403971443</v>
       </c>
       <c r="U47">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.692463238737103</v>
+        <v>3.843220740331566</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09499701806205761</v>
+        <v>0.09378472769919782</v>
       </c>
       <c r="C48">
-        <v>17648.17891475586</v>
+        <v>18157.88551236862</v>
       </c>
       <c r="D48">
-        <v>27315.25843034354</v>
+        <v>27824.9650279563</v>
       </c>
       <c r="E48">
         <v>-5406.162909602921</v>
@@ -5223,37 +5223,37 @@
         <v>3542</v>
       </c>
       <c r="M48">
-        <v>980.5679507183035</v>
+        <v>942.1033439777756</v>
       </c>
       <c r="N48">
-        <v>2561.432049281696</v>
+        <v>2599.896656022224</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>2561.432049281696</v>
+        <v>2599.896656022224</v>
       </c>
       <c r="Q48">
-        <v>3724.432049281696</v>
+        <v>3762.896656022224</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1194587210349241</v>
+        <v>0.1194285536962948</v>
       </c>
       <c r="T48">
         <v>1.348532818227661</v>
       </c>
       <c r="U48">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.612192298764557</v>
+        <v>3.759672463367837</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0952018291208228</v>
+        <v>0.093963538757963</v>
       </c>
       <c r="C49">
-        <v>17241.15177965455</v>
+        <v>17758.86471066376</v>
       </c>
       <c r="D49">
-        <v>27229.84171949413</v>
+        <v>27747.55465050335</v>
       </c>
       <c r="E49">
         <v>-5084.552485351014</v>
@@ -5305,37 +5305,37 @@
         <v>3542</v>
       </c>
       <c r="M49">
-        <v>1001.884645299136</v>
+        <v>962.5838514555534</v>
       </c>
       <c r="N49">
-        <v>2540.115354700864</v>
+        <v>2579.416148544447</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2540.115354700864</v>
+        <v>2579.416148544447</v>
       </c>
       <c r="Q49">
-        <v>3703.115354700864</v>
+        <v>3742.416148544447</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1208485082242622</v>
+        <v>0.1208177716905645</v>
       </c>
       <c r="T49">
         <v>1.373976833665919</v>
       </c>
       <c r="U49">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.535337143471695</v>
+        <v>3.67967943223235</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09540664017958797</v>
+        <v>0.09414234981672819</v>
       </c>
       <c r="C50">
-        <v>16834.65718723366</v>
+        <v>17360.27343271453</v>
       </c>
       <c r="D50">
-        <v>27144.95755132514</v>
+        <v>27670.57379680601</v>
       </c>
       <c r="E50">
         <v>-4762.942061099109</v>
@@ -5387,37 +5387,37 @@
         <v>3542</v>
       </c>
       <c r="M50">
-        <v>1023.201339879969</v>
+        <v>983.0643589333311</v>
       </c>
       <c r="N50">
-        <v>2518.798660120031</v>
+        <v>2558.935641066669</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>2518.798660120031</v>
+        <v>2558.935641066669</v>
       </c>
       <c r="Q50">
-        <v>3681.798660120031</v>
+        <v>3721.935641066669</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1222917487670365</v>
+        <v>0.1222604211461523</v>
       </c>
       <c r="T50">
         <v>1.400399465082571</v>
       </c>
       <c r="U50">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.461684286316034</v>
+        <v>3.603019444060843</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09561145123835316</v>
+        <v>0.09432116087549337</v>
       </c>
       <c r="C51">
-        <v>16428.6901726501</v>
+        <v>16962.10811349047</v>
       </c>
       <c r="D51">
-        <v>27060.60096099349</v>
+        <v>27594.01890183386</v>
       </c>
       <c r="E51">
         <v>-4441.331636847204</v>
@@ -5469,37 +5469,37 @@
         <v>3542</v>
       </c>
       <c r="M51">
-        <v>1044.518034460801</v>
+        <v>1003.544866411109</v>
       </c>
       <c r="N51">
-        <v>2497.481965539198</v>
+        <v>2538.455133588891</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>2497.481965539198</v>
+        <v>2538.455133588891</v>
       </c>
       <c r="Q51">
-        <v>3660.481965539198</v>
+        <v>3701.455133588891</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1237915869781549</v>
+        <v>0.1237596450901945</v>
       </c>
       <c r="T51">
         <v>1.427858278123405</v>
       </c>
       <c r="U51">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.391037668227952</v>
+        <v>3.529488434998377</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09581626229711834</v>
+        <v>0.09449997193425856</v>
       </c>
       <c r="C52">
-        <v>16023.24583258529</v>
+        <v>16564.3652273051</v>
       </c>
       <c r="D52">
-        <v>26976.76704518059</v>
+        <v>27517.88643990039</v>
       </c>
       <c r="E52">
         <v>-4119.721212595297</v>
@@ -5551,37 +5551,37 @@
         <v>3542</v>
       </c>
       <c r="M52">
-        <v>1065.834729041634</v>
+        <v>1024.025373888886</v>
       </c>
       <c r="N52">
-        <v>2476.165270958366</v>
+        <v>2517.974626111114</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>2476.165270958366</v>
+        <v>2517.974626111114</v>
       </c>
       <c r="Q52">
-        <v>3639.165270958366</v>
+        <v>3680.974626111114</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.125351418717718</v>
+        <v>0.1253188379919984</v>
       </c>
       <c r="T52">
         <v>1.456415443685874</v>
       </c>
       <c r="U52">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.323216914863393</v>
+        <v>3.45889866629841</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09602107335588353</v>
+        <v>0.09467878299302375</v>
       </c>
       <c r="C53">
-        <v>15618.31932429502</v>
+        <v>16167.04128727466</v>
       </c>
       <c r="D53">
-        <v>26893.45096114222</v>
+        <v>27442.17292412186</v>
       </c>
       <c r="E53">
         <v>-3798.110788343391</v>
@@ -5633,37 +5633,37 @@
         <v>3542</v>
       </c>
       <c r="M53">
-        <v>1087.151423622467</v>
+        <v>1044.505881366664</v>
       </c>
       <c r="N53">
-        <v>2454.848576377533</v>
+        <v>2497.494118633336</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>2454.848576377533</v>
+        <v>2497.494118633336</v>
       </c>
       <c r="Q53">
-        <v>3617.848576377533</v>
+        <v>3660.494118633336</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1269749170588959</v>
+        <v>0.1269416714204065</v>
       </c>
       <c r="T53">
         <v>1.486138207842728</v>
       </c>
       <c r="U53">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.25805579888568</v>
+        <v>3.391077123821971</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09622588441464872</v>
+        <v>0.09485759405178892</v>
       </c>
       <c r="C54">
-        <v>15213.90586467694</v>
+        <v>15770.13284478573</v>
       </c>
       <c r="D54">
-        <v>26810.64792577605</v>
+        <v>27366.87490588484</v>
       </c>
       <c r="E54">
         <v>-3476.500364091484</v>
@@ -5715,37 +5715,37 @@
         <v>3542</v>
       </c>
       <c r="M54">
-        <v>1108.4681182033</v>
+        <v>1064.986388844442</v>
       </c>
       <c r="N54">
-        <v>2433.5318817967</v>
+        <v>2477.013611155558</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>2433.5318817967</v>
+        <v>2477.013611155558</v>
       </c>
       <c r="Q54">
-        <v>3596.5318817967</v>
+        <v>3640.013611155558</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1286660611642896</v>
+        <v>0.1286321229083316</v>
       </c>
       <c r="T54">
         <v>1.517099420506118</v>
       </c>
       <c r="U54">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.19540087967634</v>
+        <v>3.325864102210009</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09643069547341392</v>
+        <v>0.09503640511055411</v>
       </c>
       <c r="C55">
-        <v>14810.00072935523</v>
+        <v>15373.63648897165</v>
       </c>
       <c r="D55">
-        <v>26728.35321470625</v>
+        <v>27291.98897432267</v>
       </c>
       <c r="E55">
         <v>-3154.889939839577</v>
@@ -5797,37 +5797,37 @@
         <v>3542</v>
       </c>
       <c r="M55">
-        <v>1129.784812784132</v>
+        <v>1085.46689632222</v>
       </c>
       <c r="N55">
-        <v>2412.215187215867</v>
+        <v>2456.53310367778</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2412.215187215867</v>
+        <v>2456.53310367778</v>
       </c>
       <c r="Q55">
-        <v>3575.215187215867</v>
+        <v>3619.53310367778</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1304291688486361</v>
+        <v>0.1303945085021259</v>
       </c>
       <c r="T55">
         <v>1.549378131580717</v>
       </c>
       <c r="U55">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V55">
         <v>0</v>
       </c>
       <c r="W55">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.135110297040936</v>
+        <v>3.263111949338122</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09663550653217909</v>
+        <v>0.09521521616931931</v>
       </c>
       <c r="C56">
-        <v>14406.59925178209</v>
+        <v>14977.54884619746</v>
       </c>
       <c r="D56">
-        <v>26646.56216138501</v>
+        <v>27217.51175580038</v>
       </c>
       <c r="E56">
         <v>-2833.279515587674</v>
@@ -5879,37 +5879,37 @@
         <v>3542</v>
       </c>
       <c r="M56">
-        <v>1151.101507364965</v>
+        <v>1105.947403799997</v>
       </c>
       <c r="N56">
-        <v>2390.898492635035</v>
+        <v>2436.052596200003</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>2390.898492635035</v>
+        <v>2436.052596200003</v>
       </c>
       <c r="Q56">
-        <v>3553.898492635035</v>
+        <v>3599.052596200003</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1322689333888239</v>
+        <v>0.13223351955652</v>
       </c>
       <c r="T56">
         <v>1.58306026487595</v>
       </c>
       <c r="U56">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.077052698947586</v>
+        <v>3.202683950276306</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09684031759094427</v>
+        <v>0.0953940272280845</v>
       </c>
       <c r="C57">
-        <v>14003.69682235552</v>
+        <v>14581.8665795533</v>
       </c>
       <c r="D57">
-        <v>26565.27015621035</v>
+        <v>27143.43991340812</v>
       </c>
       <c r="E57">
         <v>-2511.669091335767</v>
@@ -5961,37 +5961,37 @@
         <v>3542</v>
       </c>
       <c r="M57">
-        <v>1172.418201945798</v>
+        <v>1126.427911277775</v>
       </c>
       <c r="N57">
-        <v>2369.581798054202</v>
+        <v>2415.572088722225</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>2369.581798054202</v>
+        <v>2415.572088722225</v>
       </c>
       <c r="Q57">
-        <v>3532.581798054202</v>
+        <v>3578.572088722225</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1341904652419089</v>
+        <v>0.1341542644355538</v>
       </c>
       <c r="T57">
         <v>1.618239381873193</v>
       </c>
       <c r="U57">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.021106286239448</v>
+        <v>3.144453332998554</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09850112864970947</v>
+        <v>0.0955728382868497</v>
       </c>
       <c r="C58">
-        <v>13040.76658630419</v>
+        <v>14186.58638835599</v>
       </c>
       <c r="D58">
-        <v>25923.95034441092</v>
+        <v>27069.77014646272</v>
       </c>
       <c r="E58">
         <v>-2190.05866708386</v>
@@ -6043,45 +6043,45 @@
         <v>3542</v>
       </c>
       <c r="M58">
-        <v>1240.561374297708</v>
+        <v>1146.908418755553</v>
       </c>
       <c r="N58">
-        <v>2301.438625702292</v>
+        <v>2395.091581244447</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>2301.438625702292</v>
+        <v>2395.091581244447</v>
       </c>
       <c r="Q58">
-        <v>3464.438625702292</v>
+        <v>3558.091581244447</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1361993394519523</v>
+        <v>0.1361623158999982</v>
       </c>
       <c r="T58">
         <v>1.655017549643038</v>
       </c>
       <c r="U58">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.855159021862305</v>
+        <v>3.08830238062358</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09873193970847466</v>
+        <v>0.09575164934561488</v>
       </c>
       <c r="C59">
-        <v>12632.47128208103</v>
+        <v>13791.70500765881</v>
       </c>
       <c r="D59">
-        <v>25837.26546443968</v>
+        <v>26996.49919001745</v>
       </c>
       <c r="E59">
         <v>-1868.448242831953</v>
@@ -6125,45 +6125,45 @@
         <v>3542</v>
       </c>
       <c r="M59">
-        <v>1262.714255981595</v>
+        <v>1167.388926233331</v>
       </c>
       <c r="N59">
-        <v>2279.285744018404</v>
+        <v>2374.61107376667</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>2279.285744018404</v>
+        <v>2374.61107376667</v>
       </c>
       <c r="Q59">
-        <v>3442.285744018404</v>
+        <v>3537.61107376667</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1383016496717651</v>
+        <v>0.1382637651069749</v>
       </c>
       <c r="T59">
         <v>1.693506329867295</v>
       </c>
       <c r="U59">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.805068512706826</v>
+        <v>3.034121637103868</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09896275076723983</v>
+        <v>0.09738046040438006</v>
       </c>
       <c r="C60">
-        <v>12224.75376216426</v>
+        <v>12820.48418888984</v>
       </c>
       <c r="D60">
-        <v>25751.15836877481</v>
+        <v>26346.88879550038</v>
       </c>
       <c r="E60">
         <v>-1546.83781858005</v>
@@ -6207,37 +6207,37 @@
         <v>3542</v>
       </c>
       <c r="M60">
-        <v>1284.867137665483</v>
+        <v>1234.502945227634</v>
       </c>
       <c r="N60">
-        <v>2257.132862334517</v>
+        <v>2307.497054772366</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>2257.132862334517</v>
+        <v>2307.497054772366</v>
       </c>
       <c r="Q60">
-        <v>3420.132862334517</v>
+        <v>3470.497054772366</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1405040699020452</v>
+        <v>0.1404652833238076</v>
       </c>
       <c r="T60">
         <v>1.733827909149849</v>
       </c>
       <c r="U60">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.756705262487743</v>
+        <v>2.869170959609884</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09919356182600501</v>
+        <v>0.09758427146314523</v>
       </c>
       <c r="C61">
-        <v>11817.60826904736</v>
+        <v>12419.78291913284</v>
       </c>
       <c r="D61">
-        <v>25665.62329990981</v>
+        <v>26267.79794999529</v>
       </c>
       <c r="E61">
         <v>-1225.227394328143</v>
@@ -6289,37 +6289,37 @@
         <v>3542</v>
       </c>
       <c r="M61">
-        <v>1307.020019349371</v>
+        <v>1255.787478766042</v>
       </c>
       <c r="N61">
-        <v>2234.979980650629</v>
+        <v>2286.212521233958</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>2234.979980650629</v>
+        <v>2286.212521233958</v>
       </c>
       <c r="Q61">
-        <v>3397.979980650629</v>
+        <v>3449.212521233958</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1428139252655097</v>
+        <v>0.1427741926731687</v>
       </c>
       <c r="T61">
         <v>1.77611639473887</v>
       </c>
       <c r="U61">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.709981444479476</v>
+        <v>2.820540943345309</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09942437288477021</v>
+        <v>0.09778808252191043</v>
       </c>
       <c r="C62">
-        <v>11411.02912146715</v>
+        <v>12019.55507453756</v>
       </c>
       <c r="D62">
-        <v>25580.65457658151</v>
+        <v>26189.18052965192</v>
       </c>
       <c r="E62">
         <v>-903.6169700762402</v>
@@ -6371,37 +6371,37 @@
         <v>3542</v>
       </c>
       <c r="M62">
-        <v>1329.172901033258</v>
+        <v>1277.072012304449</v>
       </c>
       <c r="N62">
-        <v>2212.827098966742</v>
+        <v>2264.927987695551</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>2212.827098966742</v>
+        <v>2264.927987695551</v>
       </c>
       <c r="Q62">
-        <v>3375.827098966742</v>
+        <v>3427.927987695551</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1452392733971475</v>
+        <v>0.145198547489998</v>
       </c>
       <c r="T62">
         <v>1.820519304607342</v>
       </c>
       <c r="U62">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.664815087071485</v>
+        <v>2.773531927622888</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0996551839435354</v>
+        <v>0.09799189358067562</v>
       </c>
       <c r="C63">
-        <v>11005.01071314588</v>
+        <v>11619.79641701723</v>
       </c>
       <c r="D63">
-        <v>25496.24659251214</v>
+        <v>26111.0322963835</v>
       </c>
       <c r="E63">
         <v>-582.0065458243334</v>
@@ -6453,37 +6453,37 @@
         <v>3542</v>
       </c>
       <c r="M63">
-        <v>1351.325782717146</v>
+        <v>1298.356545842857</v>
       </c>
       <c r="N63">
-        <v>2190.674217282854</v>
+        <v>2243.643454157143</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>2190.674217282854</v>
+        <v>2243.643454157143</v>
       </c>
       <c r="Q63">
-        <v>3353.674217282854</v>
+        <v>3406.643454157143</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1477889983560487</v>
+        <v>0.1477472281948697</v>
       </c>
       <c r="T63">
         <v>1.867199286776761</v>
       </c>
       <c r="U63">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.621129593840805</v>
+        <v>2.728064191104481</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09988599500230058</v>
+        <v>0.0981957046394408</v>
       </c>
       <c r="C64">
-        <v>10599.5475115581</v>
+        <v>11220.50275892019</v>
       </c>
       <c r="D64">
-        <v>25412.39381517626</v>
+        <v>26033.34906253836</v>
       </c>
       <c r="E64">
         <v>-260.3961215724266</v>
@@ -6535,37 +6535,37 @@
         <v>3542</v>
       </c>
       <c r="M64">
-        <v>1373.478664401033</v>
+        <v>1319.641079381264</v>
       </c>
       <c r="N64">
-        <v>2168.521335598967</v>
+        <v>2222.358920618735</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>2168.521335598967</v>
+        <v>2222.358920618735</v>
       </c>
       <c r="Q64">
-        <v>3331.521335598967</v>
+        <v>3385.358920618735</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1504729193654184</v>
+        <v>0.1504300499894716</v>
       </c>
       <c r="T64">
         <v>1.916336110112992</v>
       </c>
       <c r="U64">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.578853310069179</v>
+        <v>2.684063155764084</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1001168060610658</v>
+        <v>0.09839951569820599</v>
       </c>
       <c r="C65">
-        <v>10194.6340567219</v>
+        <v>10821.66996228186</v>
       </c>
       <c r="D65">
-        <v>25329.09078459198</v>
+        <v>25956.12669015194</v>
       </c>
       <c r="E65">
         <v>61.21430267948017</v>
@@ -6617,37 +6617,37 @@
         <v>3542</v>
       </c>
       <c r="M65">
-        <v>1395.631546084921</v>
+        <v>1340.925612919672</v>
       </c>
       <c r="N65">
-        <v>2146.368453915079</v>
+        <v>2201.074387080328</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>2146.368453915079</v>
+        <v>2201.074387080328</v>
       </c>
       <c r="Q65">
-        <v>3309.368453915079</v>
+        <v>3364.074387080328</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1533019171861054</v>
+        <v>0.1532578891783762</v>
       </c>
       <c r="T65">
         <v>1.968128977953883</v>
       </c>
       <c r="U65">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.537919130544271</v>
+        <v>2.641458978688465</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.102075617119831</v>
+        <v>0.09860332675697117</v>
       </c>
       <c r="C66">
-        <v>9187.45039406286</v>
+        <v>10423.29393809004</v>
       </c>
       <c r="D66">
-        <v>24643.51754618484</v>
+        <v>25879.36109021202</v>
       </c>
       <c r="E66">
         <v>382.824726931387</v>
@@ -6699,45 +6699,45 @@
         <v>3542</v>
       </c>
       <c r="M66">
-        <v>1473.358709079538</v>
+        <v>1362.21014645808</v>
       </c>
       <c r="N66">
-        <v>2068.641290920462</v>
+        <v>2179.78985354192</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>2068.641290920462</v>
+        <v>2179.78985354192</v>
       </c>
       <c r="Q66">
-        <v>3231.641290920462</v>
+        <v>3342.78985354192</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.156288081552386</v>
+        <v>0.1562428305444422</v>
       </c>
       <c r="T66">
         <v>2.022799227341491</v>
       </c>
       <c r="U66">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.404030992705652</v>
+        <v>2.600186182146457</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1023334281785962</v>
+        <v>0.09880713781573636</v>
       </c>
       <c r="C67">
-        <v>8778.361421897473</v>
+        <v>10025.37064556311</v>
       </c>
       <c r="D67">
-        <v>24556.03899827136</v>
+        <v>25803.048221937</v>
       </c>
       <c r="E67">
         <v>704.4351511832938</v>
@@ -6781,45 +6781,45 @@
         <v>3542</v>
       </c>
       <c r="M67">
-        <v>1496.379938908906</v>
+        <v>1383.494679996487</v>
       </c>
       <c r="N67">
-        <v>2045.620061091094</v>
+        <v>2158.505320003513</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>2045.620061091094</v>
+        <v>2158.505320003513</v>
       </c>
       <c r="Q67">
-        <v>3208.620061091094</v>
+        <v>3321.505320003513</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1594448838824543</v>
+        <v>0.1593983399885691</v>
       </c>
       <c r="T67">
         <v>2.08059349097982</v>
       </c>
       <c r="U67">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.36704590051018</v>
+        <v>2.560183317805742</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1025912392373614</v>
+        <v>0.09901094887450154</v>
       </c>
       <c r="C68">
-        <v>8369.891308456252</v>
+        <v>9627.89609144102</v>
       </c>
       <c r="D68">
-        <v>24469.17930908204</v>
+        <v>25727.18409206681</v>
       </c>
       <c r="E68">
         <v>1026.045575435197</v>
@@ -6863,45 +6863,45 @@
         <v>3542</v>
       </c>
       <c r="M68">
-        <v>1519.401168738274</v>
+        <v>1404.779213534894</v>
       </c>
       <c r="N68">
-        <v>2022.598831261726</v>
+        <v>2137.220786465105</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2022.598831261726</v>
+        <v>2137.220786465105</v>
       </c>
       <c r="Q68">
-        <v>3185.598831261726</v>
+        <v>3300.220786465105</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1627873804672323</v>
+        <v>0.1627394676352918</v>
       </c>
       <c r="T68">
         <v>2.141787417185109</v>
       </c>
       <c r="U68">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.331181568684269</v>
+        <v>2.521392661475352</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1028490502961265</v>
+        <v>0.1015597599332667</v>
       </c>
       <c r="C69">
-        <v>7962.033509800051</v>
+        <v>8393.884473785147</v>
       </c>
       <c r="D69">
-        <v>24382.93193467775</v>
+        <v>24814.78289866284</v>
       </c>
       <c r="E69">
         <v>1347.655999687104</v>
@@ -6945,37 +6945,37 @@
         <v>3542</v>
       </c>
       <c r="M69">
-        <v>1542.422398567641</v>
+        <v>1501.481391560374</v>
       </c>
       <c r="N69">
-        <v>1999.577601432359</v>
+        <v>2040.518608439626</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>1999.577601432359</v>
+        <v>2040.518608439626</v>
       </c>
       <c r="Q69">
-        <v>3162.577601432358</v>
+        <v>3203.518608439626</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.166332452602603</v>
+        <v>0.1662830878666642</v>
       </c>
       <c r="T69">
         <v>2.206690066190718</v>
       </c>
       <c r="U69">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.296387813927787</v>
+        <v>2.35900359465599</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1031068613548917</v>
+        <v>0.1017985709920319</v>
       </c>
       <c r="C70">
-        <v>7554.781573928281</v>
+        <v>7990.091395989562</v>
       </c>
       <c r="D70">
-        <v>24297.29042305789</v>
+        <v>24732.60024511917</v>
       </c>
       <c r="E70">
         <v>1669.266423939011</v>
@@ -7027,37 +7027,37 @@
         <v>3542</v>
       </c>
       <c r="M70">
-        <v>1565.443628397009</v>
+        <v>1523.891561583663</v>
       </c>
       <c r="N70">
-        <v>1976.556371602991</v>
+        <v>2018.108438416337</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>1976.556371602991</v>
+        <v>2018.108438416337</v>
       </c>
       <c r="Q70">
-        <v>3139.556371602991</v>
+        <v>3181.108438416337</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1700990917464343</v>
+        <v>0.1700481843624975</v>
       </c>
       <c r="T70">
         <v>2.275649130759178</v>
       </c>
       <c r="U70">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.262617404899437</v>
+        <v>2.324312365322814</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1066076724136569</v>
+        <v>0.1020373820507971</v>
       </c>
       <c r="C71">
-        <v>6127.085304276821</v>
+        <v>7586.840873352303</v>
       </c>
       <c r="D71">
-        <v>23191.20457765833</v>
+        <v>24650.96014673381</v>
       </c>
       <c r="E71">
         <v>1990.876848190917</v>
@@ -7109,45 +7109,45 @@
         <v>3542</v>
       </c>
       <c r="M71">
-        <v>1692.76311881127</v>
+        <v>1546.301731606952</v>
       </c>
       <c r="N71">
-        <v>1849.23688118873</v>
+        <v>1995.698268393048</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>1849.23688118873</v>
+        <v>1995.698268393048</v>
       </c>
       <c r="Q71">
-        <v>3012.23688118873</v>
+        <v>3158.698268393047</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1741087398672871</v>
+        <v>0.1740561903096748</v>
       </c>
       <c r="T71">
         <v>2.34905716723528</v>
       </c>
       <c r="U71">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.092436892462155</v>
+        <v>2.290626678868859</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1069124834724221</v>
+        <v>0.1022761931095623</v>
       </c>
       <c r="C72">
-        <v>5713.916444282506</v>
+        <v>7184.127550772126</v>
       </c>
       <c r="D72">
-        <v>23099.64614191592</v>
+        <v>24569.85724840554</v>
       </c>
       <c r="E72">
         <v>2312.487272442824</v>
@@ -7191,45 +7191,45 @@
         <v>3542</v>
       </c>
       <c r="M72">
-        <v>1717.295917634622</v>
+        <v>1568.711901630242</v>
       </c>
       <c r="N72">
-        <v>1824.704082365378</v>
+        <v>1973.288098369758</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>1824.704082365378</v>
+        <v>1973.288098369758</v>
       </c>
       <c r="Q72">
-        <v>2987.704082365378</v>
+        <v>3136.288098369759</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1783856978628633</v>
+        <v>0.1783313966533307</v>
       </c>
       <c r="T72">
         <v>2.42735907280979</v>
       </c>
       <c r="U72">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.062544936855552</v>
+        <v>2.257903440599304</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1072172945311873</v>
+        <v>0.1045030041683275</v>
       </c>
       <c r="C73">
-        <v>5301.46768328597</v>
+        <v>6131.191207107229</v>
       </c>
       <c r="D73">
-        <v>23008.80780517129</v>
+        <v>23838.53132899255</v>
       </c>
       <c r="E73">
         <v>2634.097696694727</v>
@@ -7273,37 +7273,37 @@
         <v>3542</v>
       </c>
       <c r="M73">
-        <v>1741.828716457974</v>
+        <v>1655.058223994809</v>
       </c>
       <c r="N73">
-        <v>1800.171283542026</v>
+        <v>1886.941776005191</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>1800.171283542026</v>
+        <v>1886.941776005191</v>
       </c>
       <c r="Q73">
-        <v>2963.171283542026</v>
+        <v>3049.941776005191</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1829576184788241</v>
+        <v>0.1829014448137903</v>
       </c>
       <c r="T73">
         <v>2.51106110980323</v>
       </c>
       <c r="U73">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.033495008167446</v>
+        <v>2.140105978538135</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1075221055899525</v>
+        <v>0.1047698152270927</v>
       </c>
       <c r="C74">
-        <v>4889.730559291245</v>
+        <v>5724.865419716694</v>
       </c>
       <c r="D74">
-        <v>22918.68110542847</v>
+        <v>23753.81596585392</v>
       </c>
       <c r="E74">
         <v>2955.708120946631</v>
@@ -7355,37 +7355,37 @@
         <v>3542</v>
       </c>
       <c r="M74">
-        <v>1766.361515281325</v>
+        <v>1678.368903206004</v>
       </c>
       <c r="N74">
-        <v>1775.638484718675</v>
+        <v>1863.631096793996</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1775.638484718675</v>
+        <v>1863.631096793996</v>
       </c>
       <c r="Q74">
-        <v>2938.638484718675</v>
+        <v>3026.631096793996</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1878561048530678</v>
+        <v>0.1877979249857114</v>
       </c>
       <c r="T74">
         <v>2.600741863724774</v>
       </c>
       <c r="U74">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.005252021942899</v>
+        <v>2.110382284391773</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1146159166487176</v>
+        <v>0.1050366262858579</v>
       </c>
       <c r="C75">
-        <v>2653.383240866428</v>
+        <v>5319.139608812962</v>
       </c>
       <c r="D75">
-        <v>21003.94421125556</v>
+        <v>23669.70057920209</v>
       </c>
       <c r="E75">
         <v>3277.318545198537</v>
@@ -7437,45 +7437,45 @@
         <v>3542</v>
       </c>
       <c r="M75">
-        <v>2009.235631129296</v>
+        <v>1701.679582417198</v>
       </c>
       <c r="N75">
-        <v>1532.764368870704</v>
+        <v>1840.320417582802</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>1532.764368870704</v>
+        <v>1840.320417582802</v>
       </c>
       <c r="Q75">
-        <v>2695.764368870704</v>
+        <v>3003.320417582801</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1931174420698481</v>
+        <v>0.1930571073925896</v>
       </c>
       <c r="T75">
         <v>2.697065636455321</v>
       </c>
       <c r="U75">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.76285944023858</v>
+        <v>2.081472938030241</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1184917277074828</v>
+        <v>0.1053034373446231</v>
       </c>
       <c r="C76">
-        <v>1414.879828749872</v>
+        <v>4914.007423099851</v>
       </c>
       <c r="D76">
-        <v>20087.05122339091</v>
+        <v>23586.17881774089</v>
       </c>
       <c r="E76">
         <v>3598.928969450444</v>
@@ -7519,45 +7519,45 @@
         <v>3542</v>
       </c>
       <c r="M76">
-        <v>2148.615512453003</v>
+        <v>1724.990261628393</v>
       </c>
       <c r="N76">
-        <v>1393.384487546997</v>
+        <v>1817.009738371607</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>1393.384487546997</v>
+        <v>1817.009738371607</v>
       </c>
       <c r="Q76">
-        <v>2556.384487546997</v>
+        <v>2980.009738371607</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.198783497534073</v>
+        <v>0.1987208422923046</v>
       </c>
       <c r="T76">
         <v>2.800798930165141</v>
       </c>
       <c r="U76">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.648503410438574</v>
+        <v>2.053344925354157</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.118936538766248</v>
+        <v>0.1055702484033882</v>
       </c>
       <c r="C77">
-        <v>993.1365464085684</v>
+        <v>4509.462600611612</v>
       </c>
       <c r="D77">
-        <v>19986.91836530151</v>
+        <v>23503.24441950456</v>
       </c>
       <c r="E77">
         <v>3920.539393702351</v>
@@ -7601,45 +7601,45 @@
         <v>3542</v>
       </c>
       <c r="M77">
-        <v>2177.650857215882</v>
+        <v>1748.300940839587</v>
       </c>
       <c r="N77">
-        <v>1364.349142784118</v>
+        <v>1793.699059160413</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>1364.349142784118</v>
+        <v>1793.699059160413</v>
       </c>
       <c r="Q77">
-        <v>2527.349142784118</v>
+        <v>2956.699059160413</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2049028374354359</v>
+        <v>0.2048376759839968</v>
       </c>
       <c r="T77">
         <v>2.912830887371747</v>
       </c>
       <c r="U77">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.626523364966059</v>
+        <v>2.025966993016102</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1193813498250132</v>
+        <v>0.1117650594621534</v>
       </c>
       <c r="C78">
-        <v>572.3866259178903</v>
+        <v>2413.88103092981</v>
       </c>
       <c r="D78">
-        <v>19887.77886906274</v>
+        <v>21729.27327407466</v>
       </c>
       <c r="E78">
         <v>4242.149817954258</v>
@@ -7683,45 +7683,45 @@
         <v>3542</v>
       </c>
       <c r="M78">
-        <v>2206.68620197876</v>
+        <v>1962.262279547312</v>
       </c>
       <c r="N78">
-        <v>1335.31379802124</v>
+        <v>1579.737720452688</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>1335.31379802124</v>
+        <v>1579.737720452688</v>
       </c>
       <c r="Q78">
-        <v>2498.31379802124</v>
+        <v>2742.737720452688</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2115321223285791</v>
+        <v>0.2114642458166633</v>
       </c>
       <c r="T78">
         <v>3.034198841012237</v>
       </c>
       <c r="U78">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.605121741742822</v>
+        <v>1.805059413778839</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1198261608837784</v>
+        <v>0.1121098705209186</v>
       </c>
       <c r="C79">
-        <v>152.615358359737</v>
+        <v>2001.363815644043</v>
       </c>
       <c r="D79">
-        <v>19789.6180257565</v>
+        <v>21638.3664830408</v>
       </c>
       <c r="E79">
         <v>4563.760242206165</v>
@@ -7765,45 +7765,45 @@
         <v>3542</v>
       </c>
       <c r="M79">
-        <v>2235.721546741639</v>
+        <v>1988.081520067672</v>
       </c>
       <c r="N79">
-        <v>1306.278453258361</v>
+        <v>1553.918479932328</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>1306.278453258361</v>
+        <v>1553.918479932328</v>
       </c>
       <c r="Q79">
-        <v>2469.278453258361</v>
+        <v>2716.918479932328</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2187378667776478</v>
+        <v>0.21866703911304</v>
       </c>
       <c r="T79">
         <v>3.166120529751899</v>
       </c>
       <c r="U79">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.584276004837071</v>
+        <v>1.781617083729763</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1202709719425436</v>
+        <v>0.1124546815796838</v>
       </c>
       <c r="C80">
-        <v>-266.1916762129003</v>
+        <v>1589.604068411365</v>
       </c>
       <c r="D80">
-        <v>19692.42141543577</v>
+        <v>21548.21716006003</v>
       </c>
       <c r="E80">
         <v>4885.370666458071</v>
@@ -7847,45 +7847,45 @@
         <v>3542</v>
       </c>
       <c r="M80">
-        <v>2264.756891504517</v>
+        <v>2013.900760588031</v>
       </c>
       <c r="N80">
-        <v>1277.243108495483</v>
+        <v>1528.099239411969</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>1277.243108495483</v>
+        <v>1528.099239411969</v>
       </c>
       <c r="Q80">
-        <v>2440.243108495483</v>
+        <v>2691.099239411969</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2265986789039045</v>
+        <v>0.2265246317999964</v>
       </c>
       <c r="T80">
         <v>3.310035099286077</v>
       </c>
       <c r="U80">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.563964774005826</v>
+        <v>1.758775839066561</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1207157830013088</v>
+        <v>0.115880492638449</v>
       </c>
       <c r="C81">
-        <v>-684.0486158376334</v>
+        <v>411.5137474783878</v>
       </c>
       <c r="D81">
-        <v>19596.17490006294</v>
+        <v>20691.73726337896</v>
       </c>
       <c r="E81">
         <v>5206.981090709975</v>
@@ -7929,37 +7929,37 @@
         <v>3542</v>
       </c>
       <c r="M81">
-        <v>2293.792236267395</v>
+        <v>2138.808172820402</v>
       </c>
       <c r="N81">
-        <v>1248.207763732605</v>
+        <v>1403.191827179598</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>1248.207763732605</v>
+        <v>1403.191827179598</v>
       </c>
       <c r="Q81">
-        <v>2411.207763732605</v>
+        <v>2566.191827179598</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2352081398040904</v>
+        <v>0.2351305666476153</v>
       </c>
       <c r="T81">
         <v>3.4676558182997</v>
       </c>
       <c r="U81">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.544167751550057</v>
+        <v>1.656062495464115</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.121160594060074</v>
+        <v>0.1162643036972142</v>
       </c>
       <c r="C82">
-        <v>-1100.969323498313</v>
+        <v>-1.83001753652934</v>
       </c>
       <c r="D82">
-        <v>19500.86461665416</v>
+        <v>20600.00392261595</v>
       </c>
       <c r="E82">
         <v>5528.591514961881</v>
@@ -8011,37 +8011,37 @@
         <v>3542</v>
       </c>
       <c r="M82">
-        <v>2322.827581030274</v>
+        <v>2165.881693995344</v>
       </c>
       <c r="N82">
-        <v>1219.172418969726</v>
+        <v>1376.118306004656</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>1219.172418969726</v>
+        <v>1376.118306004656</v>
       </c>
       <c r="Q82">
-        <v>2382.172418969726</v>
+        <v>2539.118306004656</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2446785467942949</v>
+        <v>0.244597094979996</v>
       </c>
       <c r="T82">
         <v>3.641038609214684</v>
       </c>
       <c r="U82">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.524865654655681</v>
+        <v>1.635361714270814</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1216054051188391</v>
+        <v>0.1166481147559794</v>
       </c>
       <c r="C83">
-        <v>-1516.96739378159</v>
+        <v>-414.3640038606936</v>
       </c>
       <c r="D83">
-        <v>19406.47697062279</v>
+        <v>20509.08036054369</v>
       </c>
       <c r="E83">
         <v>5850.201939213788</v>
@@ -8093,37 +8093,37 @@
         <v>3542</v>
       </c>
       <c r="M83">
-        <v>2351.862925793152</v>
+        <v>2192.955215170286</v>
       </c>
       <c r="N83">
-        <v>1190.137074206848</v>
+        <v>1349.044784829714</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>1190.137074206848</v>
+        <v>1349.044784829714</v>
       </c>
       <c r="Q83">
-        <v>2353.137074206848</v>
+        <v>2512.044784829714</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2551458387308368</v>
+        <v>0.2550600999789432</v>
       </c>
       <c r="T83">
         <v>3.832672220225984</v>
       </c>
       <c r="U83">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.506040152746351</v>
+        <v>1.615172063477347</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1354162161776044</v>
+        <v>0.1170319258147445</v>
       </c>
       <c r="C84">
-        <v>-4373.983992593898</v>
+        <v>-826.0988868922686</v>
       </c>
       <c r="D84">
-        <v>16871.07079606239</v>
+        <v>20418.95590176402</v>
       </c>
       <c r="E84">
         <v>6171.812363465695</v>
@@ -8175,45 +8175,45 @@
         <v>3542</v>
       </c>
       <c r="M84">
-        <v>2810.762763611129</v>
+        <v>2220.028736345228</v>
       </c>
       <c r="N84">
-        <v>731.2372363888712</v>
+        <v>1321.971263654772</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>731.2372363888712</v>
+        <v>1321.971263654772</v>
       </c>
       <c r="Q84">
-        <v>1894.237236388871</v>
+        <v>2484.971263654772</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2667761631047722</v>
+        <v>0.2666856610888845</v>
       </c>
       <c r="T84">
         <v>4.045598454682984</v>
       </c>
       <c r="U84">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.260156156135146</v>
+        <v>1.595474843191038</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1631650272363696</v>
+        <v>0.1174157368735097</v>
       </c>
       <c r="C85">
-        <v>-8203.419903621911</v>
+        <v>-1237.04515520385</v>
       </c>
       <c r="D85">
-        <v>13363.24530928629</v>
+        <v>20329.62005770435</v>
       </c>
       <c r="E85">
         <v>6493.422787717602</v>
@@ -8257,45 +8257,45 @@
         <v>3542</v>
       </c>
       <c r="M85">
-        <v>3717.923210751411</v>
+        <v>2247.10225752017</v>
       </c>
       <c r="N85">
-        <v>-175.9232107514113</v>
+        <v>1294.89774247983</v>
       </c>
       <c r="O85">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>-175.9232107514113</v>
+        <v>1294.89774247983</v>
       </c>
       <c r="Q85">
-        <v>987.0767892485887</v>
+        <v>2457.89774247983</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2797747609344647</v>
+        <v>0.2796789352705836</v>
       </c>
       <c r="T85">
         <v>4.283574834370218</v>
       </c>
       <c r="U85">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.9526823980003998</v>
+        <v>1.576252254718856</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1640998382951347</v>
+        <v>0.1177995479322749</v>
       </c>
       <c r="C86">
-        <v>-8617.981600202304</v>
+        <v>-1647.213114611623</v>
       </c>
       <c r="D86">
-        <v>13270.2940369578</v>
+        <v>20241.06252254848</v>
       </c>
       <c r="E86">
         <v>6815.033211969505</v>
@@ -8339,45 +8339,45 @@
         <v>3542</v>
       </c>
       <c r="M86">
-        <v>3762.717466302633</v>
+        <v>2274.175778695111</v>
       </c>
       <c r="N86">
-        <v>-220.7174663026331</v>
+        <v>1267.824221304889</v>
       </c>
       <c r="O86">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>-220.7174663026331</v>
+        <v>1267.824221304889</v>
       </c>
       <c r="Q86">
-        <v>942.2825336973669</v>
+        <v>2430.824221304889</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2943981834928686</v>
+        <v>0.2942963687249949</v>
       </c>
       <c r="T86">
         <v>4.551298261518355</v>
       </c>
       <c r="U86">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.9413409408813473</v>
+        <v>1.557487346924585</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1650346493538999</v>
+        <v>0.1181833589910401</v>
       </c>
       <c r="C87">
-        <v>-9031.259139112281</v>
+        <v>-2056.61289213859</v>
       </c>
       <c r="D87">
-        <v>13178.62692229972</v>
+        <v>20153.27316927341</v>
       </c>
       <c r="E87">
         <v>7136.643636221408</v>
@@ -8421,45 +8421,45 @@
         <v>3542</v>
       </c>
       <c r="M87">
-        <v>3807.511721853854</v>
+        <v>2301.249299870053</v>
       </c>
       <c r="N87">
-        <v>-265.5117218538544</v>
+        <v>1240.750700129947</v>
       </c>
       <c r="O87">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>-265.5117218538544</v>
+        <v>1240.750700129947</v>
       </c>
       <c r="Q87">
-        <v>897.4882781461456</v>
+        <v>2403.750700129947</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3109713957257266</v>
+        <v>0.3108627933066613</v>
       </c>
       <c r="T87">
         <v>4.854718145619579</v>
       </c>
       <c r="U87">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.9302663415768611</v>
+        <v>1.539163966372531</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1659694604126651</v>
+        <v>0.1185671700498053</v>
       </c>
       <c r="C88">
-        <v>-9443.278949487594</v>
+        <v>-2465.254439875163</v>
       </c>
       <c r="D88">
-        <v>13088.21753617631</v>
+        <v>20066.24204578875</v>
       </c>
       <c r="E88">
         <v>7458.254060473315</v>
@@ -8503,45 +8503,45 @@
         <v>3542</v>
       </c>
       <c r="M88">
-        <v>3852.305977405076</v>
+        <v>2328.322821044995</v>
       </c>
       <c r="N88">
-        <v>-310.3059774050762</v>
+        <v>1213.677178955005</v>
       </c>
       <c r="O88">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>-310.3059774050762</v>
+        <v>1213.677178955005</v>
       </c>
       <c r="Q88">
-        <v>852.6940225949238</v>
+        <v>2376.677178955005</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3299122097061356</v>
+        <v>0.3297958499714228</v>
       </c>
       <c r="T88">
         <v>5.201483727449548</v>
       </c>
       <c r="U88">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.9194492910934091</v>
+        <v>1.521266710949594</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1669042714714303</v>
+        <v>0.1189509811085705</v>
       </c>
       <c r="C89">
-        <v>-9854.066740157901</v>
+        <v>-2873.147538740075</v>
       </c>
       <c r="D89">
-        <v>12999.04016975791</v>
+        <v>19979.95937117574</v>
       </c>
       <c r="E89">
         <v>7779.864484725222</v>
@@ -8585,45 +8585,45 @@
         <v>3542</v>
       </c>
       <c r="M89">
-        <v>3897.100232956298</v>
+        <v>2355.396342219936</v>
       </c>
       <c r="N89">
-        <v>-355.100232956298</v>
+        <v>1186.603657780064</v>
       </c>
       <c r="O89">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>-355.100232956298</v>
+        <v>1186.603657780064</v>
       </c>
       <c r="Q89">
-        <v>807.899767043702</v>
+        <v>2349.603657780064</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.351766995068146</v>
+        <v>0.3516416845846091</v>
       </c>
       <c r="T89">
         <v>5.601597860330283</v>
       </c>
       <c r="U89">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.9088809084371631</v>
+        <v>1.503780886685806</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1678390825301955</v>
+        <v>0.1318307921673357</v>
       </c>
       <c r="C90">
-        <v>-10263.64752401995</v>
+        <v>-5714.211642984934</v>
       </c>
       <c r="D90">
-        <v>12911.06981014778</v>
+        <v>17460.50569118279</v>
       </c>
       <c r="E90">
         <v>8101.474908977129</v>
@@ -8667,45 +8667,45 @@
         <v>3542</v>
       </c>
       <c r="M90">
-        <v>3941.89448850752</v>
+        <v>2784.35424954006</v>
       </c>
       <c r="N90">
-        <v>-399.8944885075202</v>
+        <v>757.6457504599398</v>
       </c>
       <c r="O90">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>-399.8944885075202</v>
+        <v>757.6457504599398</v>
       </c>
       <c r="Q90">
-        <v>763.1055114924798</v>
+        <v>1920.64575045994</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3772642446571582</v>
+        <v>0.3771284916333266</v>
       </c>
       <c r="T90">
         <v>6.068397682024473</v>
       </c>
       <c r="U90">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8985527162958316</v>
+        <v>1.272108245775513</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1687738935889607</v>
+        <v>0.1323566032261009</v>
       </c>
       <c r="C91">
-        <v>-10672.04564142771</v>
+        <v>-6125.247044717082</v>
       </c>
       <c r="D91">
-        <v>12824.28211699192</v>
+        <v>17371.08071370255</v>
       </c>
       <c r="E91">
         <v>8423.085333229035</v>
@@ -8749,45 +8749,45 @@
         <v>3542</v>
       </c>
       <c r="M91">
-        <v>3986.688744058742</v>
+        <v>2815.994638739379</v>
       </c>
       <c r="N91">
-        <v>-444.688744058742</v>
+        <v>726.0053612606212</v>
       </c>
       <c r="O91">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>-444.688744058742</v>
+        <v>726.0053612606212</v>
       </c>
       <c r="Q91">
-        <v>718.311255941258</v>
+        <v>1889.005361260621</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.407397357807809</v>
+        <v>0.4072492635999928</v>
       </c>
       <c r="T91">
         <v>6.620070198572154</v>
       </c>
       <c r="U91">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8884566183599234</v>
+        <v>1.257814894699383</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1697087046477259</v>
+        <v>0.1586224142848661</v>
       </c>
       <c r="C92">
-        <v>-11079.28478264553</v>
+        <v>-9985.663290622808</v>
       </c>
       <c r="D92">
-        <v>12738.65340002601</v>
+        <v>13832.27489204873</v>
       </c>
       <c r="E92">
         <v>8744.695757480942</v>
@@ -8831,37 +8831,37 @@
         <v>3542</v>
       </c>
       <c r="M92">
-        <v>4031.482999609964</v>
+        <v>3675.460259963104</v>
       </c>
       <c r="N92">
-        <v>-489.4829996099638</v>
+        <v>-133.4602599631039</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-489.4829996099638</v>
+        <v>-133.4602599631039</v>
       </c>
       <c r="Q92">
-        <v>673.5170003900362</v>
+        <v>1029.539740036896</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4435570935885899</v>
+        <v>0.443394189959992</v>
       </c>
       <c r="T92">
         <v>7.282077218429369</v>
       </c>
       <c r="U92">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8785848781559242</v>
+        <v>0.9636888306433644</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.170643515706491</v>
+        <v>0.1594342253436312</v>
       </c>
       <c r="C93">
-        <v>-11485.38800940762</v>
+        <v>-10393.82264892921</v>
       </c>
       <c r="D93">
-        <v>12654.16059751583</v>
+        <v>13745.72595799423</v>
       </c>
       <c r="E93">
         <v>9066.306181732845</v>
@@ -8913,37 +8913,37 @@
         <v>3542</v>
       </c>
       <c r="M93">
-        <v>4076.277255161186</v>
+        <v>3716.298707296027</v>
       </c>
       <c r="N93">
-        <v>-534.2772551611856</v>
+        <v>-174.2987072960268</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-534.2772551611856</v>
+        <v>-174.2987072960268</v>
       </c>
       <c r="Q93">
-        <v>628.7227448388144</v>
+        <v>988.7012927039732</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4877523262095444</v>
+        <v>0.487571322177769</v>
       </c>
       <c r="T93">
         <v>8.091196909365967</v>
       </c>
       <c r="U93">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8689300992750899</v>
+        <v>0.9530988434934375</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1715783267652562</v>
+        <v>0.1602460364023964</v>
       </c>
       <c r="C94">
-        <v>-11890.37777562527</v>
+        <v>-10800.90566370551</v>
       </c>
       <c r="D94">
-        <v>12570.78125555008</v>
+        <v>13660.25336746983</v>
       </c>
       <c r="E94">
         <v>9387.916605984752</v>
@@ -8995,37 +8995,37 @@
         <v>3542</v>
       </c>
       <c r="M94">
-        <v>4121.071510712407</v>
+        <v>3757.137154628951</v>
       </c>
       <c r="N94">
-        <v>-579.071510712407</v>
+        <v>-215.1371546289506</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-579.071510712407</v>
+        <v>-215.1371546289506</v>
       </c>
       <c r="Q94">
-        <v>583.928489287593</v>
+        <v>947.8628453710494</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5429963669857375</v>
+        <v>0.5427927374499901</v>
       </c>
       <c r="T94">
         <v>9.102596523036715</v>
       </c>
       <c r="U94">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V94">
         <v>0</v>
       </c>
       <c r="W94">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8594852068916651</v>
+        <v>0.9427390734554653</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1725131378240214</v>
+        <v>0.1610578474611616</v>
       </c>
       <c r="C95">
-        <v>-12294.27594728076</v>
+        <v>-11206.93228937637</v>
       </c>
       <c r="D95">
-        <v>12488.49350814649</v>
+        <v>13575.83716605088</v>
       </c>
       <c r="E95">
         <v>9709.527030236659</v>
@@ -9077,37 +9077,37 @@
         <v>3542</v>
       </c>
       <c r="M95">
-        <v>4165.86576626363</v>
+        <v>3797.975601961874</v>
       </c>
       <c r="N95">
-        <v>-623.8657662636297</v>
+        <v>-255.975601961874</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-623.8657662636297</v>
+        <v>-255.975601961874</v>
       </c>
       <c r="Q95">
-        <v>539.1342337363703</v>
+        <v>907.024398038126</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6140244194122715</v>
+        <v>0.6137916999428459</v>
       </c>
       <c r="T95">
         <v>10.4029674548991</v>
       </c>
       <c r="U95">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8502434304734749</v>
+        <v>0.9326020941709979</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1734479488827866</v>
+        <v>0.1618696585199268</v>
       </c>
       <c r="C96">
-        <v>-12697.10382154497</v>
+        <v>-11611.92199014681</v>
       </c>
       <c r="D96">
-        <v>12407.27605813419</v>
+        <v>13492.45788953235</v>
       </c>
       <c r="E96">
         <v>10031.13745448857</v>
@@ -9159,37 +9159,37 @@
         <v>3542</v>
       </c>
       <c r="M96">
-        <v>4210.660021814851</v>
+        <v>3838.814049294797</v>
       </c>
       <c r="N96">
-        <v>-668.6600218148515</v>
+        <v>-296.8140492947973</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-668.6600218148515</v>
+        <v>-296.8140492947973</v>
       </c>
       <c r="Q96">
-        <v>494.3399781851485</v>
+        <v>866.1859507052027</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7087284893143169</v>
+        <v>0.7084569832666537</v>
       </c>
       <c r="T96">
         <v>12.13679536404896</v>
       </c>
       <c r="U96">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8411982875960976</v>
+        <v>0.9226807952968383</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1743827599415518</v>
+        <v>0.162681469578692</v>
       </c>
       <c r="C97">
-        <v>-13098.8821451539</v>
+        <v>-12015.89375496434</v>
       </c>
       <c r="D97">
-        <v>12327.10815877717</v>
+        <v>13410.09654896673</v>
       </c>
       <c r="E97">
         <v>10352.74787874047</v>
@@ -9241,37 +9241,37 @@
         <v>3542</v>
       </c>
       <c r="M97">
-        <v>4255.454277366073</v>
+        <v>3879.652496627721</v>
       </c>
       <c r="N97">
-        <v>-713.4542773660733</v>
+        <v>-337.6524966277211</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-713.4542773660733</v>
+        <v>-337.6524966277211</v>
       </c>
       <c r="Q97">
-        <v>449.5457226339267</v>
+        <v>825.3475033722789</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8413141871771808</v>
+        <v>0.840988379919985</v>
       </c>
       <c r="T97">
         <v>14.56415443685876</v>
       </c>
       <c r="U97">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8323435687792966</v>
+        <v>0.9129683658726611</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.175317571000317</v>
+        <v>0.1634932806374572</v>
       </c>
       <c r="C98">
-        <v>-13499.63113207723</v>
+        <v>-12418.86611193638</v>
       </c>
       <c r="D98">
-        <v>12247.96959610575</v>
+        <v>13328.73461624659</v>
       </c>
       <c r="E98">
         <v>10674.35830299238</v>
@@ -9323,37 +9323,37 @@
         <v>3542</v>
       </c>
       <c r="M98">
-        <v>4300.248532917295</v>
+        <v>3920.490943960644</v>
       </c>
       <c r="N98">
-        <v>-758.2485329172951</v>
+        <v>-378.490943960644</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-758.2485329172951</v>
+        <v>-378.490943960644</v>
       </c>
       <c r="Q98">
-        <v>404.7514670827049</v>
+        <v>784.509056039356</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.040192733971474</v>
+        <v>1.039785474899979</v>
       </c>
       <c r="T98">
         <v>18.2051930460734</v>
       </c>
       <c r="U98">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8236733232711789</v>
+        <v>0.9034582787281542</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1762523820590822</v>
+        <v>0.1643050916962224</v>
       </c>
       <c r="C99">
-        <v>-13899.3704805108</v>
+        <v>-12820.85714222606</v>
       </c>
       <c r="D99">
-        <v>12169.84067192407</v>
+        <v>13248.35401020881</v>
       </c>
       <c r="E99">
         <v>10995.96872724428</v>
@@ -9405,37 +9405,37 @@
         <v>3542</v>
       </c>
       <c r="M99">
-        <v>4345.042788468516</v>
+        <v>3961.329391293567</v>
       </c>
       <c r="N99">
-        <v>-803.0427884685159</v>
+        <v>-419.3293912935669</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-803.0427884685159</v>
+        <v>-419.3293912935669</v>
       </c>
       <c r="Q99">
-        <v>359.9572115314841</v>
+        <v>743.6706087064331</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.371656978628632</v>
+        <v>1.371113966533306</v>
       </c>
       <c r="T99">
         <v>24.27359072809788</v>
       </c>
       <c r="U99">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8151818457116824</v>
+        <v>0.8941442758546683</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1771871931178473</v>
+        <v>0.1651169027549875</v>
       </c>
       <c r="C100">
-        <v>-14298.11938922272</v>
+        <v>-13221.88449344821</v>
       </c>
       <c r="D100">
-        <v>12092.70218746406</v>
+        <v>13168.93708323856</v>
       </c>
       <c r="E100">
         <v>11317.57915149619</v>
@@ -9487,37 +9487,37 @@
         <v>3542</v>
       </c>
       <c r="M100">
-        <v>4389.837044019738</v>
+        <v>4002.16783862649</v>
       </c>
       <c r="N100">
-        <v>-847.8370440197377</v>
+        <v>-460.1678386264903</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-847.8370440197377</v>
+        <v>-460.1678386264903</v>
       </c>
       <c r="Q100">
-        <v>315.1629559802623</v>
+        <v>702.8321613735097</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.034585467942947</v>
+        <v>2.033770949799958</v>
       </c>
       <c r="T100">
         <v>36.41038609214681</v>
       </c>
       <c r="U100">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8068636636125837</v>
+        <v>0.8850203546724777</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2621730041766125</v>
+        <v>0.1659287138137527</v>
       </c>
       <c r="C101">
-        <v>-19040.60072990235</v>
+        <v>-13621.96539258635</v>
       </c>
       <c r="D101">
-        <v>7671.831271036335</v>
+        <v>13090.46660835234</v>
       </c>
       <c r="E101">
         <v>11639.18957574809</v>
@@ -9569,45 +9569,45 @@
         <v>3542</v>
       </c>
       <c r="M101">
-        <v>7137.799076450655</v>
+        <v>4043.006285959414</v>
       </c>
       <c r="N101">
-        <v>-3595.799076450655</v>
+        <v>-501.0062859594141</v>
       </c>
       <c r="O101">
         <v>-0</v>
       </c>
       <c r="P101">
-        <v>-3595.799076450655</v>
+        <v>-501.0062859594141</v>
       </c>
       <c r="Q101">
-        <v>-2432.799076450655</v>
+        <v>661.9937140405859</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.023370935885895</v>
+        <v>4.021741899599916</v>
       </c>
       <c r="T101">
         <v>72.82077218429362</v>
       </c>
       <c r="U101">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.4962313959895459</v>
+        <v>0.8760807551303313</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/bermuda/bermuda_diversified.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_diversified.xlsx
@@ -1133,43 +1133,43 @@
         <v>4.58214747736093</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>187.680931446827</v>
       </c>
       <c r="G2">
         <v>4.29335651970045</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0683550317219779</v>
       </c>
       <c r="I2">
         <v>0.628096631885553</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>11960.8</v>
       </c>
       <c r="L2">
-        <v>37048.4883705928</v>
+        <v>36653.449433731</v>
       </c>
       <c r="M2">
         <v>27034.0424251906</v>
       </c>
       <c r="N2">
-        <v>31921.4883705928</v>
+        <v>31848.0598579829</v>
       </c>
       <c r="O2">
         <v>20200.2424251906</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>321.610424251906</v>
       </c>
       <c r="Q2">
         <v>0.0956599074340356</v>
       </c>
       <c r="R2">
-        <v>0.0855594189959992</v>
+        <v>0.08568823005476441</v>
       </c>
       <c r="S2">
         <v>0.0618811058765187</v>
@@ -1191,13 +1191,13 @@
         <v>0.152707929330083</v>
       </c>
       <c r="X2">
-        <v>0.0855594189959992</v>
+        <v>0.0859610292888881</v>
       </c>
       <c r="Y2">
         <v>1.95805627019448</v>
       </c>
       <c r="Z2">
-        <v>0.728207721842937</v>
+        <v>0.735563355396906</v>
       </c>
       <c r="AA2">
         <v>20188</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0855594189959992</v>
+        <v>0.08568823005476439</v>
       </c>
       <c r="C2">
-        <v>37048.48837059282</v>
+        <v>36653.44943373097</v>
       </c>
       <c r="D2">
-        <v>31921.48837059282</v>
+        <v>31848.05985798288</v>
       </c>
       <c r="E2">
-        <v>-20200.24242519059</v>
+        <v>-19878.63200093869</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>321.610424251906</v>
       </c>
       <c r="G2">
         <v>5127</v>
@@ -1451,28 +1451,28 @@
         <v>3542</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>18.8724553565182</v>
       </c>
       <c r="N2">
-        <v>3542</v>
+        <v>3523.127544643482</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>3542</v>
+        <v>3523.127544643482</v>
       </c>
       <c r="Q2">
-        <v>4705</v>
+        <v>4686.127544643482</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0855594189959992</v>
+        <v>0.08596102928888807</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7355633553969059</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>187.6809314468272</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08568823005476439</v>
+        <v>0.08581704111352957</v>
       </c>
       <c r="C3">
-        <v>36653.44943373097</v>
+        <v>36258.74753456071</v>
       </c>
       <c r="D3">
-        <v>31848.05985798288</v>
+        <v>31774.96838306452</v>
       </c>
       <c r="E3">
-        <v>-19878.63200093869</v>
+        <v>-19557.02157668678</v>
       </c>
       <c r="F3">
-        <v>321.610424251906</v>
+        <v>643.2208485038119</v>
       </c>
       <c r="G3">
         <v>5127</v>
@@ -1533,28 +1533,28 @@
         <v>3542</v>
       </c>
       <c r="M3">
-        <v>18.8724553565182</v>
+        <v>37.7449107130364</v>
       </c>
       <c r="N3">
-        <v>3523.127544643482</v>
+        <v>3504.255089286964</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>3523.127544643482</v>
+        <v>3504.255089286964</v>
       </c>
       <c r="Q3">
-        <v>4686.127544643482</v>
+        <v>4667.255089286964</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08596102928888807</v>
+        <v>0.08637083571020326</v>
       </c>
       <c r="T3">
-        <v>0.7355633553969059</v>
+        <v>0.743069103921364</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>187.6809314468272</v>
+        <v>93.84046572341362</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08581704111352957</v>
+        <v>0.08594585217229476</v>
       </c>
       <c r="C4">
-        <v>36258.74753456071</v>
+        <v>35864.38035788525</v>
       </c>
       <c r="D4">
-        <v>31774.96838306452</v>
+        <v>31702.21163064097</v>
       </c>
       <c r="E4">
-        <v>-19557.02157668678</v>
+        <v>-19235.41115243488</v>
       </c>
       <c r="F4">
-        <v>643.2208485038119</v>
+        <v>964.8312727557178</v>
       </c>
       <c r="G4">
         <v>5127</v>
@@ -1615,28 +1615,28 @@
         <v>3542</v>
       </c>
       <c r="M4">
-        <v>37.7449107130364</v>
+        <v>56.6173660695546</v>
       </c>
       <c r="N4">
-        <v>3504.255089286964</v>
+        <v>3485.382633930446</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>3504.255089286964</v>
+        <v>3485.382633930446</v>
       </c>
       <c r="Q4">
-        <v>4667.255089286964</v>
+        <v>4648.382633930445</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08637083571020326</v>
+        <v>0.08678909174845278</v>
       </c>
       <c r="T4">
-        <v>0.743069103921364</v>
+        <v>0.7507296101473575</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>93.84046572341362</v>
+        <v>62.56031048227575</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08594585217229476</v>
+        <v>0.08607466323105994</v>
       </c>
       <c r="C5">
-        <v>35864.38035788525</v>
+        <v>35470.34560966431</v>
       </c>
       <c r="D5">
-        <v>31702.21163064097</v>
+        <v>31629.78730667194</v>
       </c>
       <c r="E5">
-        <v>-19235.41115243488</v>
+        <v>-18913.80072818297</v>
       </c>
       <c r="F5">
-        <v>964.8312727557178</v>
+        <v>1286.441697007624</v>
       </c>
       <c r="G5">
         <v>5127</v>
@@ -1697,28 +1697,28 @@
         <v>3542</v>
       </c>
       <c r="M5">
-        <v>56.6173660695546</v>
+        <v>75.48982142607281</v>
       </c>
       <c r="N5">
-        <v>3485.382633930446</v>
+        <v>3466.510178573927</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>3485.382633930446</v>
+        <v>3466.510178573927</v>
       </c>
       <c r="Q5">
-        <v>4648.382633930445</v>
+        <v>4629.510178573927</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08678909174845278</v>
+        <v>0.08721606145416583</v>
       </c>
       <c r="T5">
-        <v>0.7507296101473575</v>
+        <v>0.7585497102530592</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.56031048227575</v>
+        <v>46.92023286170681</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08607466323105994</v>
+        <v>0.08620347428982512</v>
       </c>
       <c r="C6">
-        <v>35470.34560966431</v>
+        <v>35076.64101677293</v>
       </c>
       <c r="D6">
-        <v>31629.78730667194</v>
+        <v>31557.69313803245</v>
       </c>
       <c r="E6">
-        <v>-18913.80072818297</v>
+        <v>-18592.19030393106</v>
       </c>
       <c r="F6">
-        <v>1286.441697007624</v>
+        <v>1608.05212125953</v>
       </c>
       <c r="G6">
         <v>5127</v>
@@ -1779,28 +1779,28 @@
         <v>3542</v>
       </c>
       <c r="M6">
-        <v>75.48982142607281</v>
+        <v>94.362276782591</v>
       </c>
       <c r="N6">
-        <v>3466.510178573927</v>
+        <v>3447.637723217409</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>3466.510178573927</v>
+        <v>3447.637723217409</v>
       </c>
       <c r="Q6">
-        <v>4629.510178573927</v>
+        <v>4610.637723217409</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08721606145416583</v>
+        <v>0.08765201999578862</v>
       </c>
       <c r="T6">
-        <v>0.7585497102530592</v>
+        <v>0.7665344440451966</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.92023286170681</v>
+        <v>37.53618628936545</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08620347428982512</v>
+        <v>0.08633228534859032</v>
       </c>
       <c r="C7">
-        <v>35076.64101677293</v>
+        <v>34683.26432676362</v>
       </c>
       <c r="D7">
-        <v>31557.69313803245</v>
+        <v>31485.92687227505</v>
       </c>
       <c r="E7">
-        <v>-18592.19030393106</v>
+        <v>-18270.57987967916</v>
       </c>
       <c r="F7">
-        <v>1608.05212125953</v>
+        <v>1929.662545511436</v>
       </c>
       <c r="G7">
         <v>5127</v>
@@ -1861,28 +1861,28 @@
         <v>3542</v>
       </c>
       <c r="M7">
-        <v>94.362276782591</v>
+        <v>113.2347321391092</v>
       </c>
       <c r="N7">
-        <v>3447.637723217409</v>
+        <v>3428.765267860891</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>3447.637723217409</v>
+        <v>3428.765267860891</v>
       </c>
       <c r="Q7">
-        <v>4610.637723217409</v>
+        <v>4591.76526786089</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08765201999578862</v>
+        <v>0.08809725425106298</v>
       </c>
       <c r="T7">
-        <v>0.7665344440451966</v>
+        <v>0.7746890657903583</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.53618628936545</v>
+        <v>31.28015524113787</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08633228534859032</v>
+        <v>0.08646109640735551</v>
       </c>
       <c r="C8">
-        <v>34683.26432676362</v>
+        <v>34290.21330763189</v>
       </c>
       <c r="D8">
-        <v>31485.92687227505</v>
+        <v>31414.48627739523</v>
       </c>
       <c r="E8">
-        <v>-18270.57987967916</v>
+        <v>-17948.96945542725</v>
       </c>
       <c r="F8">
-        <v>1929.662545511436</v>
+        <v>2251.272969763341</v>
       </c>
       <c r="G8">
         <v>5127</v>
@@ -1943,28 +1943,28 @@
         <v>3542</v>
       </c>
       <c r="M8">
-        <v>113.2347321391092</v>
+        <v>132.1071874956274</v>
       </c>
       <c r="N8">
-        <v>3428.765267860891</v>
+        <v>3409.892812504373</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3428.765267860891</v>
+        <v>3409.892812504373</v>
       </c>
       <c r="Q8">
-        <v>4591.76526786089</v>
+        <v>4572.892812504373</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08809725425106298</v>
+        <v>0.08855206343655828</v>
       </c>
       <c r="T8">
-        <v>0.7746890657903583</v>
+        <v>0.7830190557450933</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.28015524113787</v>
+        <v>26.81156163526104</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08646109640735551</v>
+        <v>0.08658990746612068</v>
       </c>
       <c r="C9">
-        <v>34290.21330763189</v>
+        <v>33897.4857475848</v>
       </c>
       <c r="D9">
-        <v>31414.48627739523</v>
+        <v>31343.36914160005</v>
       </c>
       <c r="E9">
-        <v>-17948.96945542725</v>
+        <v>-17627.35903117535</v>
       </c>
       <c r="F9">
-        <v>2251.272969763342</v>
+        <v>2572.883394015248</v>
       </c>
       <c r="G9">
         <v>5127</v>
@@ -2025,28 +2025,28 @@
         <v>3542</v>
       </c>
       <c r="M9">
-        <v>132.1071874956274</v>
+        <v>150.9796428521456</v>
       </c>
       <c r="N9">
-        <v>3409.892812504373</v>
+        <v>3391.020357147854</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>3409.892812504373</v>
+        <v>3391.020357147854</v>
       </c>
       <c r="Q9">
-        <v>4572.892812504373</v>
+        <v>4554.020357147854</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08855206343655828</v>
+        <v>0.08901675977825999</v>
       </c>
       <c r="T9">
-        <v>0.7830190557450933</v>
+        <v>0.7915301324379748</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.81156163526103</v>
+        <v>23.4601164308534</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08658990746612068</v>
+        <v>0.0867187185248859</v>
       </c>
       <c r="C10">
-        <v>33897.4857475848</v>
+        <v>33505.07945481258</v>
       </c>
       <c r="D10">
-        <v>31343.36914160005</v>
+        <v>31272.57327307973</v>
       </c>
       <c r="E10">
-        <v>-17627.35903117535</v>
+        <v>-17305.74860692344</v>
       </c>
       <c r="F10">
-        <v>2572.883394015248</v>
+        <v>2894.493818267153</v>
       </c>
       <c r="G10">
         <v>5127</v>
@@ -2107,28 +2107,28 @@
         <v>3542</v>
       </c>
       <c r="M10">
-        <v>150.9796428521456</v>
+        <v>169.8520982086638</v>
       </c>
       <c r="N10">
-        <v>3391.020357147854</v>
+        <v>3372.147901791336</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3391.020357147854</v>
+        <v>3372.147901791336</v>
       </c>
       <c r="Q10">
-        <v>4554.020357147854</v>
+        <v>4535.147901791336</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08901675977825999</v>
+        <v>0.08949166922637275</v>
       </c>
       <c r="T10">
-        <v>0.7915301324379748</v>
+        <v>0.8002282657614691</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.4601164308534</v>
+        <v>20.85343682742526</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0867187185248859</v>
+        <v>0.08684752958365108</v>
       </c>
       <c r="C11">
-        <v>33505.07945481258</v>
+        <v>33112.99225726369</v>
       </c>
       <c r="D11">
-        <v>31272.57327307973</v>
+        <v>31202.09649978275</v>
       </c>
       <c r="E11">
-        <v>-17305.74860692344</v>
+        <v>-16984.13818267154</v>
       </c>
       <c r="F11">
-        <v>2894.493818267153</v>
+        <v>3216.104242519059</v>
       </c>
       <c r="G11">
         <v>5127</v>
@@ -2189,28 +2189,28 @@
         <v>3542</v>
       </c>
       <c r="M11">
-        <v>169.8520982086638</v>
+        <v>188.724553565182</v>
       </c>
       <c r="N11">
-        <v>3372.147901791336</v>
+        <v>3353.275446434818</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>3372.147901791336</v>
+        <v>3353.275446434818</v>
       </c>
       <c r="Q11">
-        <v>4535.147901791336</v>
+        <v>4516.275446434818</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08949166922637275</v>
+        <v>0.0899771322177769</v>
       </c>
       <c r="T11">
-        <v>0.8002282657614691</v>
+        <v>0.8091196909365965</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.85343682742526</v>
+        <v>18.76809314468273</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08684752958365108</v>
+        <v>0.08697634064241626</v>
       </c>
       <c r="C12">
-        <v>33112.99225726369</v>
+        <v>32721.22200242248</v>
       </c>
       <c r="D12">
-        <v>31202.09649978275</v>
+        <v>31131.93666919345</v>
       </c>
       <c r="E12">
-        <v>-16984.13818267153</v>
+        <v>-16662.52775841963</v>
       </c>
       <c r="F12">
-        <v>3216.104242519059</v>
+        <v>3537.714666770965</v>
       </c>
       <c r="G12">
         <v>5127</v>
@@ -2271,28 +2271,28 @@
         <v>3542</v>
       </c>
       <c r="M12">
-        <v>188.724553565182</v>
+        <v>207.5970089217002</v>
       </c>
       <c r="N12">
-        <v>3353.275446434818</v>
+        <v>3334.4029910783</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>3353.275446434818</v>
+        <v>3334.4029910783</v>
       </c>
       <c r="Q12">
-        <v>4516.275446434818</v>
+        <v>4497.402991078299</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0899771322177769</v>
+        <v>0.09047350448988674</v>
       </c>
       <c r="T12">
-        <v>0.8091196909365965</v>
+        <v>0.8182109234190301</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.76809314468273</v>
+        <v>17.06190285880248</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08697634064241626</v>
+        <v>0.08710515170118144</v>
       </c>
       <c r="C13">
-        <v>32721.22200242248</v>
+        <v>32329.76655709016</v>
       </c>
       <c r="D13">
-        <v>31131.93666919345</v>
+        <v>31062.09164811303</v>
       </c>
       <c r="E13">
-        <v>-16662.52775841963</v>
+        <v>-16340.91733416772</v>
       </c>
       <c r="F13">
-        <v>3537.714666770965</v>
+        <v>3859.325091022871</v>
       </c>
       <c r="G13">
         <v>5127</v>
@@ -2353,28 +2353,28 @@
         <v>3542</v>
       </c>
       <c r="M13">
-        <v>207.5970089217002</v>
+        <v>226.4694642782184</v>
       </c>
       <c r="N13">
-        <v>3334.4029910783</v>
+        <v>3315.530535721782</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>3334.4029910783</v>
+        <v>3315.530535721782</v>
       </c>
       <c r="Q13">
-        <v>4497.402991078299</v>
+        <v>4478.530535721782</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09047350448988674</v>
+        <v>0.09098115794999909</v>
       </c>
       <c r="T13">
-        <v>0.8182109234190301</v>
+        <v>0.827508774821519</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.06190285880248</v>
+        <v>15.64007762056894</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08710515170118144</v>
+        <v>0.08723396275994663</v>
       </c>
       <c r="C14">
-        <v>32329.76655709016</v>
+        <v>31938.62380716849</v>
       </c>
       <c r="D14">
-        <v>31062.09164811303</v>
+        <v>30992.55932244327</v>
       </c>
       <c r="E14">
-        <v>-16340.91733416772</v>
+        <v>-16019.30690991582</v>
       </c>
       <c r="F14">
-        <v>3859.325091022871</v>
+        <v>4180.935515274778</v>
       </c>
       <c r="G14">
         <v>5127</v>
@@ -2435,28 +2435,28 @@
         <v>3542</v>
       </c>
       <c r="M14">
-        <v>226.4694642782184</v>
+        <v>245.3419196347366</v>
       </c>
       <c r="N14">
-        <v>3315.530535721782</v>
+        <v>3296.658080365263</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3315.530535721782</v>
+        <v>3296.658080365263</v>
       </c>
       <c r="Q14">
-        <v>4478.530535721782</v>
+        <v>4459.658080365263</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09098115794999909</v>
+        <v>0.09150048160459678</v>
       </c>
       <c r="T14">
-        <v>0.827508774821519</v>
+        <v>0.8370203699344101</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.64007762056894</v>
+        <v>14.43699472667902</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08723396275994663</v>
+        <v>0.08736277381871183</v>
       </c>
       <c r="C15">
-        <v>31938.62380716849</v>
+        <v>31547.79165744662</v>
       </c>
       <c r="D15">
-        <v>30992.55932244327</v>
+        <v>30923.3375969733</v>
       </c>
       <c r="E15">
-        <v>-16019.30690991582</v>
+        <v>-15697.69648566391</v>
       </c>
       <c r="F15">
-        <v>4180.935515274778</v>
+        <v>4502.545939526683</v>
       </c>
       <c r="G15">
         <v>5127</v>
@@ -2517,28 +2517,28 @@
         <v>3542</v>
       </c>
       <c r="M15">
-        <v>245.3419196347366</v>
+        <v>264.2143749912548</v>
       </c>
       <c r="N15">
-        <v>3296.658080365263</v>
+        <v>3277.785625008745</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>3296.658080365263</v>
+        <v>3277.785625008745</v>
       </c>
       <c r="Q15">
-        <v>4459.658080365263</v>
+        <v>4440.785625008745</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09150048160459678</v>
+        <v>0.09203188255348743</v>
       </c>
       <c r="T15">
-        <v>0.8370203699344101</v>
+        <v>0.8467531649336475</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.43699472667902</v>
+        <v>13.40578081763052</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08736277381871183</v>
+        <v>0.087491584877477</v>
       </c>
       <c r="C16">
-        <v>31547.79165744662</v>
+        <v>31157.26803139051</v>
       </c>
       <c r="D16">
-        <v>30923.3375969733</v>
+        <v>30854.42439516911</v>
       </c>
       <c r="E16">
-        <v>-15697.69648566391</v>
+        <v>-15376.086061412</v>
       </c>
       <c r="F16">
-        <v>4502.545939526683</v>
+        <v>4824.156363778589</v>
       </c>
       <c r="G16">
         <v>5127</v>
@@ -2599,28 +2599,28 @@
         <v>3542</v>
       </c>
       <c r="M16">
-        <v>264.2143749912548</v>
+        <v>283.086830347773</v>
       </c>
       <c r="N16">
-        <v>3277.785625008745</v>
+        <v>3258.913169652227</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>3277.785625008745</v>
+        <v>3258.913169652227</v>
       </c>
       <c r="Q16">
-        <v>4440.785625008745</v>
+        <v>4421.913169652227</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09203188255348743</v>
+        <v>0.0925757870541167</v>
       </c>
       <c r="T16">
-        <v>0.8467531649336475</v>
+        <v>0.8567149668740434</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.40578081763052</v>
+        <v>12.51206209645515</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.087491584877477</v>
+        <v>0.08762039593624218</v>
       </c>
       <c r="C17">
-        <v>31157.26803139051</v>
+        <v>30767.05087093536</v>
       </c>
       <c r="D17">
-        <v>30854.42439516911</v>
+        <v>30785.81765896586</v>
       </c>
       <c r="E17">
-        <v>-15376.08606141201</v>
+        <v>-15054.4756371601</v>
       </c>
       <c r="F17">
-        <v>4824.156363778588</v>
+        <v>5145.766788030495</v>
       </c>
       <c r="G17">
         <v>5127</v>
@@ -2681,28 +2681,28 @@
         <v>3542</v>
       </c>
       <c r="M17">
-        <v>283.0868303477729</v>
+        <v>301.9592857042912</v>
       </c>
       <c r="N17">
-        <v>3258.913169652227</v>
+        <v>3240.040714295709</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>3258.913169652227</v>
+        <v>3240.040714295709</v>
       </c>
       <c r="Q17">
-        <v>4421.913169652227</v>
+        <v>4403.040714295708</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0925757870541167</v>
+        <v>0.0931326416619038</v>
       </c>
       <c r="T17">
-        <v>0.8567149668740434</v>
+        <v>0.8669139545749248</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.51206209645515</v>
+        <v>11.7300582154267</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08762039593624218</v>
+        <v>0.08774920699500736</v>
       </c>
       <c r="C18">
-        <v>30767.05087093536</v>
+        <v>30377.13813628067</v>
       </c>
       <c r="D18">
-        <v>30785.81765896586</v>
+        <v>30717.51534856307</v>
       </c>
       <c r="E18">
-        <v>-15054.4756371601</v>
+        <v>-14732.86521290819</v>
       </c>
       <c r="F18">
-        <v>5145.766788030495</v>
+        <v>5467.377212282401</v>
       </c>
       <c r="G18">
         <v>5127</v>
@@ -2763,28 +2763,28 @@
         <v>3542</v>
       </c>
       <c r="M18">
-        <v>301.9592857042912</v>
+        <v>320.8317410608094</v>
       </c>
       <c r="N18">
-        <v>3240.040714295709</v>
+        <v>3221.168258939191</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>3240.040714295709</v>
+        <v>3221.168258939191</v>
       </c>
       <c r="Q18">
-        <v>4403.040714295708</v>
+        <v>4384.168258939191</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0931326416619038</v>
+        <v>0.09370291445301107</v>
       </c>
       <c r="T18">
-        <v>0.8669139545749248</v>
+        <v>0.8773587010155866</v>
       </c>
       <c r="U18">
         <v>0.05868110587651873</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.7300582154267</v>
+        <v>11.04005479098984</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08774920699500736</v>
+        <v>0.08787801805377257</v>
       </c>
       <c r="C19">
-        <v>30377.13813628067</v>
+        <v>29987.52780568812</v>
       </c>
       <c r="D19">
-        <v>30717.51534856307</v>
+        <v>30649.51544222243</v>
       </c>
       <c r="E19">
-        <v>-14732.86521290819</v>
+        <v>-14411.25478865629</v>
       </c>
       <c r="F19">
-        <v>5467.377212282401</v>
+        <v>5788.987636534307</v>
       </c>
       <c r="G19">
         <v>5127</v>
@@ -2845,28 +2845,28 @@
         <v>3542</v>
       </c>
       <c r="M19">
-        <v>320.8317410608094</v>
+        <v>339.7041964173276</v>
       </c>
       <c r="N19">
-        <v>3221.168258939191</v>
+        <v>3202.295803582672</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3221.168258939191</v>
+        <v>3202.295803582672</v>
       </c>
       <c r="Q19">
-        <v>4384.168258939191</v>
+        <v>4365.295803582672</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09370291445301107</v>
+        <v>0.09428709633658439</v>
       </c>
       <c r="T19">
-        <v>0.8773587010155866</v>
+        <v>0.8880581973694351</v>
       </c>
       <c r="U19">
         <v>0.05868110587651873</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.04005479098984</v>
+        <v>10.42671841371263</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08787801805377257</v>
+        <v>0.08800682911253775</v>
       </c>
       <c r="C20">
-        <v>29987.52780568812</v>
+        <v>29598.21787528209</v>
       </c>
       <c r="D20">
-        <v>30649.51544222243</v>
+        <v>30581.81593606831</v>
       </c>
       <c r="E20">
-        <v>-14411.25478865629</v>
+        <v>-14089.64436440438</v>
       </c>
       <c r="F20">
-        <v>5788.987636534306</v>
+        <v>6110.598060786213</v>
       </c>
       <c r="G20">
         <v>5127</v>
@@ -2927,28 +2927,28 @@
         <v>3542</v>
       </c>
       <c r="M20">
-        <v>339.7041964173275</v>
+        <v>358.5766517738458</v>
       </c>
       <c r="N20">
-        <v>3202.295803582672</v>
+        <v>3183.423348226154</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>3202.295803582672</v>
+        <v>3183.423348226154</v>
       </c>
       <c r="Q20">
-        <v>4365.295803582672</v>
+        <v>4346.423348226154</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09428709633658439</v>
+        <v>0.09488570246419653</v>
       </c>
       <c r="T20">
-        <v>0.8880581973694351</v>
+        <v>0.8990218788184404</v>
       </c>
       <c r="U20">
         <v>0.05868110587651873</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.42671841371263</v>
+        <v>9.877943760359329</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08800682911253775</v>
+        <v>0.08813564017130296</v>
       </c>
       <c r="C21">
-        <v>29598.21787528209</v>
+        <v>29209.2063588528</v>
       </c>
       <c r="D21">
-        <v>30581.81593606831</v>
+        <v>30514.41484389091</v>
       </c>
       <c r="E21">
-        <v>-14089.64436440438</v>
+        <v>-13768.03394015248</v>
       </c>
       <c r="F21">
-        <v>6110.598060786213</v>
+        <v>6432.208485038119</v>
       </c>
       <c r="G21">
         <v>5127</v>
@@ -3009,28 +3009,28 @@
         <v>3542</v>
       </c>
       <c r="M21">
-        <v>358.5766517738458</v>
+        <v>377.449107130364</v>
       </c>
       <c r="N21">
-        <v>3183.423348226154</v>
+        <v>3164.550892869636</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3183.423348226154</v>
+        <v>3164.550892869636</v>
       </c>
       <c r="Q21">
-        <v>4346.423348226154</v>
+        <v>4327.550892869636</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09488570246419653</v>
+        <v>0.095499273744999</v>
       </c>
       <c r="T21">
-        <v>0.8990218788184404</v>
+        <v>0.910259652303671</v>
       </c>
       <c r="U21">
         <v>0.05868110587651873</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.877943760359329</v>
+        <v>9.384046572341362</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08813564017130296</v>
+        <v>0.08826445123006812</v>
       </c>
       <c r="C22">
-        <v>29209.2063588528</v>
+        <v>28820.49128766207</v>
       </c>
       <c r="D22">
-        <v>30514.41484389091</v>
+        <v>30447.3101969521</v>
       </c>
       <c r="E22">
-        <v>-13768.03394015248</v>
+        <v>-13446.42351590057</v>
       </c>
       <c r="F22">
-        <v>6432.208485038119</v>
+        <v>6753.818909290026</v>
       </c>
       <c r="G22">
         <v>5127</v>
@@ -3091,28 +3091,28 @@
         <v>3542</v>
       </c>
       <c r="M22">
-        <v>377.449107130364</v>
+        <v>396.3215624868823</v>
       </c>
       <c r="N22">
-        <v>3164.550892869636</v>
+        <v>3145.678437513118</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>3164.550892869636</v>
+        <v>3145.678437513118</v>
       </c>
       <c r="Q22">
-        <v>4327.550892869636</v>
+        <v>4308.678437513117</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.095499273744999</v>
+        <v>0.09612837847594835</v>
       </c>
       <c r="T22">
-        <v>0.910259652303671</v>
+        <v>0.9217819263834643</v>
       </c>
       <c r="U22">
         <v>0.05868110587651873</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.384046572341362</v>
+        <v>8.937187211753677</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08826445123006812</v>
+        <v>0.08872326228883332</v>
       </c>
       <c r="C23">
-        <v>28820.49128766207</v>
+        <v>28262.24060391155</v>
       </c>
       <c r="D23">
-        <v>30447.3101969521</v>
+        <v>30210.66993745348</v>
       </c>
       <c r="E23">
-        <v>-13446.42351590057</v>
+        <v>-13124.81309164866</v>
       </c>
       <c r="F23">
-        <v>6753.818909290025</v>
+        <v>7075.429333541931</v>
       </c>
       <c r="G23">
         <v>5127</v>
@@ -3173,45 +3173,45 @@
         <v>3542</v>
       </c>
       <c r="M23">
-        <v>396.3215624868822</v>
+        <v>425.8071618437132</v>
       </c>
       <c r="N23">
-        <v>3145.678437513118</v>
+        <v>3116.192838156287</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>3145.678437513118</v>
+        <v>3116.192838156287</v>
       </c>
       <c r="Q23">
-        <v>4308.678437513117</v>
+        <v>4279.192838156287</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09612837847594835</v>
+        <v>0.09677361409743486</v>
       </c>
       <c r="T23">
-        <v>0.9217819263834643</v>
+        <v>0.9335996433883804</v>
       </c>
       <c r="U23">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>8.937187211753677</v>
+        <v>8.318319458656834</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08872326228883332</v>
+        <v>0.0888670733475985</v>
       </c>
       <c r="C24">
-        <v>28262.24060391155</v>
+        <v>27867.21231345746</v>
       </c>
       <c r="D24">
-        <v>30210.66993745348</v>
+        <v>30137.2520712513</v>
       </c>
       <c r="E24">
-        <v>-13124.81309164866</v>
+        <v>-12803.20266739676</v>
       </c>
       <c r="F24">
-        <v>7075.429333541931</v>
+        <v>7397.039757793837</v>
       </c>
       <c r="G24">
         <v>5127</v>
@@ -3255,28 +3255,28 @@
         <v>3542</v>
       </c>
       <c r="M24">
-        <v>425.8071618437132</v>
+        <v>445.1620328366093</v>
       </c>
       <c r="N24">
-        <v>3116.192838156287</v>
+        <v>3096.837967163391</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>3116.192838156287</v>
+        <v>3096.837967163391</v>
       </c>
       <c r="Q24">
-        <v>4279.192838156287</v>
+        <v>4259.83796716339</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09677361409743486</v>
+        <v>0.09743560908571323</v>
       </c>
       <c r="T24">
-        <v>0.9335996433883804</v>
+        <v>0.9457243140817361</v>
       </c>
       <c r="U24">
         <v>0.06018110587651872</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.318319458656834</v>
+        <v>7.956653395236972</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0888670733475985</v>
+        <v>0.08901088440636369</v>
       </c>
       <c r="C25">
-        <v>27867.21231345746</v>
+        <v>27472.53999760711</v>
       </c>
       <c r="D25">
-        <v>30137.2520712513</v>
+        <v>30064.19017965286</v>
       </c>
       <c r="E25">
-        <v>-12803.20266739676</v>
+        <v>-12481.59224314485</v>
       </c>
       <c r="F25">
-        <v>7397.039757793837</v>
+        <v>7718.650182045743</v>
       </c>
       <c r="G25">
         <v>5127</v>
@@ -3337,28 +3337,28 @@
         <v>3542</v>
       </c>
       <c r="M25">
-        <v>445.1620328366093</v>
+        <v>464.5169038295054</v>
       </c>
       <c r="N25">
-        <v>3096.837967163391</v>
+        <v>3077.483096170495</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>3096.837967163391</v>
+        <v>3077.483096170495</v>
       </c>
       <c r="Q25">
-        <v>4259.83796716339</v>
+        <v>4240.483096170495</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09743560908571323</v>
+        <v>0.09811502499473579</v>
       </c>
       <c r="T25">
-        <v>0.9457243140817361</v>
+        <v>0.9581680550564958</v>
       </c>
       <c r="U25">
         <v>0.06018110587651872</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.956653395236972</v>
+        <v>7.625126170435432</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08901088440636369</v>
+        <v>0.08915469546512887</v>
       </c>
       <c r="C26">
-        <v>27472.53999760711</v>
+        <v>27078.22107364872</v>
       </c>
       <c r="D26">
-        <v>30064.19017965286</v>
+        <v>29991.48167994637</v>
       </c>
       <c r="E26">
-        <v>-12481.59224314485</v>
+        <v>-12159.98181889295</v>
       </c>
       <c r="F26">
-        <v>7718.650182045742</v>
+        <v>8040.260606297648</v>
       </c>
       <c r="G26">
         <v>5127</v>
@@ -3419,28 +3419,28 @@
         <v>3542</v>
       </c>
       <c r="M26">
-        <v>464.5169038295053</v>
+        <v>483.8717748224014</v>
       </c>
       <c r="N26">
-        <v>3077.483096170495</v>
+        <v>3058.128225177599</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>3077.483096170495</v>
+        <v>3058.128225177599</v>
       </c>
       <c r="Q26">
-        <v>4240.483096170495</v>
+        <v>4221.128225177599</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09811502499473579</v>
+        <v>0.09881255866133226</v>
       </c>
       <c r="T26">
-        <v>0.9581680550564958</v>
+        <v>0.9709436291239157</v>
       </c>
       <c r="U26">
         <v>0.06018110587651872</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.625126170435433</v>
+        <v>7.320121123618016</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08915469546512887</v>
+        <v>0.08929850652389407</v>
       </c>
       <c r="C27">
-        <v>27078.22107364872</v>
+        <v>26684.25298379478</v>
       </c>
       <c r="D27">
-        <v>29991.48167994637</v>
+        <v>29919.12401434434</v>
       </c>
       <c r="E27">
-        <v>-12159.98181889295</v>
+        <v>-11838.37139464104</v>
       </c>
       <c r="F27">
-        <v>8040.260606297648</v>
+        <v>8361.871030549555</v>
       </c>
       <c r="G27">
         <v>5127</v>
@@ -3501,28 +3501,28 @@
         <v>3542</v>
       </c>
       <c r="M27">
-        <v>483.8717748224014</v>
+        <v>503.2266458152975</v>
       </c>
       <c r="N27">
-        <v>3058.128225177599</v>
+        <v>3038.773354184702</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>3058.128225177599</v>
+        <v>3038.773354184702</v>
       </c>
       <c r="Q27">
-        <v>4221.128225177599</v>
+        <v>4201.773354184703</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09881255866133226</v>
+        <v>0.0995289445891881</v>
       </c>
       <c r="T27">
-        <v>0.9709436291239157</v>
+        <v>0.9840644889769417</v>
       </c>
       <c r="U27">
         <v>0.06018110587651872</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.320121123618016</v>
+        <v>7.038578003478859</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08929850652389407</v>
+        <v>0.08944231758265925</v>
       </c>
       <c r="C28">
-        <v>26684.25298379478</v>
+        <v>26290.63319488212</v>
       </c>
       <c r="D28">
-        <v>29919.12401434434</v>
+        <v>29847.11464968359</v>
       </c>
       <c r="E28">
-        <v>-11838.37139464104</v>
+        <v>-11516.76097038913</v>
       </c>
       <c r="F28">
-        <v>8361.871030549555</v>
+        <v>8683.48145480146</v>
       </c>
       <c r="G28">
         <v>5127</v>
@@ -3583,28 +3583,28 @@
         <v>3542</v>
       </c>
       <c r="M28">
-        <v>503.2266458152975</v>
+        <v>522.5815168081936</v>
       </c>
       <c r="N28">
-        <v>3038.773354184702</v>
+        <v>3019.418483191806</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>3038.773354184702</v>
+        <v>3019.418483191806</v>
       </c>
       <c r="Q28">
-        <v>4201.773354184703</v>
+        <v>4182.418483191806</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0995289445891881</v>
+        <v>0.100264957528766</v>
       </c>
       <c r="T28">
-        <v>0.9840644889769417</v>
+        <v>0.9975448244423792</v>
       </c>
       <c r="U28">
         <v>0.06018110587651872</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.038578003478859</v>
+        <v>6.777889929275939</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08944231758265925</v>
+        <v>0.09006212864142443</v>
       </c>
       <c r="C29">
-        <v>26290.63319488212</v>
+        <v>25662.59527231056</v>
       </c>
       <c r="D29">
-        <v>29847.11464968359</v>
+        <v>29540.68715136393</v>
       </c>
       <c r="E29">
-        <v>-11516.76097038913</v>
+        <v>-11195.15054613723</v>
       </c>
       <c r="F29">
-        <v>8683.48145480146</v>
+        <v>9005.091879053367</v>
       </c>
       <c r="G29">
         <v>5127</v>
@@ -3665,45 +3665,45 @@
         <v>3542</v>
       </c>
       <c r="M29">
-        <v>522.5815168081936</v>
+        <v>557.2450439954804</v>
       </c>
       <c r="N29">
-        <v>3019.418483191806</v>
+        <v>2984.754956004519</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>3019.418483191806</v>
+        <v>2984.754956004519</v>
       </c>
       <c r="Q29">
-        <v>4182.418483191806</v>
+        <v>4147.754956004519</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.100264957528766</v>
+        <v>0.1010214152722211</v>
       </c>
       <c r="T29">
-        <v>0.9975448244423792</v>
+        <v>1.011399613670745</v>
       </c>
       <c r="U29">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.777889929275939</v>
+        <v>6.356270079323895</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09006212864142443</v>
+        <v>0.09022293970018963</v>
       </c>
       <c r="C30">
-        <v>25662.59527231056</v>
+        <v>25262.506964478</v>
       </c>
       <c r="D30">
-        <v>29540.68715136393</v>
+        <v>29462.20926778328</v>
       </c>
       <c r="E30">
-        <v>-11195.15054613723</v>
+        <v>-10873.54012188532</v>
       </c>
       <c r="F30">
-        <v>9005.091879053367</v>
+        <v>9326.702303305274</v>
       </c>
       <c r="G30">
         <v>5127</v>
@@ -3747,28 +3747,28 @@
         <v>3542</v>
       </c>
       <c r="M30">
-        <v>557.2450439954804</v>
+        <v>577.1466527096047</v>
       </c>
       <c r="N30">
-        <v>2984.754956004519</v>
+        <v>2964.853347290396</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2984.754956004519</v>
+        <v>2964.853347290396</v>
       </c>
       <c r="Q30">
-        <v>4147.754956004519</v>
+        <v>4127.853347290396</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1010214152722211</v>
+        <v>0.1017991816845059</v>
       </c>
       <c r="T30">
-        <v>1.011399613670745</v>
+        <v>1.025644678652024</v>
       </c>
       <c r="U30">
         <v>0.06188110587651872</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.356270079323895</v>
+        <v>6.137088352450658</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09022293970018963</v>
+        <v>0.0903837507589548</v>
       </c>
       <c r="C31">
-        <v>25262.50696447801</v>
+        <v>24862.83452104974</v>
       </c>
       <c r="D31">
-        <v>29462.20926778328</v>
+        <v>29384.14724860692</v>
       </c>
       <c r="E31">
-        <v>-10873.54012188532</v>
+        <v>-10551.92969763342</v>
       </c>
       <c r="F31">
-        <v>9326.702303305272</v>
+        <v>9648.312727557177</v>
       </c>
       <c r="G31">
         <v>5127</v>
@@ -3829,28 +3829,28 @@
         <v>3542</v>
       </c>
       <c r="M31">
-        <v>577.1466527096046</v>
+        <v>597.0482614237288</v>
       </c>
       <c r="N31">
-        <v>2964.853347290396</v>
+        <v>2944.951738576271</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2964.853347290396</v>
+        <v>2944.951738576271</v>
       </c>
       <c r="Q31">
-        <v>4127.853347290396</v>
+        <v>4107.951738576271</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1017991816845059</v>
+        <v>0.1025991699942846</v>
       </c>
       <c r="T31">
-        <v>1.025644678652024</v>
+        <v>1.04029674548991</v>
       </c>
       <c r="U31">
         <v>0.06188110587651872</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.137088352450659</v>
+        <v>5.932518740702304</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0903837507589548</v>
+        <v>0.09054456181772</v>
       </c>
       <c r="C32">
-        <v>24862.83452104974</v>
+        <v>24463.57464518245</v>
       </c>
       <c r="D32">
-        <v>29384.14724860692</v>
+        <v>29306.49779699153</v>
       </c>
       <c r="E32">
-        <v>-10551.92969763342</v>
+        <v>-10230.31927338151</v>
       </c>
       <c r="F32">
-        <v>9648.312727557177</v>
+        <v>9969.923151809084</v>
       </c>
       <c r="G32">
         <v>5127</v>
@@ -3911,28 +3911,28 @@
         <v>3542</v>
       </c>
       <c r="M32">
-        <v>597.0482614237288</v>
+        <v>616.9498701378532</v>
       </c>
       <c r="N32">
-        <v>2944.951738576271</v>
+        <v>2925.050129862147</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>2944.951738576271</v>
+        <v>2925.050129862147</v>
       </c>
       <c r="Q32">
-        <v>4107.951738576271</v>
+        <v>4088.050129862147</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1025991699942846</v>
+        <v>0.1034223463710133</v>
       </c>
       <c r="T32">
-        <v>1.04029674548991</v>
+        <v>1.0553735099173</v>
       </c>
       <c r="U32">
         <v>0.06188110587651872</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.932518740702304</v>
+        <v>5.741147168421584</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09054456181772</v>
+        <v>0.09096137287648519</v>
       </c>
       <c r="C33">
-        <v>24463.57464518245</v>
+        <v>23942.59961608493</v>
       </c>
       <c r="D33">
-        <v>29306.49779699153</v>
+        <v>29107.13319214592</v>
       </c>
       <c r="E33">
-        <v>-10230.31927338151</v>
+        <v>-9908.708849129604</v>
       </c>
       <c r="F33">
-        <v>9969.923151809084</v>
+        <v>10291.53357606099</v>
       </c>
       <c r="G33">
         <v>5127</v>
@@ -3993,45 +3993,45 @@
         <v>3542</v>
       </c>
       <c r="M33">
-        <v>616.9498701378532</v>
+        <v>645.0847057128265</v>
       </c>
       <c r="N33">
-        <v>2925.050129862147</v>
+        <v>2896.915294287173</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2925.050129862147</v>
+        <v>2896.915294287173</v>
       </c>
       <c r="Q33">
-        <v>4088.050129862147</v>
+        <v>4059.915294287173</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1034223463710133</v>
+        <v>0.1042697338176459</v>
       </c>
       <c r="T33">
-        <v>1.0553735099173</v>
+        <v>1.070893708592554</v>
       </c>
       <c r="U33">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>5.741147168421584</v>
+        <v>5.490751785978318</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09096137287648519</v>
+        <v>0.09113018393525037</v>
       </c>
       <c r="C34">
-        <v>23942.59961608493</v>
+        <v>23541.01491433906</v>
       </c>
       <c r="D34">
-        <v>29107.13319214592</v>
+        <v>29027.15891465195</v>
       </c>
       <c r="E34">
-        <v>-9908.708849129604</v>
+        <v>-9587.098424877699</v>
       </c>
       <c r="F34">
-        <v>10291.53357606099</v>
+        <v>10613.1440003129</v>
       </c>
       <c r="G34">
         <v>5127</v>
@@ -4075,28 +4075,28 @@
         <v>3542</v>
       </c>
       <c r="M34">
-        <v>645.0847057128265</v>
+        <v>665.2436027663522</v>
       </c>
       <c r="N34">
-        <v>2896.915294287173</v>
+        <v>2876.756397233648</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2896.915294287173</v>
+        <v>2876.756397233648</v>
       </c>
       <c r="Q34">
-        <v>4059.915294287173</v>
+        <v>4039.756397233648</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1042697338176459</v>
+        <v>0.1051424164119391</v>
       </c>
       <c r="T34">
-        <v>1.070893708592554</v>
+        <v>1.086877196780503</v>
       </c>
       <c r="U34">
         <v>0.06268110587651873</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.490751785978318</v>
+        <v>5.324365368221401</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09113018393525037</v>
+        <v>0.09129899499401556</v>
       </c>
       <c r="C35">
-        <v>23541.01491433906</v>
+        <v>23139.86848041861</v>
       </c>
       <c r="D35">
-        <v>29027.15891465195</v>
+        <v>28947.62290498341</v>
       </c>
       <c r="E35">
-        <v>-9587.098424877699</v>
+        <v>-9265.488000625792</v>
       </c>
       <c r="F35">
-        <v>10613.1440003129</v>
+        <v>10934.7544245648</v>
       </c>
       <c r="G35">
         <v>5127</v>
@@ -4157,28 +4157,28 @@
         <v>3542</v>
       </c>
       <c r="M35">
-        <v>665.2436027663522</v>
+        <v>685.402499819878</v>
       </c>
       <c r="N35">
-        <v>2876.756397233648</v>
+        <v>2856.597500180122</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2876.756397233648</v>
+        <v>2856.597500180122</v>
       </c>
       <c r="Q35">
-        <v>4039.756397233648</v>
+        <v>4019.597500180122</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1051424164119391</v>
+        <v>0.1060415439333321</v>
       </c>
       <c r="T35">
-        <v>1.086877196780503</v>
+        <v>1.103345033095359</v>
       </c>
       <c r="U35">
         <v>0.06268110587651873</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.324365368221401</v>
+        <v>5.167766386803124</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09129899499401556</v>
+        <v>0.09146780605278074</v>
       </c>
       <c r="C36">
-        <v>23139.86848041861</v>
+        <v>22739.15672153429</v>
       </c>
       <c r="D36">
-        <v>28947.62290498341</v>
+        <v>28868.52157035101</v>
       </c>
       <c r="E36">
-        <v>-9265.488000625792</v>
+        <v>-8943.877576373885</v>
       </c>
       <c r="F36">
-        <v>10934.7544245648</v>
+        <v>11256.36484881671</v>
       </c>
       <c r="G36">
         <v>5127</v>
@@ -4239,28 +4239,28 @@
         <v>3542</v>
       </c>
       <c r="M36">
-        <v>685.402499819878</v>
+        <v>705.561396873404</v>
       </c>
       <c r="N36">
-        <v>2856.597500180122</v>
+        <v>2836.438603126596</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2856.597500180122</v>
+        <v>2836.438603126596</v>
       </c>
       <c r="Q36">
-        <v>4019.597500180122</v>
+        <v>3999.438603126596</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1060415439333321</v>
+        <v>0.1069683369169218</v>
       </c>
       <c r="T36">
-        <v>1.103345033095359</v>
+        <v>1.120319572066057</v>
       </c>
       <c r="U36">
         <v>0.06268110587651873</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.167766386803124</v>
+        <v>5.020115918608748</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09146780605278074</v>
+        <v>0.09163661711154593</v>
       </c>
       <c r="C37">
-        <v>22739.15672153429</v>
+        <v>22338.87608405997</v>
       </c>
       <c r="D37">
-        <v>28868.52157035101</v>
+        <v>28789.85135712858</v>
       </c>
       <c r="E37">
-        <v>-8943.877576373885</v>
+        <v>-8622.26715212198</v>
       </c>
       <c r="F37">
-        <v>11256.36484881671</v>
+        <v>11577.97527306861</v>
       </c>
       <c r="G37">
         <v>5127</v>
@@ -4321,28 +4321,28 @@
         <v>3542</v>
       </c>
       <c r="M37">
-        <v>705.561396873404</v>
+        <v>725.7202939269297</v>
       </c>
       <c r="N37">
-        <v>2836.438603126596</v>
+        <v>2816.27970607307</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2836.438603126596</v>
+        <v>2816.27970607307</v>
       </c>
       <c r="Q37">
-        <v>3999.438603126596</v>
+        <v>3979.27970607307</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1069683369169218</v>
+        <v>0.1079240921812487</v>
       </c>
       <c r="T37">
-        <v>1.120319572066057</v>
+        <v>1.137824565379589</v>
       </c>
       <c r="U37">
         <v>0.06268110587651873</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.020115918608748</v>
+        <v>4.88066825420295</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09163661711154594</v>
+        <v>0.09180542817031115</v>
       </c>
       <c r="C38">
-        <v>22338.87608405996</v>
+        <v>21939.02305300042</v>
       </c>
       <c r="D38">
-        <v>28789.85135712858</v>
+        <v>28711.60875032093</v>
       </c>
       <c r="E38">
-        <v>-8622.267152121982</v>
+        <v>-8300.656727870075</v>
       </c>
       <c r="F38">
-        <v>11577.97527306861</v>
+        <v>11899.58569732052</v>
       </c>
       <c r="G38">
         <v>5127</v>
@@ -4403,28 +4403,28 @@
         <v>3542</v>
       </c>
       <c r="M38">
-        <v>725.7202939269296</v>
+        <v>745.8791909804554</v>
       </c>
       <c r="N38">
-        <v>2816.27970607307</v>
+        <v>2796.120809019545</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2816.27970607307</v>
+        <v>2796.120809019545</v>
       </c>
       <c r="Q38">
-        <v>3979.27970607307</v>
+        <v>3959.120809019545</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1079240921812487</v>
+        <v>0.1089101888825384</v>
       </c>
       <c r="T38">
-        <v>1.137824565379589</v>
+        <v>1.155885272766566</v>
       </c>
       <c r="U38">
         <v>0.06268110587651873</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.880668254202951</v>
+        <v>4.748758301386655</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09180542817031115</v>
+        <v>0.09197423922907633</v>
       </c>
       <c r="C39">
-        <v>21939.02305300042</v>
+        <v>21539.59415146795</v>
       </c>
       <c r="D39">
-        <v>28711.60875032093</v>
+        <v>28633.79027304037</v>
       </c>
       <c r="E39">
-        <v>-8300.656727870075</v>
+        <v>-7979.046303618168</v>
       </c>
       <c r="F39">
-        <v>11899.58569732052</v>
+        <v>12221.19612157243</v>
       </c>
       <c r="G39">
         <v>5127</v>
@@ -4485,28 +4485,28 @@
         <v>3542</v>
       </c>
       <c r="M39">
-        <v>745.8791909804554</v>
+        <v>766.0380880339814</v>
       </c>
       <c r="N39">
-        <v>2796.120809019545</v>
+        <v>2775.961911966019</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2796.120809019545</v>
+        <v>2775.961911966019</v>
       </c>
       <c r="Q39">
-        <v>3959.120809019545</v>
+        <v>3938.961911966019</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1089101888825384</v>
+        <v>0.1099280951548374</v>
       </c>
       <c r="T39">
-        <v>1.155885272766566</v>
+        <v>1.17452858361764</v>
       </c>
       <c r="U39">
         <v>0.06268110587651873</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.748758301386655</v>
+        <v>4.623790977665953</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09197423922907633</v>
+        <v>0.0921430502878415</v>
       </c>
       <c r="C40">
-        <v>21539.59415146795</v>
+        <v>21140.58594016722</v>
       </c>
       <c r="D40">
-        <v>28633.79027304037</v>
+        <v>28556.39248599156</v>
       </c>
       <c r="E40">
-        <v>-7979.046303618168</v>
+        <v>-7657.435879366261</v>
       </c>
       <c r="F40">
-        <v>12221.19612157243</v>
+        <v>12542.80654582433</v>
       </c>
       <c r="G40">
         <v>5127</v>
@@ -4567,28 +4567,28 @@
         <v>3542</v>
       </c>
       <c r="M40">
-        <v>766.0380880339814</v>
+        <v>786.1969850875072</v>
       </c>
       <c r="N40">
-        <v>2775.961911966019</v>
+        <v>2755.803014912493</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>2775.961911966019</v>
+        <v>2755.803014912493</v>
       </c>
       <c r="Q40">
-        <v>3938.961911966019</v>
+        <v>3918.803014912493</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1099280951548374</v>
+        <v>0.1109793754032774</v>
       </c>
       <c r="T40">
-        <v>1.17452858361764</v>
+        <v>1.193783150562191</v>
       </c>
       <c r="U40">
         <v>0.06268110587651873</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.623790977665953</v>
+        <v>4.505232234648878</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0921430502878415</v>
+        <v>0.09231186134660668</v>
       </c>
       <c r="C41">
-        <v>21140.58594016722</v>
+        <v>20741.9950168887</v>
       </c>
       <c r="D41">
-        <v>28556.39248599156</v>
+        <v>28479.41198696494</v>
       </c>
       <c r="E41">
-        <v>-7657.435879366261</v>
+        <v>-7335.825455114356</v>
       </c>
       <c r="F41">
-        <v>12542.80654582433</v>
+        <v>12864.41697007624</v>
       </c>
       <c r="G41">
         <v>5127</v>
@@ -4649,28 +4649,28 @@
         <v>3542</v>
       </c>
       <c r="M41">
-        <v>786.1969850875072</v>
+        <v>806.355882141033</v>
       </c>
       <c r="N41">
-        <v>2755.803014912493</v>
+        <v>2735.644117858967</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>2755.803014912493</v>
+        <v>2735.644117858967</v>
       </c>
       <c r="Q41">
-        <v>3918.803014912493</v>
+        <v>3898.644117858967</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1109793754032774</v>
+        <v>0.1120656983266653</v>
       </c>
       <c r="T41">
-        <v>1.193783150562191</v>
+        <v>1.213679536404895</v>
       </c>
       <c r="U41">
         <v>0.06268110587651873</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.505232234648878</v>
+        <v>4.392601428782656</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09231186134660668</v>
+        <v>0.09248067240537186</v>
       </c>
       <c r="C42">
-        <v>20741.9950168887</v>
+        <v>20343.81801600998</v>
       </c>
       <c r="D42">
-        <v>28479.41198696494</v>
+        <v>28402.84541033812</v>
       </c>
       <c r="E42">
-        <v>-7335.825455114356</v>
+        <v>-7014.21503086245</v>
       </c>
       <c r="F42">
-        <v>12864.41697007624</v>
+        <v>13186.02739432814</v>
       </c>
       <c r="G42">
         <v>5127</v>
@@ -4731,28 +4731,28 @@
         <v>3542</v>
       </c>
       <c r="M42">
-        <v>806.355882141033</v>
+        <v>826.5147791945589</v>
       </c>
       <c r="N42">
-        <v>2735.644117858967</v>
+        <v>2715.485220805441</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>2735.644117858967</v>
+        <v>2715.485220805441</v>
       </c>
       <c r="Q42">
-        <v>3898.644117858967</v>
+        <v>3878.485220805441</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1120656983266653</v>
+        <v>0.1131888457559308</v>
       </c>
       <c r="T42">
-        <v>1.213679536404895</v>
+        <v>1.234250376004978</v>
       </c>
       <c r="U42">
         <v>0.06268110587651873</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.392601428782656</v>
+        <v>4.285464808568444</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09248067240537186</v>
+        <v>0.09306948346413707</v>
       </c>
       <c r="C43">
-        <v>20343.81801600998</v>
+        <v>19758.33666547222</v>
       </c>
       <c r="D43">
-        <v>28402.84541033812</v>
+        <v>28138.97448405227</v>
       </c>
       <c r="E43">
-        <v>-7014.21503086245</v>
+        <v>-6692.604606610543</v>
       </c>
       <c r="F43">
-        <v>13186.02739432814</v>
+        <v>13507.63781858005</v>
       </c>
       <c r="G43">
         <v>5127</v>
@@ -4813,45 +4813,45 @@
         <v>3542</v>
       </c>
       <c r="M43">
-        <v>826.5147791945589</v>
+        <v>860.1813140666648</v>
       </c>
       <c r="N43">
-        <v>2715.485220805441</v>
+        <v>2681.818685933335</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>2715.485220805441</v>
+        <v>2681.818685933335</v>
       </c>
       <c r="Q43">
-        <v>3878.485220805441</v>
+        <v>3844.818685933335</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1131888457559308</v>
+        <v>0.1143507224068952</v>
       </c>
       <c r="T43">
-        <v>1.234250376004978</v>
+        <v>1.255530554901615</v>
       </c>
       <c r="U43">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.285464808568444</v>
+        <v>4.117736507498106</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09306948346413707</v>
+        <v>0.09324829452290226</v>
       </c>
       <c r="C44">
-        <v>19758.33666547222</v>
+        <v>19357.56131210316</v>
       </c>
       <c r="D44">
-        <v>28138.97448405227</v>
+        <v>28059.80955493511</v>
       </c>
       <c r="E44">
-        <v>-6692.604606610545</v>
+        <v>-6370.99418235864</v>
       </c>
       <c r="F44">
-        <v>13507.63781858005</v>
+        <v>13829.24824283195</v>
       </c>
       <c r="G44">
         <v>5127</v>
@@ -4895,28 +4895,28 @@
         <v>3542</v>
       </c>
       <c r="M44">
-        <v>860.1813140666646</v>
+        <v>880.6618215444423</v>
       </c>
       <c r="N44">
-        <v>2681.818685933335</v>
+        <v>2661.338178455558</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>2681.818685933335</v>
+        <v>2661.338178455558</v>
       </c>
       <c r="Q44">
-        <v>3844.818685933335</v>
+        <v>3824.338178455558</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1143507224068952</v>
+        <v>0.1155533666596477</v>
       </c>
       <c r="T44">
-        <v>1.255530554901615</v>
+        <v>1.277557406741994</v>
       </c>
       <c r="U44">
         <v>0.06368110587651873</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.117736507498107</v>
+        <v>4.021975193370244</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09324829452290226</v>
+        <v>0.09342710558166745</v>
       </c>
       <c r="C45">
-        <v>19357.56131210316</v>
+        <v>18957.23014719814</v>
       </c>
       <c r="D45">
-        <v>28059.80955493511</v>
+        <v>27981.08881428201</v>
       </c>
       <c r="E45">
-        <v>-6370.99418235864</v>
+        <v>-6049.383758106733</v>
       </c>
       <c r="F45">
-        <v>13829.24824283195</v>
+        <v>14150.85866708386</v>
       </c>
       <c r="G45">
         <v>5127</v>
@@ -4977,28 +4977,28 @@
         <v>3542</v>
       </c>
       <c r="M45">
-        <v>880.6618215444423</v>
+        <v>901.1423290222201</v>
       </c>
       <c r="N45">
-        <v>2661.338178455558</v>
+        <v>2640.85767097778</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>2661.338178455558</v>
+        <v>2640.85767097778</v>
       </c>
       <c r="Q45">
-        <v>3824.338178455558</v>
+        <v>3803.85767097778</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1155533666596477</v>
+        <v>0.1167989624928557</v>
       </c>
       <c r="T45">
-        <v>1.277557406741994</v>
+        <v>1.300370931862387</v>
       </c>
       <c r="U45">
         <v>0.06368110587651873</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.021975193370244</v>
+        <v>3.930566666248193</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09342710558166745</v>
+        <v>0.09360591664043262</v>
       </c>
       <c r="C46">
-        <v>18957.23014719814</v>
+        <v>18557.33944275385</v>
       </c>
       <c r="D46">
-        <v>27981.08881428201</v>
+        <v>27902.80853408963</v>
       </c>
       <c r="E46">
-        <v>-6049.383758106733</v>
+        <v>-5727.773333854826</v>
       </c>
       <c r="F46">
-        <v>14150.85866708386</v>
+        <v>14472.46909133577</v>
       </c>
       <c r="G46">
         <v>5127</v>
@@ -5059,28 +5059,28 @@
         <v>3542</v>
       </c>
       <c r="M46">
-        <v>901.1423290222201</v>
+        <v>921.6228364999979</v>
       </c>
       <c r="N46">
-        <v>2640.85767097778</v>
+        <v>2620.377163500002</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>2640.85767097778</v>
+        <v>2620.377163500002</v>
       </c>
       <c r="Q46">
-        <v>3803.85767097778</v>
+        <v>3783.377163500002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1167989624928557</v>
+        <v>0.1180898527199985</v>
       </c>
       <c r="T46">
-        <v>1.300370931862387</v>
+        <v>1.32401403971443</v>
       </c>
       <c r="U46">
         <v>0.06368110587651873</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.930566666248193</v>
+        <v>3.843220740331566</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09360591664043262</v>
+        <v>0.09378472769919782</v>
       </c>
       <c r="C47">
-        <v>18557.33944275385</v>
+        <v>18157.88551236862</v>
       </c>
       <c r="D47">
-        <v>27902.80853408963</v>
+        <v>27824.9650279563</v>
       </c>
       <c r="E47">
-        <v>-5727.773333854826</v>
+        <v>-5406.162909602921</v>
       </c>
       <c r="F47">
-        <v>14472.46909133577</v>
+        <v>14794.07951558767</v>
       </c>
       <c r="G47">
         <v>5127</v>
@@ -5141,28 +5141,28 @@
         <v>3542</v>
       </c>
       <c r="M47">
-        <v>921.6228364999979</v>
+        <v>942.1033439777756</v>
       </c>
       <c r="N47">
-        <v>2620.377163500002</v>
+        <v>2599.896656022224</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>2620.377163500002</v>
+        <v>2599.896656022224</v>
       </c>
       <c r="Q47">
-        <v>3783.377163500002</v>
+        <v>3762.896656022224</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1180898527199985</v>
+        <v>0.1194285536962948</v>
       </c>
       <c r="T47">
-        <v>1.32401403971443</v>
+        <v>1.348532818227661</v>
       </c>
       <c r="U47">
         <v>0.06368110587651873</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.843220740331566</v>
+        <v>3.759672463367837</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09378472769919782</v>
+        <v>0.093963538757963</v>
       </c>
       <c r="C48">
-        <v>18157.88551236862</v>
+        <v>17758.86471066376</v>
       </c>
       <c r="D48">
-        <v>27824.9650279563</v>
+        <v>27747.55465050335</v>
       </c>
       <c r="E48">
-        <v>-5406.162909602921</v>
+        <v>-5084.552485351014</v>
       </c>
       <c r="F48">
-        <v>14794.07951558767</v>
+        <v>15115.68993983958</v>
       </c>
       <c r="G48">
         <v>5127</v>
@@ -5223,28 +5223,28 @@
         <v>3542</v>
       </c>
       <c r="M48">
-        <v>942.1033439777756</v>
+        <v>962.5838514555534</v>
       </c>
       <c r="N48">
-        <v>2599.896656022224</v>
+        <v>2579.416148544447</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>2599.896656022224</v>
+        <v>2579.416148544447</v>
       </c>
       <c r="Q48">
-        <v>3762.896656022224</v>
+        <v>3742.416148544447</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1194285536962948</v>
+        <v>0.1208177716905645</v>
       </c>
       <c r="T48">
-        <v>1.348532818227661</v>
+        <v>1.373976833665919</v>
       </c>
       <c r="U48">
         <v>0.06368110587651873</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.759672463367837</v>
+        <v>3.67967943223235</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.093963538757963</v>
+        <v>0.09414234981672819</v>
       </c>
       <c r="C49">
-        <v>17758.86471066376</v>
+        <v>17360.27343271453</v>
       </c>
       <c r="D49">
-        <v>27747.55465050335</v>
+        <v>27670.57379680601</v>
       </c>
       <c r="E49">
-        <v>-5084.552485351014</v>
+        <v>-4762.942061099107</v>
       </c>
       <c r="F49">
-        <v>15115.68993983958</v>
+        <v>15437.30036409149</v>
       </c>
       <c r="G49">
         <v>5127</v>
@@ -5305,28 +5305,28 @@
         <v>3542</v>
       </c>
       <c r="M49">
-        <v>962.5838514555534</v>
+        <v>983.0643589333312</v>
       </c>
       <c r="N49">
-        <v>2579.416148544447</v>
+        <v>2558.935641066669</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2579.416148544447</v>
+        <v>2558.935641066669</v>
       </c>
       <c r="Q49">
-        <v>3742.416148544447</v>
+        <v>3721.935641066669</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1208177716905645</v>
+        <v>0.1222604211461523</v>
       </c>
       <c r="T49">
-        <v>1.373976833665919</v>
+        <v>1.400399465082571</v>
       </c>
       <c r="U49">
         <v>0.06368110587651873</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.67967943223235</v>
+        <v>3.603019444060843</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09414234981672819</v>
+        <v>0.09432116087549337</v>
       </c>
       <c r="C50">
-        <v>17360.27343271453</v>
+        <v>16962.10811349047</v>
       </c>
       <c r="D50">
-        <v>27670.57379680601</v>
+        <v>27594.01890183386</v>
       </c>
       <c r="E50">
-        <v>-4762.942061099109</v>
+        <v>-4441.331636847204</v>
       </c>
       <c r="F50">
-        <v>15437.30036409148</v>
+        <v>15758.91078834339</v>
       </c>
       <c r="G50">
         <v>5127</v>
@@ -5387,28 +5387,28 @@
         <v>3542</v>
       </c>
       <c r="M50">
-        <v>983.0643589333311</v>
+        <v>1003.544866411109</v>
       </c>
       <c r="N50">
-        <v>2558.935641066669</v>
+        <v>2538.455133588891</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>2558.935641066669</v>
+        <v>2538.455133588891</v>
       </c>
       <c r="Q50">
-        <v>3721.935641066669</v>
+        <v>3701.455133588891</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1222604211461523</v>
+        <v>0.1237596450901945</v>
       </c>
       <c r="T50">
-        <v>1.400399465082571</v>
+        <v>1.427858278123405</v>
       </c>
       <c r="U50">
         <v>0.06368110587651873</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.603019444060843</v>
+        <v>3.529488434998377</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09432116087549337</v>
+        <v>0.09449997193425856</v>
       </c>
       <c r="C51">
-        <v>16962.10811349047</v>
+        <v>16564.3652273051</v>
       </c>
       <c r="D51">
-        <v>27594.01890183386</v>
+        <v>27517.88643990039</v>
       </c>
       <c r="E51">
-        <v>-4441.331636847204</v>
+        <v>-4119.721212595297</v>
       </c>
       <c r="F51">
-        <v>15758.91078834339</v>
+        <v>16080.5212125953</v>
       </c>
       <c r="G51">
         <v>5127</v>
@@ -5469,28 +5469,28 @@
         <v>3542</v>
       </c>
       <c r="M51">
-        <v>1003.544866411109</v>
+        <v>1024.025373888886</v>
       </c>
       <c r="N51">
-        <v>2538.455133588891</v>
+        <v>2517.974626111114</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>2538.455133588891</v>
+        <v>2517.974626111114</v>
       </c>
       <c r="Q51">
-        <v>3701.455133588891</v>
+        <v>3680.974626111114</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1237596450901945</v>
+        <v>0.1253188379919984</v>
       </c>
       <c r="T51">
-        <v>1.427858278123405</v>
+        <v>1.456415443685874</v>
       </c>
       <c r="U51">
         <v>0.06368110587651873</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.529488434998377</v>
+        <v>3.45889866629841</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09449997193425856</v>
+        <v>0.09467878299302375</v>
       </c>
       <c r="C52">
-        <v>16564.3652273051</v>
+        <v>16167.04128727466</v>
       </c>
       <c r="D52">
-        <v>27517.88643990039</v>
+        <v>27442.17292412186</v>
       </c>
       <c r="E52">
-        <v>-4119.721212595297</v>
+        <v>-3798.110788343391</v>
       </c>
       <c r="F52">
-        <v>16080.5212125953</v>
+        <v>16402.1316368472</v>
       </c>
       <c r="G52">
         <v>5127</v>
@@ -5551,28 +5551,28 @@
         <v>3542</v>
       </c>
       <c r="M52">
-        <v>1024.025373888886</v>
+        <v>1044.505881366664</v>
       </c>
       <c r="N52">
-        <v>2517.974626111114</v>
+        <v>2497.494118633336</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>2517.974626111114</v>
+        <v>2497.494118633336</v>
       </c>
       <c r="Q52">
-        <v>3680.974626111114</v>
+        <v>3660.494118633336</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1253188379919984</v>
+        <v>0.1269416714204065</v>
       </c>
       <c r="T52">
-        <v>1.456415443685874</v>
+        <v>1.486138207842728</v>
       </c>
       <c r="U52">
         <v>0.06368110587651873</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.45889866629841</v>
+        <v>3.391077123821971</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09467878299302375</v>
+        <v>0.09485759405178892</v>
       </c>
       <c r="C53">
-        <v>16167.04128727466</v>
+        <v>15770.13284478573</v>
       </c>
       <c r="D53">
-        <v>27442.17292412186</v>
+        <v>27366.87490588484</v>
       </c>
       <c r="E53">
-        <v>-3798.110788343391</v>
+        <v>-3476.500364091484</v>
       </c>
       <c r="F53">
-        <v>16402.1316368472</v>
+        <v>16723.74206109911</v>
       </c>
       <c r="G53">
         <v>5127</v>
@@ -5633,28 +5633,28 @@
         <v>3542</v>
       </c>
       <c r="M53">
-        <v>1044.505881366664</v>
+        <v>1064.986388844442</v>
       </c>
       <c r="N53">
-        <v>2497.494118633336</v>
+        <v>2477.013611155558</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>2497.494118633336</v>
+        <v>2477.013611155558</v>
       </c>
       <c r="Q53">
-        <v>3660.494118633336</v>
+        <v>3640.013611155558</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1269416714204065</v>
+        <v>0.1286321229083316</v>
       </c>
       <c r="T53">
-        <v>1.486138207842728</v>
+        <v>1.517099420506118</v>
       </c>
       <c r="U53">
         <v>0.06368110587651873</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.391077123821971</v>
+        <v>3.325864102210009</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09485759405178892</v>
+        <v>0.09503640511055411</v>
       </c>
       <c r="C54">
-        <v>15770.13284478573</v>
+        <v>15373.63648897165</v>
       </c>
       <c r="D54">
-        <v>27366.87490588484</v>
+        <v>27291.98897432267</v>
       </c>
       <c r="E54">
-        <v>-3476.500364091484</v>
+        <v>-3154.889939839577</v>
       </c>
       <c r="F54">
-        <v>16723.74206109911</v>
+        <v>17045.35248535102</v>
       </c>
       <c r="G54">
         <v>5127</v>
@@ -5715,28 +5715,28 @@
         <v>3542</v>
       </c>
       <c r="M54">
-        <v>1064.986388844442</v>
+        <v>1085.46689632222</v>
       </c>
       <c r="N54">
-        <v>2477.013611155558</v>
+        <v>2456.53310367778</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>2477.013611155558</v>
+        <v>2456.53310367778</v>
       </c>
       <c r="Q54">
-        <v>3640.013611155558</v>
+        <v>3619.53310367778</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1286321229083316</v>
+        <v>0.1303945085021259</v>
       </c>
       <c r="T54">
-        <v>1.517099420506118</v>
+        <v>1.549378131580717</v>
       </c>
       <c r="U54">
         <v>0.06368110587651873</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.325864102210009</v>
+        <v>3.263111949338122</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09503640511055411</v>
+        <v>0.09521521616931931</v>
       </c>
       <c r="C55">
-        <v>15373.63648897165</v>
+        <v>14977.54884619746</v>
       </c>
       <c r="D55">
-        <v>27291.98897432267</v>
+        <v>27217.51175580038</v>
       </c>
       <c r="E55">
-        <v>-3154.889939839577</v>
+        <v>-2833.279515587674</v>
       </c>
       <c r="F55">
-        <v>17045.35248535102</v>
+        <v>17366.96290960292</v>
       </c>
       <c r="G55">
         <v>5127</v>
@@ -5797,28 +5797,28 @@
         <v>3542</v>
       </c>
       <c r="M55">
-        <v>1085.46689632222</v>
+        <v>1105.947403799997</v>
       </c>
       <c r="N55">
-        <v>2456.53310367778</v>
+        <v>2436.052596200003</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2456.53310367778</v>
+        <v>2436.052596200003</v>
       </c>
       <c r="Q55">
-        <v>3619.53310367778</v>
+        <v>3599.052596200003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1303945085021259</v>
+        <v>0.13223351955652</v>
       </c>
       <c r="T55">
-        <v>1.549378131580717</v>
+        <v>1.58306026487595</v>
       </c>
       <c r="U55">
         <v>0.06368110587651873</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.263111949338122</v>
+        <v>3.202683950276306</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09521521616931931</v>
+        <v>0.0953940272280845</v>
       </c>
       <c r="C56">
-        <v>14977.54884619746</v>
+        <v>14581.8665795533</v>
       </c>
       <c r="D56">
-        <v>27217.51175580038</v>
+        <v>27143.43991340812</v>
       </c>
       <c r="E56">
-        <v>-2833.279515587674</v>
+        <v>-2511.669091335767</v>
       </c>
       <c r="F56">
-        <v>17366.96290960292</v>
+        <v>17688.57333385483</v>
       </c>
       <c r="G56">
         <v>5127</v>
@@ -5879,28 +5879,28 @@
         <v>3542</v>
       </c>
       <c r="M56">
-        <v>1105.947403799997</v>
+        <v>1126.427911277775</v>
       </c>
       <c r="N56">
-        <v>2436.052596200003</v>
+        <v>2415.572088722225</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>2436.052596200003</v>
+        <v>2415.572088722225</v>
       </c>
       <c r="Q56">
-        <v>3599.052596200003</v>
+        <v>3578.572088722225</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.13223351955652</v>
+        <v>0.1341542644355538</v>
       </c>
       <c r="T56">
-        <v>1.58306026487595</v>
+        <v>1.618239381873193</v>
       </c>
       <c r="U56">
         <v>0.06368110587651873</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.202683950276306</v>
+        <v>3.144453332998554</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0953940272280845</v>
+        <v>0.0955728382868497</v>
       </c>
       <c r="C57">
-        <v>14581.8665795533</v>
+        <v>14186.58638835599</v>
       </c>
       <c r="D57">
-        <v>27143.43991340812</v>
+        <v>27069.77014646272</v>
       </c>
       <c r="E57">
-        <v>-2511.669091335767</v>
+        <v>-2190.05866708386</v>
       </c>
       <c r="F57">
-        <v>17688.57333385483</v>
+        <v>18010.18375810673</v>
       </c>
       <c r="G57">
         <v>5127</v>
@@ -5961,28 +5961,28 @@
         <v>3542</v>
       </c>
       <c r="M57">
-        <v>1126.427911277775</v>
+        <v>1146.908418755553</v>
       </c>
       <c r="N57">
-        <v>2415.572088722225</v>
+        <v>2395.091581244447</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>2415.572088722225</v>
+        <v>2395.091581244447</v>
       </c>
       <c r="Q57">
-        <v>3578.572088722225</v>
+        <v>3558.091581244447</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1341542644355538</v>
+        <v>0.1361623158999982</v>
       </c>
       <c r="T57">
-        <v>1.618239381873193</v>
+        <v>1.655017549643038</v>
       </c>
       <c r="U57">
         <v>0.06368110587651873</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.144453332998554</v>
+        <v>3.08830238062358</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0955728382868497</v>
+        <v>0.09575164934561488</v>
       </c>
       <c r="C58">
-        <v>14186.58638835599</v>
+        <v>13791.70500765881</v>
       </c>
       <c r="D58">
-        <v>27069.77014646272</v>
+        <v>26996.49919001745</v>
       </c>
       <c r="E58">
-        <v>-2190.05866708386</v>
+        <v>-1868.448242831953</v>
       </c>
       <c r="F58">
-        <v>18010.18375810673</v>
+        <v>18331.79418235864</v>
       </c>
       <c r="G58">
         <v>5127</v>
@@ -6043,28 +6043,28 @@
         <v>3542</v>
       </c>
       <c r="M58">
-        <v>1146.908418755553</v>
+        <v>1167.388926233331</v>
       </c>
       <c r="N58">
-        <v>2395.091581244447</v>
+        <v>2374.61107376667</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>2395.091581244447</v>
+        <v>2374.61107376667</v>
       </c>
       <c r="Q58">
-        <v>3558.091581244447</v>
+        <v>3537.61107376667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1361623158999982</v>
+        <v>0.1382637651069749</v>
       </c>
       <c r="T58">
-        <v>1.655017549643038</v>
+        <v>1.693506329867295</v>
       </c>
       <c r="U58">
         <v>0.06368110587651873</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.08830238062358</v>
+        <v>3.034121637103868</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09575164934561488</v>
+        <v>0.09738046040438006</v>
       </c>
       <c r="C59">
-        <v>13791.70500765881</v>
+        <v>12820.48418888983</v>
       </c>
       <c r="D59">
-        <v>26996.49919001745</v>
+        <v>26346.88879550038</v>
       </c>
       <c r="E59">
-        <v>-1868.448242831953</v>
+        <v>-1546.837818580047</v>
       </c>
       <c r="F59">
-        <v>18331.79418235864</v>
+        <v>18653.40460661055</v>
       </c>
       <c r="G59">
         <v>5127</v>
@@ -6125,45 +6125,45 @@
         <v>3542</v>
       </c>
       <c r="M59">
-        <v>1167.388926233331</v>
+        <v>1234.502945227635</v>
       </c>
       <c r="N59">
-        <v>2374.61107376667</v>
+        <v>2307.497054772365</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>2374.61107376667</v>
+        <v>2307.497054772365</v>
       </c>
       <c r="Q59">
-        <v>3537.61107376667</v>
+        <v>3470.497054772365</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1382637651069749</v>
+        <v>0.1404652833238076</v>
       </c>
       <c r="T59">
-        <v>1.693506329867295</v>
+        <v>1.73382790914985</v>
       </c>
       <c r="U59">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.034121637103868</v>
+        <v>2.869170959609884</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09738046040438006</v>
+        <v>0.09758427146314523</v>
       </c>
       <c r="C60">
-        <v>12820.48418888984</v>
+        <v>12419.78291913284</v>
       </c>
       <c r="D60">
-        <v>26346.88879550038</v>
+        <v>26267.79794999529</v>
       </c>
       <c r="E60">
-        <v>-1546.83781858005</v>
+        <v>-1225.227394328143</v>
       </c>
       <c r="F60">
-        <v>18653.40460661054</v>
+        <v>18975.01503086245</v>
       </c>
       <c r="G60">
         <v>5127</v>
@@ -6207,28 +6207,28 @@
         <v>3542</v>
       </c>
       <c r="M60">
-        <v>1234.502945227634</v>
+        <v>1255.787478766042</v>
       </c>
       <c r="N60">
-        <v>2307.497054772366</v>
+        <v>2286.212521233958</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>2307.497054772366</v>
+        <v>2286.212521233958</v>
       </c>
       <c r="Q60">
-        <v>3470.497054772366</v>
+        <v>3449.212521233958</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1404652833238076</v>
+        <v>0.1427741926731687</v>
       </c>
       <c r="T60">
-        <v>1.733827909149849</v>
+        <v>1.77611639473887</v>
       </c>
       <c r="U60">
         <v>0.06618110587651872</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.869170959609884</v>
+        <v>2.820540943345309</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09758427146314523</v>
+        <v>0.09778808252191043</v>
       </c>
       <c r="C61">
-        <v>12419.78291913284</v>
+        <v>12019.55507453756</v>
       </c>
       <c r="D61">
-        <v>26267.79794999529</v>
+        <v>26189.18052965192</v>
       </c>
       <c r="E61">
-        <v>-1225.227394328143</v>
+        <v>-903.6169700762402</v>
       </c>
       <c r="F61">
-        <v>18975.01503086245</v>
+        <v>19296.62545511435</v>
       </c>
       <c r="G61">
         <v>5127</v>
@@ -6289,28 +6289,28 @@
         <v>3542</v>
       </c>
       <c r="M61">
-        <v>1255.787478766042</v>
+        <v>1277.072012304449</v>
       </c>
       <c r="N61">
-        <v>2286.212521233958</v>
+        <v>2264.927987695551</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>2286.212521233958</v>
+        <v>2264.927987695551</v>
       </c>
       <c r="Q61">
-        <v>3449.212521233958</v>
+        <v>3427.927987695551</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1427741926731687</v>
+        <v>0.145198547489998</v>
       </c>
       <c r="T61">
-        <v>1.77611639473887</v>
+        <v>1.820519304607342</v>
       </c>
       <c r="U61">
         <v>0.06618110587651872</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.820540943345309</v>
+        <v>2.773531927622888</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09778808252191043</v>
+        <v>0.09799189358067562</v>
       </c>
       <c r="C62">
-        <v>12019.55507453756</v>
+        <v>11619.79641701723</v>
       </c>
       <c r="D62">
-        <v>26189.18052965192</v>
+        <v>26111.0322963835</v>
       </c>
       <c r="E62">
-        <v>-903.6169700762402</v>
+        <v>-582.0065458243334</v>
       </c>
       <c r="F62">
-        <v>19296.62545511435</v>
+        <v>19618.23587936626</v>
       </c>
       <c r="G62">
         <v>5127</v>
@@ -6371,28 +6371,28 @@
         <v>3542</v>
       </c>
       <c r="M62">
-        <v>1277.072012304449</v>
+        <v>1298.356545842857</v>
       </c>
       <c r="N62">
-        <v>2264.927987695551</v>
+        <v>2243.643454157143</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>2264.927987695551</v>
+        <v>2243.643454157143</v>
       </c>
       <c r="Q62">
-        <v>3427.927987695551</v>
+        <v>3406.643454157143</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.145198547489998</v>
+        <v>0.1477472281948697</v>
       </c>
       <c r="T62">
-        <v>1.820519304607342</v>
+        <v>1.867199286776761</v>
       </c>
       <c r="U62">
         <v>0.06618110587651872</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.773531927622888</v>
+        <v>2.728064191104481</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09799189358067562</v>
+        <v>0.0981957046394408</v>
       </c>
       <c r="C63">
-        <v>11619.79641701723</v>
+        <v>11220.50275892019</v>
       </c>
       <c r="D63">
-        <v>26111.0322963835</v>
+        <v>26033.34906253836</v>
       </c>
       <c r="E63">
-        <v>-582.0065458243334</v>
+        <v>-260.3961215724266</v>
       </c>
       <c r="F63">
-        <v>19618.23587936626</v>
+        <v>19939.84630361817</v>
       </c>
       <c r="G63">
         <v>5127</v>
@@ -6453,28 +6453,28 @@
         <v>3542</v>
       </c>
       <c r="M63">
-        <v>1298.356545842857</v>
+        <v>1319.641079381264</v>
       </c>
       <c r="N63">
-        <v>2243.643454157143</v>
+        <v>2222.358920618735</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>2243.643454157143</v>
+        <v>2222.358920618735</v>
       </c>
       <c r="Q63">
-        <v>3406.643454157143</v>
+        <v>3385.358920618735</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1477472281948697</v>
+        <v>0.1504300499894716</v>
       </c>
       <c r="T63">
-        <v>1.867199286776761</v>
+        <v>1.916336110112992</v>
       </c>
       <c r="U63">
         <v>0.06618110587651872</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.728064191104481</v>
+        <v>2.684063155764084</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0981957046394408</v>
+        <v>0.09839951569820599</v>
       </c>
       <c r="C64">
-        <v>11220.50275892019</v>
+        <v>10821.66996228186</v>
       </c>
       <c r="D64">
-        <v>26033.34906253836</v>
+        <v>25956.12669015194</v>
       </c>
       <c r="E64">
-        <v>-260.3961215724266</v>
+        <v>61.21430267948017</v>
       </c>
       <c r="F64">
-        <v>19939.84630361817</v>
+        <v>20261.45672787007</v>
       </c>
       <c r="G64">
         <v>5127</v>
@@ -6535,28 +6535,28 @@
         <v>3542</v>
       </c>
       <c r="M64">
-        <v>1319.641079381264</v>
+        <v>1340.925612919672</v>
       </c>
       <c r="N64">
-        <v>2222.358920618735</v>
+        <v>2201.074387080328</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>2222.358920618735</v>
+        <v>2201.074387080328</v>
       </c>
       <c r="Q64">
-        <v>3385.358920618735</v>
+        <v>3364.074387080328</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1504300499894716</v>
+        <v>0.1532578891783762</v>
       </c>
       <c r="T64">
-        <v>1.916336110112992</v>
+        <v>1.968128977953883</v>
       </c>
       <c r="U64">
         <v>0.06618110587651872</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.684063155764084</v>
+        <v>2.641458978688465</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09839951569820599</v>
+        <v>0.09860332675697117</v>
       </c>
       <c r="C65">
-        <v>10821.66996228186</v>
+        <v>10423.29393809004</v>
       </c>
       <c r="D65">
-        <v>25956.12669015194</v>
+        <v>25879.36109021202</v>
       </c>
       <c r="E65">
-        <v>61.21430267948017</v>
+        <v>382.824726931387</v>
       </c>
       <c r="F65">
-        <v>20261.45672787007</v>
+        <v>20583.06715212198</v>
       </c>
       <c r="G65">
         <v>5127</v>
@@ -6617,28 +6617,28 @@
         <v>3542</v>
       </c>
       <c r="M65">
-        <v>1340.925612919672</v>
+        <v>1362.21014645808</v>
       </c>
       <c r="N65">
-        <v>2201.074387080328</v>
+        <v>2179.78985354192</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>2201.074387080328</v>
+        <v>2179.78985354192</v>
       </c>
       <c r="Q65">
-        <v>3364.074387080328</v>
+        <v>3342.78985354192</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1532578891783762</v>
+        <v>0.1562428305444422</v>
       </c>
       <c r="T65">
-        <v>1.968128977953883</v>
+        <v>2.022799227341491</v>
       </c>
       <c r="U65">
         <v>0.06618110587651872</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.641458978688465</v>
+        <v>2.600186182146457</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09860332675697117</v>
+        <v>0.09880713781573636</v>
       </c>
       <c r="C66">
-        <v>10423.29393809004</v>
+        <v>10025.37064556311</v>
       </c>
       <c r="D66">
-        <v>25879.36109021202</v>
+        <v>25803.048221937</v>
       </c>
       <c r="E66">
-        <v>382.824726931387</v>
+        <v>704.4351511832938</v>
       </c>
       <c r="F66">
-        <v>20583.06715212198</v>
+        <v>20904.67757637389</v>
       </c>
       <c r="G66">
         <v>5127</v>
@@ -6699,28 +6699,28 @@
         <v>3542</v>
       </c>
       <c r="M66">
-        <v>1362.21014645808</v>
+        <v>1383.494679996487</v>
       </c>
       <c r="N66">
-        <v>2179.78985354192</v>
+        <v>2158.505320003513</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>2179.78985354192</v>
+        <v>2158.505320003513</v>
       </c>
       <c r="Q66">
-        <v>3342.78985354192</v>
+        <v>3321.505320003513</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1562428305444422</v>
+        <v>0.1593983399885691</v>
       </c>
       <c r="T66">
-        <v>2.022799227341491</v>
+        <v>2.08059349097982</v>
       </c>
       <c r="U66">
         <v>0.06618110587651872</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.600186182146457</v>
+        <v>2.560183317805742</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09880713781573636</v>
+        <v>0.09901094887450154</v>
       </c>
       <c r="C67">
-        <v>10025.37064556311</v>
+        <v>9627.89609144102</v>
       </c>
       <c r="D67">
-        <v>25803.048221937</v>
+        <v>25727.18409206681</v>
       </c>
       <c r="E67">
-        <v>704.4351511832938</v>
+        <v>1026.045575435197</v>
       </c>
       <c r="F67">
-        <v>20904.67757637389</v>
+        <v>21226.28800062579</v>
       </c>
       <c r="G67">
         <v>5127</v>
@@ -6781,28 +6781,28 @@
         <v>3542</v>
       </c>
       <c r="M67">
-        <v>1383.494679996487</v>
+        <v>1404.779213534894</v>
       </c>
       <c r="N67">
-        <v>2158.505320003513</v>
+        <v>2137.220786465105</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>2158.505320003513</v>
+        <v>2137.220786465105</v>
       </c>
       <c r="Q67">
-        <v>3321.505320003513</v>
+        <v>3300.220786465105</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1593983399885691</v>
+        <v>0.1627394676352918</v>
       </c>
       <c r="T67">
-        <v>2.08059349097982</v>
+        <v>2.141787417185109</v>
       </c>
       <c r="U67">
         <v>0.06618110587651872</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.560183317805742</v>
+        <v>2.521392661475352</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09901094887450154</v>
+        <v>0.1015597599332667</v>
       </c>
       <c r="C68">
-        <v>9627.89609144102</v>
+        <v>8393.884473785147</v>
       </c>
       <c r="D68">
-        <v>25727.18409206681</v>
+        <v>24814.78289866284</v>
       </c>
       <c r="E68">
-        <v>1026.045575435197</v>
+        <v>1347.655999687104</v>
       </c>
       <c r="F68">
-        <v>21226.28800062579</v>
+        <v>21547.8984248777</v>
       </c>
       <c r="G68">
         <v>5127</v>
@@ -6863,45 +6863,45 @@
         <v>3542</v>
       </c>
       <c r="M68">
-        <v>1404.779213534894</v>
+        <v>1501.481391560374</v>
       </c>
       <c r="N68">
-        <v>2137.220786465105</v>
+        <v>2040.518608439626</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2137.220786465105</v>
+        <v>2040.518608439626</v>
       </c>
       <c r="Q68">
-        <v>3300.220786465105</v>
+        <v>3203.518608439626</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1627394676352918</v>
+        <v>0.1662830878666642</v>
       </c>
       <c r="T68">
-        <v>2.141787417185109</v>
+        <v>2.206690066190718</v>
       </c>
       <c r="U68">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.521392661475352</v>
+        <v>2.35900359465599</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1015597599332667</v>
+        <v>0.1017985709920319</v>
       </c>
       <c r="C69">
-        <v>8393.884473785147</v>
+        <v>7990.091395989562</v>
       </c>
       <c r="D69">
-        <v>24814.78289866284</v>
+        <v>24732.60024511917</v>
       </c>
       <c r="E69">
-        <v>1347.655999687104</v>
+        <v>1669.266423939011</v>
       </c>
       <c r="F69">
-        <v>21547.8984248777</v>
+        <v>21869.5088491296</v>
       </c>
       <c r="G69">
         <v>5127</v>
@@ -6945,28 +6945,28 @@
         <v>3542</v>
       </c>
       <c r="M69">
-        <v>1501.481391560374</v>
+        <v>1523.891561583663</v>
       </c>
       <c r="N69">
-        <v>2040.518608439626</v>
+        <v>2018.108438416337</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2040.518608439626</v>
+        <v>2018.108438416337</v>
       </c>
       <c r="Q69">
-        <v>3203.518608439626</v>
+        <v>3181.108438416337</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1662830878666642</v>
+        <v>0.1700481843624975</v>
       </c>
       <c r="T69">
-        <v>2.206690066190718</v>
+        <v>2.275649130759178</v>
       </c>
       <c r="U69">
         <v>0.06968110587651873</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.35900359465599</v>
+        <v>2.324312365322814</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1017985709920319</v>
+        <v>0.1020373820507971</v>
       </c>
       <c r="C70">
-        <v>7990.091395989562</v>
+        <v>7586.840873352303</v>
       </c>
       <c r="D70">
-        <v>24732.60024511917</v>
+        <v>24650.96014673381</v>
       </c>
       <c r="E70">
-        <v>1669.266423939011</v>
+        <v>1990.876848190917</v>
       </c>
       <c r="F70">
-        <v>21869.5088491296</v>
+        <v>22191.11927338151</v>
       </c>
       <c r="G70">
         <v>5127</v>
@@ -7027,28 +7027,28 @@
         <v>3542</v>
       </c>
       <c r="M70">
-        <v>1523.891561583663</v>
+        <v>1546.301731606952</v>
       </c>
       <c r="N70">
-        <v>2018.108438416337</v>
+        <v>1995.698268393048</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>2018.108438416337</v>
+        <v>1995.698268393048</v>
       </c>
       <c r="Q70">
-        <v>3181.108438416337</v>
+        <v>3158.698268393047</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1700481843624975</v>
+        <v>0.1740561903096748</v>
       </c>
       <c r="T70">
-        <v>2.275649130759178</v>
+        <v>2.34905716723528</v>
       </c>
       <c r="U70">
         <v>0.06968110587651873</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.324312365322814</v>
+        <v>2.290626678868859</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1020373820507971</v>
+        <v>0.1022761931095623</v>
       </c>
       <c r="C71">
-        <v>7586.840873352303</v>
+        <v>7184.127550772126</v>
       </c>
       <c r="D71">
-        <v>24650.96014673381</v>
+        <v>24569.85724840554</v>
       </c>
       <c r="E71">
-        <v>1990.876848190917</v>
+        <v>2312.487272442824</v>
       </c>
       <c r="F71">
-        <v>22191.11927338151</v>
+        <v>22512.72969763342</v>
       </c>
       <c r="G71">
         <v>5127</v>
@@ -7109,28 +7109,28 @@
         <v>3542</v>
       </c>
       <c r="M71">
-        <v>1546.301731606952</v>
+        <v>1568.711901630242</v>
       </c>
       <c r="N71">
-        <v>1995.698268393048</v>
+        <v>1973.288098369758</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>1995.698268393048</v>
+        <v>1973.288098369758</v>
       </c>
       <c r="Q71">
-        <v>3158.698268393047</v>
+        <v>3136.288098369759</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1740561903096748</v>
+        <v>0.1783313966533307</v>
       </c>
       <c r="T71">
-        <v>2.34905716723528</v>
+        <v>2.42735907280979</v>
       </c>
       <c r="U71">
         <v>0.06968110587651873</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.290626678868859</v>
+        <v>2.257903440599304</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1022761931095623</v>
+        <v>0.1045030041683275</v>
       </c>
       <c r="C72">
-        <v>7184.127550772126</v>
+        <v>6131.191207107226</v>
       </c>
       <c r="D72">
-        <v>24569.85724840554</v>
+        <v>23838.53132899255</v>
       </c>
       <c r="E72">
-        <v>2312.487272442824</v>
+        <v>2634.097696694731</v>
       </c>
       <c r="F72">
-        <v>22512.72969763342</v>
+        <v>22834.34012188533</v>
       </c>
       <c r="G72">
         <v>5127</v>
@@ -7191,45 +7191,45 @@
         <v>3542</v>
       </c>
       <c r="M72">
-        <v>1568.711901630242</v>
+        <v>1655.05822399481</v>
       </c>
       <c r="N72">
-        <v>1973.288098369758</v>
+        <v>1886.94177600519</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>1973.288098369758</v>
+        <v>1886.94177600519</v>
       </c>
       <c r="Q72">
-        <v>3136.288098369759</v>
+        <v>3049.94177600519</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1783313966533307</v>
+        <v>0.1829014448137904</v>
       </c>
       <c r="T72">
-        <v>2.42735907280979</v>
+        <v>2.511061109803231</v>
       </c>
       <c r="U72">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.257903440599304</v>
+        <v>2.140105978538135</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1045030041683275</v>
+        <v>0.1047698152270927</v>
       </c>
       <c r="C73">
-        <v>6131.191207107229</v>
+        <v>5724.865419716694</v>
       </c>
       <c r="D73">
-        <v>23838.53132899255</v>
+        <v>23753.81596585392</v>
       </c>
       <c r="E73">
-        <v>2634.097696694727</v>
+        <v>2955.708120946631</v>
       </c>
       <c r="F73">
-        <v>22834.34012188532</v>
+        <v>23155.95054613722</v>
       </c>
       <c r="G73">
         <v>5127</v>
@@ -7273,28 +7273,28 @@
         <v>3542</v>
       </c>
       <c r="M73">
-        <v>1655.058223994809</v>
+        <v>1678.368903206004</v>
       </c>
       <c r="N73">
-        <v>1886.941776005191</v>
+        <v>1863.631096793996</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>1886.941776005191</v>
+        <v>1863.631096793996</v>
       </c>
       <c r="Q73">
-        <v>3049.941776005191</v>
+        <v>3026.631096793996</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1829014448137903</v>
+        <v>0.1877979249857114</v>
       </c>
       <c r="T73">
-        <v>2.51106110980323</v>
+        <v>2.600741863724774</v>
       </c>
       <c r="U73">
         <v>0.07248110587651872</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.140105978538135</v>
+        <v>2.110382284391773</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1047698152270927</v>
+        <v>0.1050366262858579</v>
       </c>
       <c r="C74">
-        <v>5724.865419716694</v>
+        <v>5319.139608812962</v>
       </c>
       <c r="D74">
-        <v>23753.81596585392</v>
+        <v>23669.70057920209</v>
       </c>
       <c r="E74">
-        <v>2955.708120946631</v>
+        <v>3277.318545198537</v>
       </c>
       <c r="F74">
-        <v>23155.95054613722</v>
+        <v>23477.56097038913</v>
       </c>
       <c r="G74">
         <v>5127</v>
@@ -7355,28 +7355,28 @@
         <v>3542</v>
       </c>
       <c r="M74">
-        <v>1678.368903206004</v>
+        <v>1701.679582417198</v>
       </c>
       <c r="N74">
-        <v>1863.631096793996</v>
+        <v>1840.320417582802</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1863.631096793996</v>
+        <v>1840.320417582802</v>
       </c>
       <c r="Q74">
-        <v>3026.631096793996</v>
+        <v>3003.320417582801</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1877979249857114</v>
+        <v>0.1930571073925896</v>
       </c>
       <c r="T74">
-        <v>2.600741863724774</v>
+        <v>2.697065636455321</v>
       </c>
       <c r="U74">
         <v>0.07248110587651872</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.110382284391773</v>
+        <v>2.081472938030241</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1050366262858579</v>
+        <v>0.1053034373446231</v>
       </c>
       <c r="C75">
-        <v>5319.139608812962</v>
+        <v>4914.007423099851</v>
       </c>
       <c r="D75">
-        <v>23669.70057920209</v>
+        <v>23586.17881774089</v>
       </c>
       <c r="E75">
-        <v>3277.318545198537</v>
+        <v>3598.928969450444</v>
       </c>
       <c r="F75">
-        <v>23477.56097038913</v>
+        <v>23799.17139464104</v>
       </c>
       <c r="G75">
         <v>5127</v>
@@ -7437,28 +7437,28 @@
         <v>3542</v>
       </c>
       <c r="M75">
-        <v>1701.679582417198</v>
+        <v>1724.990261628393</v>
       </c>
       <c r="N75">
-        <v>1840.320417582802</v>
+        <v>1817.009738371607</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>1840.320417582802</v>
+        <v>1817.009738371607</v>
       </c>
       <c r="Q75">
-        <v>3003.320417582801</v>
+        <v>2980.009738371607</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1930571073925896</v>
+        <v>0.1987208422923046</v>
       </c>
       <c r="T75">
-        <v>2.697065636455321</v>
+        <v>2.800798930165141</v>
       </c>
       <c r="U75">
         <v>0.07248110587651872</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.081472938030241</v>
+        <v>2.053344925354157</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1053034373446231</v>
+        <v>0.1055702484033882</v>
       </c>
       <c r="C76">
-        <v>4914.007423099851</v>
+        <v>4509.462600611612</v>
       </c>
       <c r="D76">
-        <v>23586.17881774089</v>
+        <v>23503.24441950456</v>
       </c>
       <c r="E76">
-        <v>3598.928969450444</v>
+        <v>3920.539393702351</v>
       </c>
       <c r="F76">
-        <v>23799.17139464104</v>
+        <v>24120.78181889295</v>
       </c>
       <c r="G76">
         <v>5127</v>
@@ -7519,28 +7519,28 @@
         <v>3542</v>
       </c>
       <c r="M76">
-        <v>1724.990261628393</v>
+        <v>1748.300940839587</v>
       </c>
       <c r="N76">
-        <v>1817.009738371607</v>
+        <v>1793.699059160413</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>1817.009738371607</v>
+        <v>1793.699059160413</v>
       </c>
       <c r="Q76">
-        <v>2980.009738371607</v>
+        <v>2956.699059160413</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1987208422923046</v>
+        <v>0.2048376759839968</v>
       </c>
       <c r="T76">
-        <v>2.800798930165141</v>
+        <v>2.912830887371747</v>
       </c>
       <c r="U76">
         <v>0.07248110587651872</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.053344925354157</v>
+        <v>2.025966993016102</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1055702484033882</v>
+        <v>0.1117650594621534</v>
       </c>
       <c r="C77">
-        <v>4509.462600611612</v>
+        <v>2413.88103092981</v>
       </c>
       <c r="D77">
-        <v>23503.24441950456</v>
+        <v>21729.27327407466</v>
       </c>
       <c r="E77">
-        <v>3920.539393702351</v>
+        <v>4242.149817954258</v>
       </c>
       <c r="F77">
-        <v>24120.78181889295</v>
+        <v>24442.39224314485</v>
       </c>
       <c r="G77">
         <v>5127</v>
@@ -7601,45 +7601,45 @@
         <v>3542</v>
       </c>
       <c r="M77">
-        <v>1748.300940839587</v>
+        <v>1962.262279547312</v>
       </c>
       <c r="N77">
-        <v>1793.699059160413</v>
+        <v>1579.737720452688</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>1793.699059160413</v>
+        <v>1579.737720452688</v>
       </c>
       <c r="Q77">
-        <v>2956.699059160413</v>
+        <v>2742.737720452688</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2048376759839968</v>
+        <v>0.2114642458166633</v>
       </c>
       <c r="T77">
-        <v>2.912830887371747</v>
+        <v>3.034198841012237</v>
       </c>
       <c r="U77">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.025966993016102</v>
+        <v>1.805059413778839</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1117650594621534</v>
+        <v>0.1121098705209186</v>
       </c>
       <c r="C78">
-        <v>2413.88103092981</v>
+        <v>2001.363815644043</v>
       </c>
       <c r="D78">
-        <v>21729.27327407466</v>
+        <v>21638.3664830408</v>
       </c>
       <c r="E78">
-        <v>4242.149817954258</v>
+        <v>4563.760242206165</v>
       </c>
       <c r="F78">
-        <v>24442.39224314485</v>
+        <v>24764.00266739676</v>
       </c>
       <c r="G78">
         <v>5127</v>
@@ -7683,28 +7683,28 @@
         <v>3542</v>
       </c>
       <c r="M78">
-        <v>1962.262279547312</v>
+        <v>1988.081520067672</v>
       </c>
       <c r="N78">
-        <v>1579.737720452688</v>
+        <v>1553.918479932328</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>1579.737720452688</v>
+        <v>1553.918479932328</v>
       </c>
       <c r="Q78">
-        <v>2742.737720452688</v>
+        <v>2716.918479932328</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2114642458166633</v>
+        <v>0.21866703911304</v>
       </c>
       <c r="T78">
-        <v>3.034198841012237</v>
+        <v>3.166120529751899</v>
       </c>
       <c r="U78">
         <v>0.08028110587651874</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.805059413778839</v>
+        <v>1.781617083729763</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1121098705209186</v>
+        <v>0.1124546815796838</v>
       </c>
       <c r="C79">
-        <v>2001.363815644043</v>
+        <v>1589.604068411365</v>
       </c>
       <c r="D79">
-        <v>21638.3664830408</v>
+        <v>21548.21716006003</v>
       </c>
       <c r="E79">
-        <v>4563.760242206165</v>
+        <v>4885.370666458071</v>
       </c>
       <c r="F79">
-        <v>24764.00266739676</v>
+        <v>25085.61309164867</v>
       </c>
       <c r="G79">
         <v>5127</v>
@@ -7765,28 +7765,28 @@
         <v>3542</v>
       </c>
       <c r="M79">
-        <v>1988.081520067672</v>
+        <v>2013.900760588031</v>
       </c>
       <c r="N79">
-        <v>1553.918479932328</v>
+        <v>1528.099239411969</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>1553.918479932328</v>
+        <v>1528.099239411969</v>
       </c>
       <c r="Q79">
-        <v>2716.918479932328</v>
+        <v>2691.099239411969</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.21866703911304</v>
+        <v>0.2265246317999964</v>
       </c>
       <c r="T79">
-        <v>3.166120529751899</v>
+        <v>3.310035099286077</v>
       </c>
       <c r="U79">
         <v>0.08028110587651874</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.781617083729763</v>
+        <v>1.758775839066561</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1124546815796838</v>
+        <v>0.115880492638449</v>
       </c>
       <c r="C80">
-        <v>1589.604068411365</v>
+        <v>411.5137474783878</v>
       </c>
       <c r="D80">
-        <v>21548.21716006003</v>
+        <v>20691.73726337896</v>
       </c>
       <c r="E80">
-        <v>4885.370666458071</v>
+        <v>5206.981090709975</v>
       </c>
       <c r="F80">
-        <v>25085.61309164867</v>
+        <v>25407.22351590057</v>
       </c>
       <c r="G80">
         <v>5127</v>
@@ -7847,45 +7847,45 @@
         <v>3542</v>
       </c>
       <c r="M80">
-        <v>2013.900760588031</v>
+        <v>2138.808172820402</v>
       </c>
       <c r="N80">
-        <v>1528.099239411969</v>
+        <v>1403.191827179598</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>1528.099239411969</v>
+        <v>1403.191827179598</v>
       </c>
       <c r="Q80">
-        <v>2691.099239411969</v>
+        <v>2566.191827179598</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2265246317999964</v>
+        <v>0.2351305666476153</v>
       </c>
       <c r="T80">
-        <v>3.310035099286077</v>
+        <v>3.4676558182997</v>
       </c>
       <c r="U80">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>1.758775839066561</v>
+        <v>1.656062495464115</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.115880492638449</v>
+        <v>0.1162643036972142</v>
       </c>
       <c r="C81">
-        <v>411.5137474783878</v>
+        <v>-1.83001753652934</v>
       </c>
       <c r="D81">
-        <v>20691.73726337896</v>
+        <v>20600.00392261595</v>
       </c>
       <c r="E81">
-        <v>5206.981090709975</v>
+        <v>5528.591514961881</v>
       </c>
       <c r="F81">
-        <v>25407.22351590057</v>
+        <v>25728.83394015248</v>
       </c>
       <c r="G81">
         <v>5127</v>
@@ -7929,28 +7929,28 @@
         <v>3542</v>
       </c>
       <c r="M81">
-        <v>2138.808172820402</v>
+        <v>2165.881693995344</v>
       </c>
       <c r="N81">
-        <v>1403.191827179598</v>
+        <v>1376.118306004656</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>1403.191827179598</v>
+        <v>1376.118306004656</v>
       </c>
       <c r="Q81">
-        <v>2566.191827179598</v>
+        <v>2539.118306004656</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2351305666476153</v>
+        <v>0.244597094979996</v>
       </c>
       <c r="T81">
-        <v>3.4676558182997</v>
+        <v>3.641038609214684</v>
       </c>
       <c r="U81">
         <v>0.08418110587651872</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.656062495464115</v>
+        <v>1.635361714270814</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1162643036972142</v>
+        <v>0.1166481147559794</v>
       </c>
       <c r="C82">
-        <v>-1.83001753652934</v>
+        <v>-414.3640038606936</v>
       </c>
       <c r="D82">
-        <v>20600.00392261595</v>
+        <v>20509.08036054369</v>
       </c>
       <c r="E82">
-        <v>5528.591514961881</v>
+        <v>5850.201939213788</v>
       </c>
       <c r="F82">
-        <v>25728.83394015248</v>
+        <v>26050.44436440438</v>
       </c>
       <c r="G82">
         <v>5127</v>
@@ -8011,28 +8011,28 @@
         <v>3542</v>
       </c>
       <c r="M82">
-        <v>2165.881693995344</v>
+        <v>2192.955215170286</v>
       </c>
       <c r="N82">
-        <v>1376.118306004656</v>
+        <v>1349.044784829714</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>1376.118306004656</v>
+        <v>1349.044784829714</v>
       </c>
       <c r="Q82">
-        <v>2539.118306004656</v>
+        <v>2512.044784829714</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.244597094979996</v>
+        <v>0.2550600999789432</v>
       </c>
       <c r="T82">
-        <v>3.641038609214684</v>
+        <v>3.832672220225984</v>
       </c>
       <c r="U82">
         <v>0.08418110587651872</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.635361714270814</v>
+        <v>1.615172063477347</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1166481147559794</v>
+        <v>0.1170319258147445</v>
       </c>
       <c r="C83">
-        <v>-414.3640038606936</v>
+        <v>-826.0988868922686</v>
       </c>
       <c r="D83">
-        <v>20509.08036054369</v>
+        <v>20418.95590176402</v>
       </c>
       <c r="E83">
-        <v>5850.201939213788</v>
+        <v>6171.812363465695</v>
       </c>
       <c r="F83">
-        <v>26050.44436440438</v>
+        <v>26372.05478865629</v>
       </c>
       <c r="G83">
         <v>5127</v>
@@ -8093,28 +8093,28 @@
         <v>3542</v>
       </c>
       <c r="M83">
-        <v>2192.955215170286</v>
+        <v>2220.028736345228</v>
       </c>
       <c r="N83">
-        <v>1349.044784829714</v>
+        <v>1321.971263654772</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>1349.044784829714</v>
+        <v>1321.971263654772</v>
       </c>
       <c r="Q83">
-        <v>2512.044784829714</v>
+        <v>2484.971263654772</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2550600999789432</v>
+        <v>0.2666856610888845</v>
       </c>
       <c r="T83">
-        <v>3.832672220225984</v>
+        <v>4.045598454682984</v>
       </c>
       <c r="U83">
         <v>0.08418110587651872</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.615172063477347</v>
+        <v>1.595474843191038</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1170319258147445</v>
+        <v>0.1174157368735097</v>
       </c>
       <c r="C84">
-        <v>-826.0988868922686</v>
+        <v>-1237.04515520385</v>
       </c>
       <c r="D84">
-        <v>20418.95590176402</v>
+        <v>20329.62005770435</v>
       </c>
       <c r="E84">
-        <v>6171.812363465695</v>
+        <v>6493.422787717602</v>
       </c>
       <c r="F84">
-        <v>26372.05478865629</v>
+        <v>26693.6652129082</v>
       </c>
       <c r="G84">
         <v>5127</v>
@@ -8175,28 +8175,28 @@
         <v>3542</v>
       </c>
       <c r="M84">
-        <v>2220.028736345228</v>
+        <v>2247.10225752017</v>
       </c>
       <c r="N84">
-        <v>1321.971263654772</v>
+        <v>1294.89774247983</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>1321.971263654772</v>
+        <v>1294.89774247983</v>
       </c>
       <c r="Q84">
-        <v>2484.971263654772</v>
+        <v>2457.89774247983</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2666856610888845</v>
+        <v>0.2796789352705836</v>
       </c>
       <c r="T84">
-        <v>4.045598454682984</v>
+        <v>4.283574834370218</v>
       </c>
       <c r="U84">
         <v>0.08418110587651872</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.595474843191038</v>
+        <v>1.576252254718856</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1174157368735097</v>
+        <v>0.1177995479322749</v>
       </c>
       <c r="C85">
-        <v>-1237.04515520385</v>
+        <v>-1647.213114611626</v>
       </c>
       <c r="D85">
-        <v>20329.62005770435</v>
+        <v>20241.06252254848</v>
       </c>
       <c r="E85">
-        <v>6493.422787717602</v>
+        <v>6815.033211969509</v>
       </c>
       <c r="F85">
-        <v>26693.6652129082</v>
+        <v>27015.2756371601</v>
       </c>
       <c r="G85">
         <v>5127</v>
@@ -8257,28 +8257,28 @@
         <v>3542</v>
       </c>
       <c r="M85">
-        <v>2247.10225752017</v>
+        <v>2274.175778695112</v>
       </c>
       <c r="N85">
-        <v>1294.89774247983</v>
+        <v>1267.824221304888</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>1294.89774247983</v>
+        <v>1267.824221304888</v>
       </c>
       <c r="Q85">
-        <v>2457.89774247983</v>
+        <v>2430.824221304888</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2796789352705836</v>
+        <v>0.2942963687249951</v>
       </c>
       <c r="T85">
-        <v>4.283574834370218</v>
+        <v>4.551298261518357</v>
       </c>
       <c r="U85">
         <v>0.08418110587651872</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.576252254718856</v>
+        <v>1.557487346924584</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1177995479322749</v>
+        <v>0.1181833589910401</v>
       </c>
       <c r="C86">
-        <v>-1647.213114611623</v>
+        <v>-2056.61289213859</v>
       </c>
       <c r="D86">
-        <v>20241.06252254848</v>
+        <v>20153.27316927341</v>
       </c>
       <c r="E86">
-        <v>6815.033211969505</v>
+        <v>7136.643636221408</v>
       </c>
       <c r="F86">
-        <v>27015.2756371601</v>
+        <v>27336.886061412</v>
       </c>
       <c r="G86">
         <v>5127</v>
@@ -8339,28 +8339,28 @@
         <v>3542</v>
       </c>
       <c r="M86">
-        <v>2274.175778695111</v>
+        <v>2301.249299870053</v>
       </c>
       <c r="N86">
-        <v>1267.824221304889</v>
+        <v>1240.750700129947</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>1267.824221304889</v>
+        <v>1240.750700129947</v>
       </c>
       <c r="Q86">
-        <v>2430.824221304889</v>
+        <v>2403.750700129947</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2942963687249949</v>
+        <v>0.3108627933066613</v>
       </c>
       <c r="T86">
-        <v>4.551298261518355</v>
+        <v>4.854718145619579</v>
       </c>
       <c r="U86">
         <v>0.08418110587651872</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.557487346924585</v>
+        <v>1.539163966372531</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1181833589910401</v>
+        <v>0.1185671700498053</v>
       </c>
       <c r="C87">
-        <v>-2056.61289213859</v>
+        <v>-2465.254439875163</v>
       </c>
       <c r="D87">
-        <v>20153.27316927341</v>
+        <v>20066.24204578875</v>
       </c>
       <c r="E87">
-        <v>7136.643636221408</v>
+        <v>7458.254060473315</v>
       </c>
       <c r="F87">
-        <v>27336.886061412</v>
+        <v>27658.49648566391</v>
       </c>
       <c r="G87">
         <v>5127</v>
@@ -8421,28 +8421,28 @@
         <v>3542</v>
       </c>
       <c r="M87">
-        <v>2301.249299870053</v>
+        <v>2328.322821044995</v>
       </c>
       <c r="N87">
-        <v>1240.750700129947</v>
+        <v>1213.677178955005</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>1240.750700129947</v>
+        <v>1213.677178955005</v>
       </c>
       <c r="Q87">
-        <v>2403.750700129947</v>
+        <v>2376.677178955005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3108627933066613</v>
+        <v>0.3297958499714228</v>
       </c>
       <c r="T87">
-        <v>4.854718145619579</v>
+        <v>5.201483727449548</v>
       </c>
       <c r="U87">
         <v>0.08418110587651872</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.539163966372531</v>
+        <v>1.521266710949594</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1185671700498053</v>
+        <v>0.1189509811085705</v>
       </c>
       <c r="C88">
-        <v>-2465.254439875163</v>
+        <v>-2873.147538740075</v>
       </c>
       <c r="D88">
-        <v>20066.24204578875</v>
+        <v>19979.95937117574</v>
       </c>
       <c r="E88">
-        <v>7458.254060473315</v>
+        <v>7779.864484725222</v>
       </c>
       <c r="F88">
-        <v>27658.49648566391</v>
+        <v>27980.10690991582</v>
       </c>
       <c r="G88">
         <v>5127</v>
@@ -8503,28 +8503,28 @@
         <v>3542</v>
       </c>
       <c r="M88">
-        <v>2328.322821044995</v>
+        <v>2355.396342219936</v>
       </c>
       <c r="N88">
-        <v>1213.677178955005</v>
+        <v>1186.603657780064</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>1213.677178955005</v>
+        <v>1186.603657780064</v>
       </c>
       <c r="Q88">
-        <v>2376.677178955005</v>
+        <v>2349.603657780064</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3297958499714228</v>
+        <v>0.3516416845846091</v>
       </c>
       <c r="T88">
-        <v>5.201483727449548</v>
+        <v>5.601597860330283</v>
       </c>
       <c r="U88">
         <v>0.08418110587651872</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.521266710949594</v>
+        <v>1.503780886685806</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1189509811085705</v>
+        <v>0.1318307921673357</v>
       </c>
       <c r="C89">
-        <v>-2873.147538740075</v>
+        <v>-5714.211642984934</v>
       </c>
       <c r="D89">
-        <v>19979.95937117574</v>
+        <v>17460.50569118279</v>
       </c>
       <c r="E89">
-        <v>7779.864484725222</v>
+        <v>8101.474908977129</v>
       </c>
       <c r="F89">
-        <v>27980.10690991582</v>
+        <v>28301.71733416772</v>
       </c>
       <c r="G89">
         <v>5127</v>
@@ -8585,45 +8585,45 @@
         <v>3542</v>
       </c>
       <c r="M89">
-        <v>2355.396342219936</v>
+        <v>2784.35424954006</v>
       </c>
       <c r="N89">
-        <v>1186.603657780064</v>
+        <v>757.6457504599398</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1186.603657780064</v>
+        <v>757.6457504599398</v>
       </c>
       <c r="Q89">
-        <v>2349.603657780064</v>
+        <v>1920.64575045994</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3516416845846091</v>
+        <v>0.3771284916333266</v>
       </c>
       <c r="T89">
-        <v>5.601597860330283</v>
+        <v>6.068397682024473</v>
       </c>
       <c r="U89">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.503780886685806</v>
+        <v>1.272108245775513</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1318307921673357</v>
+        <v>0.1323566032261009</v>
       </c>
       <c r="C90">
-        <v>-5714.211642984934</v>
+        <v>-6125.247044717082</v>
       </c>
       <c r="D90">
-        <v>17460.50569118279</v>
+        <v>17371.08071370255</v>
       </c>
       <c r="E90">
-        <v>8101.474908977129</v>
+        <v>8423.085333229035</v>
       </c>
       <c r="F90">
-        <v>28301.71733416772</v>
+        <v>28623.32775841963</v>
       </c>
       <c r="G90">
         <v>5127</v>
@@ -8667,28 +8667,28 @@
         <v>3542</v>
       </c>
       <c r="M90">
-        <v>2784.35424954006</v>
+        <v>2815.994638739379</v>
       </c>
       <c r="N90">
-        <v>757.6457504599398</v>
+        <v>726.0053612606212</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>757.6457504599398</v>
+        <v>726.0053612606212</v>
       </c>
       <c r="Q90">
-        <v>1920.64575045994</v>
+        <v>1889.005361260621</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3771284916333266</v>
+        <v>0.4072492635999928</v>
       </c>
       <c r="T90">
-        <v>6.068397682024473</v>
+        <v>6.620070198572154</v>
       </c>
       <c r="U90">
         <v>0.09838110587651873</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.272108245775513</v>
+        <v>1.257814894699383</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1323566032261009</v>
+        <v>0.1586224142848661</v>
       </c>
       <c r="C91">
-        <v>-6125.247044717082</v>
+        <v>-9985.663290622808</v>
       </c>
       <c r="D91">
-        <v>17371.08071370255</v>
+        <v>13832.27489204873</v>
       </c>
       <c r="E91">
-        <v>8423.085333229035</v>
+        <v>8744.695757480942</v>
       </c>
       <c r="F91">
-        <v>28623.32775841963</v>
+        <v>28944.93818267154</v>
       </c>
       <c r="G91">
         <v>5127</v>
@@ -8749,45 +8749,45 @@
         <v>3542</v>
       </c>
       <c r="M91">
-        <v>2815.994638739379</v>
+        <v>3675.460259963104</v>
       </c>
       <c r="N91">
-        <v>726.0053612606212</v>
+        <v>-133.4602599631039</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P91">
-        <v>726.0053612606212</v>
+        <v>-133.4602599631039</v>
       </c>
       <c r="Q91">
-        <v>1889.005361260621</v>
+        <v>1029.539740036896</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4072492635999928</v>
+        <v>0.443394189959992</v>
       </c>
       <c r="T91">
-        <v>6.620070198572154</v>
+        <v>7.282077218429369</v>
       </c>
       <c r="U91">
-        <v>0.09838110587651873</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.09838110587651873</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.257814894699383</v>
+        <v>0.9636888306433644</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1586224142848661</v>
+        <v>0.1594342253436312</v>
       </c>
       <c r="C92">
-        <v>-9985.663290622808</v>
+        <v>-10393.82264892921</v>
       </c>
       <c r="D92">
-        <v>13832.27489204873</v>
+        <v>13745.72595799423</v>
       </c>
       <c r="E92">
-        <v>8744.695757480942</v>
+        <v>9066.306181732845</v>
       </c>
       <c r="F92">
-        <v>28944.93818267154</v>
+        <v>29266.54860692344</v>
       </c>
       <c r="G92">
         <v>5127</v>
@@ -8831,28 +8831,28 @@
         <v>3542</v>
       </c>
       <c r="M92">
-        <v>3675.460259963104</v>
+        <v>3716.298707296027</v>
       </c>
       <c r="N92">
-        <v>-133.4602599631039</v>
+        <v>-174.2987072960268</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-133.4602599631039</v>
+        <v>-174.2987072960268</v>
       </c>
       <c r="Q92">
-        <v>1029.539740036896</v>
+        <v>988.7012927039732</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.443394189959992</v>
+        <v>0.487571322177769</v>
       </c>
       <c r="T92">
-        <v>7.282077218429369</v>
+        <v>8.091196909365967</v>
       </c>
       <c r="U92">
         <v>0.1269811058765187</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9636888306433644</v>
+        <v>0.9530988434934375</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1594342253436312</v>
+        <v>0.1602460364023964</v>
       </c>
       <c r="C93">
-        <v>-10393.82264892921</v>
+        <v>-10800.90566370551</v>
       </c>
       <c r="D93">
-        <v>13745.72595799423</v>
+        <v>13660.25336746983</v>
       </c>
       <c r="E93">
-        <v>9066.306181732845</v>
+        <v>9387.916605984752</v>
       </c>
       <c r="F93">
-        <v>29266.54860692344</v>
+        <v>29588.15903117535</v>
       </c>
       <c r="G93">
         <v>5127</v>
@@ -8913,28 +8913,28 @@
         <v>3542</v>
       </c>
       <c r="M93">
-        <v>3716.298707296027</v>
+        <v>3757.137154628951</v>
       </c>
       <c r="N93">
-        <v>-174.2987072960268</v>
+        <v>-215.1371546289506</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-174.2987072960268</v>
+        <v>-215.1371546289506</v>
       </c>
       <c r="Q93">
-        <v>988.7012927039732</v>
+        <v>947.8628453710494</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.487571322177769</v>
+        <v>0.5427927374499901</v>
       </c>
       <c r="T93">
-        <v>8.091196909365967</v>
+        <v>9.102596523036715</v>
       </c>
       <c r="U93">
         <v>0.1269811058765187</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9530988434934375</v>
+        <v>0.9427390734554653</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1602460364023964</v>
+        <v>0.1610578474611616</v>
       </c>
       <c r="C94">
-        <v>-10800.90566370551</v>
+        <v>-11206.93228937637</v>
       </c>
       <c r="D94">
-        <v>13660.25336746983</v>
+        <v>13575.83716605088</v>
       </c>
       <c r="E94">
-        <v>9387.916605984752</v>
+        <v>9709.527030236659</v>
       </c>
       <c r="F94">
-        <v>29588.15903117535</v>
+        <v>29909.76945542725</v>
       </c>
       <c r="G94">
         <v>5127</v>
@@ -8995,28 +8995,28 @@
         <v>3542</v>
       </c>
       <c r="M94">
-        <v>3757.137154628951</v>
+        <v>3797.975601961874</v>
       </c>
       <c r="N94">
-        <v>-215.1371546289506</v>
+        <v>-255.975601961874</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-215.1371546289506</v>
+        <v>-255.975601961874</v>
       </c>
       <c r="Q94">
-        <v>947.8628453710494</v>
+        <v>907.024398038126</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5427927374499901</v>
+        <v>0.6137916999428459</v>
       </c>
       <c r="T94">
-        <v>9.102596523036715</v>
+        <v>10.4029674548991</v>
       </c>
       <c r="U94">
         <v>0.1269811058765187</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9427390734554653</v>
+        <v>0.9326020941709979</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1610578474611616</v>
+        <v>0.1618696585199268</v>
       </c>
       <c r="C95">
-        <v>-11206.93228937637</v>
+        <v>-11611.92199014681</v>
       </c>
       <c r="D95">
-        <v>13575.83716605088</v>
+        <v>13492.45788953235</v>
       </c>
       <c r="E95">
-        <v>9709.527030236659</v>
+        <v>10031.13745448857</v>
       </c>
       <c r="F95">
-        <v>29909.76945542725</v>
+        <v>30231.37987967916</v>
       </c>
       <c r="G95">
         <v>5127</v>
@@ -9077,28 +9077,28 @@
         <v>3542</v>
       </c>
       <c r="M95">
-        <v>3797.975601961874</v>
+        <v>3838.814049294797</v>
       </c>
       <c r="N95">
-        <v>-255.975601961874</v>
+        <v>-296.8140492947973</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-255.975601961874</v>
+        <v>-296.8140492947973</v>
       </c>
       <c r="Q95">
-        <v>907.024398038126</v>
+        <v>866.1859507052027</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6137916999428459</v>
+        <v>0.7084569832666537</v>
       </c>
       <c r="T95">
-        <v>10.4029674548991</v>
+        <v>12.13679536404896</v>
       </c>
       <c r="U95">
         <v>0.1269811058765187</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.9326020941709979</v>
+        <v>0.9226807952968383</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1618696585199268</v>
+        <v>0.162681469578692</v>
       </c>
       <c r="C96">
-        <v>-11611.92199014681</v>
+        <v>-12015.89375496434</v>
       </c>
       <c r="D96">
-        <v>13492.45788953235</v>
+        <v>13410.09654896673</v>
       </c>
       <c r="E96">
-        <v>10031.13745448857</v>
+        <v>10352.74787874047</v>
       </c>
       <c r="F96">
-        <v>30231.37987967916</v>
+        <v>30552.99030393107</v>
       </c>
       <c r="G96">
         <v>5127</v>
@@ -9159,28 +9159,28 @@
         <v>3542</v>
       </c>
       <c r="M96">
-        <v>3838.814049294797</v>
+        <v>3879.652496627721</v>
       </c>
       <c r="N96">
-        <v>-296.8140492947973</v>
+        <v>-337.6524966277211</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-296.8140492947973</v>
+        <v>-337.6524966277211</v>
       </c>
       <c r="Q96">
-        <v>866.1859507052027</v>
+        <v>825.3475033722789</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7084569832666537</v>
+        <v>0.840988379919985</v>
       </c>
       <c r="T96">
-        <v>12.13679536404896</v>
+        <v>14.56415443685876</v>
       </c>
       <c r="U96">
         <v>0.1269811058765187</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9226807952968383</v>
+        <v>0.9129683658726611</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.162681469578692</v>
+        <v>0.1634932806374572</v>
       </c>
       <c r="C97">
-        <v>-12015.89375496434</v>
+        <v>-12418.86611193638</v>
       </c>
       <c r="D97">
-        <v>13410.09654896673</v>
+        <v>13328.73461624659</v>
       </c>
       <c r="E97">
-        <v>10352.74787874047</v>
+        <v>10674.35830299238</v>
       </c>
       <c r="F97">
-        <v>30552.99030393107</v>
+        <v>30874.60072818297</v>
       </c>
       <c r="G97">
         <v>5127</v>
@@ -9241,28 +9241,28 @@
         <v>3542</v>
       </c>
       <c r="M97">
-        <v>3879.652496627721</v>
+        <v>3920.490943960644</v>
       </c>
       <c r="N97">
-        <v>-337.6524966277211</v>
+        <v>-378.4909439606445</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-337.6524966277211</v>
+        <v>-378.4909439606445</v>
       </c>
       <c r="Q97">
-        <v>825.3475033722789</v>
+        <v>784.5090560393555</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.840988379919985</v>
+        <v>1.039785474899982</v>
       </c>
       <c r="T97">
-        <v>14.56415443685876</v>
+        <v>18.20519304607345</v>
       </c>
       <c r="U97">
         <v>0.1269811058765187</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9129683658726611</v>
+        <v>0.9034582787281541</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1634932806374572</v>
+        <v>0.1643050916962224</v>
       </c>
       <c r="C98">
-        <v>-12418.86611193638</v>
+        <v>-12820.85714222606</v>
       </c>
       <c r="D98">
-        <v>13328.73461624659</v>
+        <v>13248.35401020881</v>
       </c>
       <c r="E98">
-        <v>10674.35830299238</v>
+        <v>10995.96872724428</v>
       </c>
       <c r="F98">
-        <v>30874.60072818297</v>
+        <v>31196.21115243487</v>
       </c>
       <c r="G98">
         <v>5127</v>
@@ -9323,28 +9323,28 @@
         <v>3542</v>
       </c>
       <c r="M98">
-        <v>3920.490943960644</v>
+        <v>3961.329391293567</v>
       </c>
       <c r="N98">
-        <v>-378.490943960644</v>
+        <v>-419.3293912935669</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-378.490943960644</v>
+        <v>-419.3293912935669</v>
       </c>
       <c r="Q98">
-        <v>784.509056039356</v>
+        <v>743.6706087064331</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.039785474899979</v>
+        <v>1.371113966533306</v>
       </c>
       <c r="T98">
-        <v>18.2051930460734</v>
+        <v>24.27359072809788</v>
       </c>
       <c r="U98">
         <v>0.1269811058765187</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9034582787281542</v>
+        <v>0.8941442758546683</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1643050916962224</v>
+        <v>0.1651169027549875</v>
       </c>
       <c r="C99">
-        <v>-12820.85714222606</v>
+        <v>-13221.88449344821</v>
       </c>
       <c r="D99">
-        <v>13248.35401020881</v>
+        <v>13168.93708323856</v>
       </c>
       <c r="E99">
-        <v>10995.96872724428</v>
+        <v>11317.57915149619</v>
       </c>
       <c r="F99">
-        <v>31196.21115243487</v>
+        <v>31517.82157668678</v>
       </c>
       <c r="G99">
         <v>5127</v>
@@ -9405,28 +9405,28 @@
         <v>3542</v>
       </c>
       <c r="M99">
-        <v>3961.329391293567</v>
+        <v>4002.16783862649</v>
       </c>
       <c r="N99">
-        <v>-419.3293912935669</v>
+        <v>-460.1678386264903</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-419.3293912935669</v>
+        <v>-460.1678386264903</v>
       </c>
       <c r="Q99">
-        <v>743.6706087064331</v>
+        <v>702.8321613735097</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.371113966533306</v>
+        <v>2.033770949799958</v>
       </c>
       <c r="T99">
-        <v>24.27359072809788</v>
+        <v>36.41038609214681</v>
       </c>
       <c r="U99">
         <v>0.1269811058765187</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8941442758546683</v>
+        <v>0.8850203546724777</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1651169027549875</v>
+        <v>0.1659287138137527</v>
       </c>
       <c r="C100">
-        <v>-13221.88449344821</v>
+        <v>-13621.96539258635</v>
       </c>
       <c r="D100">
-        <v>13168.93708323856</v>
+        <v>13090.46660835234</v>
       </c>
       <c r="E100">
-        <v>11317.57915149619</v>
+        <v>11639.18957574809</v>
       </c>
       <c r="F100">
-        <v>31517.82157668678</v>
+        <v>31839.43200093869</v>
       </c>
       <c r="G100">
         <v>5127</v>
@@ -9487,28 +9487,28 @@
         <v>3542</v>
       </c>
       <c r="M100">
-        <v>4002.16783862649</v>
+        <v>4043.006285959414</v>
       </c>
       <c r="N100">
-        <v>-460.1678386264903</v>
+        <v>-501.0062859594141</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-460.1678386264903</v>
+        <v>-501.0062859594141</v>
       </c>
       <c r="Q100">
-        <v>702.8321613735097</v>
+        <v>661.9937140405859</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.033770949799958</v>
+        <v>4.021741899599916</v>
       </c>
       <c r="T100">
-        <v>36.41038609214681</v>
+        <v>72.82077218429362</v>
       </c>
       <c r="U100">
         <v>0.1269811058765187</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8850203546724777</v>
+        <v>0.8760807551303313</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1659287138137527</v>
-      </c>
-      <c r="C101">
-        <v>-13621.96539258635</v>
-      </c>
-      <c r="D101">
-        <v>13090.46660835234</v>
-      </c>
-      <c r="E101">
-        <v>11639.18957574809</v>
-      </c>
-      <c r="F101">
-        <v>31839.43200093869</v>
-      </c>
-      <c r="G101">
-        <v>5127</v>
-      </c>
-      <c r="H101">
-        <v>11960.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4705</v>
-      </c>
-      <c r="K101">
-        <v>1163</v>
-      </c>
-      <c r="L101">
-        <v>3542</v>
-      </c>
-      <c r="M101">
-        <v>4043.006285959414</v>
-      </c>
-      <c r="N101">
-        <v>-501.0062859594141</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-501.0062859594141</v>
-      </c>
-      <c r="Q101">
-        <v>661.9937140405859</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.021741899599916</v>
-      </c>
-      <c r="T101">
-        <v>72.82077218429362</v>
-      </c>
-      <c r="U101">
-        <v>0.1269811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.1269811058765187</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Caa/CCC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8760807551303313</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
